--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -552,7 +552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v6.85)</t>
+          <t>NINELIVES — item pool (v6.86)</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,8 @@
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score. Any card played on top of this card is cursed</t>
+          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score.
+Any card played on top of this card is cursed</t>
         </is>
       </c>
       <c r="O3" s="9" t="inlineStr">
@@ -2402,7 +2403,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>same-rank landing</t>
+          <t>conditional: rank-matched tie save</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr"/>
@@ -2435,7 +2436,8 @@
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>Safe if this card lands on a card of the same rank, or a card of the same rank lands on this card</t>
+          <t>If another pile's top card matches this rank → Safe
+If no pile's top card matches this rank → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
@@ -2623,7 +2625,8 @@
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>If this column has no Base → peek at the next card. If it has one → this sticker becomes a curse</t>
+          <t>If this column has no Base → peek at the next card.
+If it has one → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O13" s="9" t="inlineStr">
@@ -2679,7 +2682,8 @@
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → +1 coin per pile whose top card matches. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → +1 coin per pile whose top card matches.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
@@ -2735,7 +2739,8 @@
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → make all pile sizes equal. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → make all pile sizes equal.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O15" s="9" t="inlineStr">
@@ -2801,7 +2806,8 @@
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → this card is safe when it lands. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → this card is safe when it lands.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
@@ -2857,7 +2863,8 @@
       <c r="M17" s="8" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → +1 pile size to every pile whose top matches, including this one. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → +1 pile size to every pile whose top matches, including this one.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O17" s="9" t="inlineStr">
@@ -2927,7 +2934,8 @@
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → earn coins equal to pile size. Any card played on top of this card is cursed</t>
+          <t>At deal end if this card tops its pile → earn coins equal to pile size.
+Any card played on top of this card is cursed</t>
         </is>
       </c>
       <c r="O18" s="9" t="inlineStr">
@@ -2993,7 +3001,8 @@
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>If this column has no Pillar → peek at the next card. If it has one → this sticker becomes a curse</t>
+          <t>If this column has no Pillar → peek at the next card.
+If it has one → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
@@ -3049,7 +3058,8 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → bury 1 card under this pile. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → bury 1 card under this pile.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
@@ -3115,7 +3125,8 @@
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → optionally shuffle those piles. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → optionally shuffle those piles.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
@@ -3171,7 +3182,8 @@
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → this card shows a tell (higher, lower, or same) for the next draw. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → this card shows a tell (higher, lower, or same) for the next draw.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O22" s="9" t="inlineStr">
@@ -5123,7 +5135,7 @@
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>The suit your deck holds the fewest of is safe when it lands in this column. Rechecked at the start of each deal, shown on the plaque</t>
+          <t>The suit your deck holds the fewest of is safe when it lands in this column</t>
         </is>
       </c>
       <c r="O53" s="9" t="inlineStr">
@@ -12143,7 +12155,8 @@
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → bury 1 card under this pile. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → bury 1 card under this pile.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O3" s="9" t="inlineStr">
@@ -14211,7 +14224,8 @@
       <c r="M39" s="8" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → +1 coin per pile whose top card matches. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → +1 coin per pile whose top card matches.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O39" s="9" t="inlineStr">
@@ -14281,7 +14295,8 @@
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → earn coins equal to pile size. Any card played on top of this card is cursed</t>
+          <t>At deal end if this card tops its pile → earn coins equal to pile size.
+Any card played on top of this card is cursed</t>
         </is>
       </c>
       <c r="O40" s="9" t="inlineStr">
@@ -16712,7 +16727,8 @@
       <c r="M87" s="8" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>If this column has no Base → peek at the next card. If it has one → this sticker becomes a curse</t>
+          <t>If this column has no Base → peek at the next card.
+If it has one → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O87" s="9" t="inlineStr">
@@ -16778,7 +16794,8 @@
       <c r="M88" s="8" t="inlineStr"/>
       <c r="N88" s="11" t="inlineStr">
         <is>
-          <t>If this column has no Pillar → peek at the next card. If it has one → this sticker becomes a curse</t>
+          <t>If this column has no Pillar → peek at the next card.
+If it has one → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O88" s="9" t="inlineStr">
@@ -17693,7 +17710,8 @@
       <c r="M104" s="8" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score. Any card played on top of this card is cursed</t>
+          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score.
+Any card played on top of this card is cursed</t>
         </is>
       </c>
       <c r="O104" s="9" t="inlineStr">
@@ -17749,7 +17767,8 @@
       <c r="M105" s="8" t="inlineStr"/>
       <c r="N105" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → make all pile sizes equal. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → make all pile sizes equal.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O105" s="9" t="inlineStr">
@@ -17805,7 +17824,8 @@
       <c r="M106" s="8" t="inlineStr"/>
       <c r="N106" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → +1 pile size to every pile whose top matches, including this one. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → +1 pile size to every pile whose top matches, including this one.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O106" s="9" t="inlineStr">
@@ -18698,7 +18718,8 @@
       <c r="M122" s="8" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → this card is safe when it lands. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → this card is safe when it lands.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O122" s="9" t="inlineStr">
@@ -18721,7 +18742,7 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>same-rank landing</t>
+          <t>conditional: rank-matched tie save</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr"/>
@@ -18754,7 +18775,8 @@
       <c r="M123" s="8" t="inlineStr"/>
       <c r="N123" s="11" t="inlineStr">
         <is>
-          <t>Safe if this card lands on a card of the same rank, or a card of the same rank lands on this card</t>
+          <t>If another pile's top card matches this rank → Safe
+If no pile's top card matches this rank → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O123" s="9" t="inlineStr">
@@ -19398,7 +19420,7 @@
       <c r="M133" s="8" t="inlineStr"/>
       <c r="N133" s="11" t="inlineStr">
         <is>
-          <t>The suit your deck holds the fewest of is safe when it lands in this column. Rechecked at the start of each deal, shown on the plaque</t>
+          <t>The suit your deck holds the fewest of is safe when it lands in this column</t>
         </is>
       </c>
       <c r="O133" s="9" t="inlineStr">
@@ -20196,7 +20218,8 @@
       <c r="M149" s="8" t="inlineStr"/>
       <c r="N149" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → optionally shuffle those piles. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → optionally shuffle those piles.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O149" s="9" t="inlineStr">
@@ -21145,7 +21168,8 @@
       <c r="M170" s="8" t="inlineStr"/>
       <c r="N170" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → this card shows a tell (higher, lower, or same) for the next draw. If none does → this sticker becomes a curse</t>
+          <t>If another pile's top card matches this card's suit → this card shows a tell (higher, lower, or same) for the next draw.
+If none does → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O170" s="9" t="inlineStr">

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -552,7 +552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v6.88)</t>
+          <t>NINELIVES — item pool (v6.89)</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       <c r="M96" s="8" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>Set every top card in this column to the rank your full deck holds the most copies of</t>
+          <t>Set every top card in this column to {rank}</t>
         </is>
       </c>
       <c r="O96" s="9" t="inlineStr">
@@ -7909,7 +7909,11 @@
           <t>chorus</t>
         </is>
       </c>
-      <c r="P96" s="8" t="inlineStr"/>
+      <c r="P96" s="14" t="inlineStr">
+        <is>
+          <t>UNWIRED</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -9087,7 +9091,7 @@
       <c r="M114" s="8" t="inlineStr"/>
       <c r="N114" s="11" t="inlineStr">
         <is>
-          <t>25% chance to permanently purge a card from the deck</t>
+          <t>50% chance to purge a card from the deck</t>
         </is>
       </c>
       <c r="O114" s="9" t="inlineStr">
@@ -14315,7 +14319,7 @@
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Set every top card in this column to the rank your full deck holds the most copies of</t>
+          <t>Set every top card in this column to {rank}</t>
         </is>
       </c>
       <c r="O31" s="9" t="inlineStr">
@@ -14323,7 +14327,11 @@
           <t>chorus</t>
         </is>
       </c>
-      <c r="P31" s="8" t="inlineStr"/>
+      <c r="P31" s="14" t="inlineStr">
+        <is>
+          <t>UNWIRED</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -16760,7 +16768,7 @@
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>25% chance to permanently purge a card from the deck</t>
+          <t>50% chance to purge a card from the deck</t>
         </is>
       </c>
       <c r="O74" s="9" t="inlineStr">

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -7911,7 +7911,7 @@
       </c>
       <c r="P96" s="14" t="inlineStr">
         <is>
-          <t>UNWIRED</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="P31" s="14" t="inlineStr">
         <is>
-          <t>UNWIRED</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -552,7 +552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v6.89)</t>
+          <t>NINELIVES — item pool (v6.90)</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>charges the shield</t>
+          <t>conditional: rank-matched charge</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -3385,7 +3385,8 @@
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Charge the Same Shield</t>
+          <t>If another pile's top card matches this rank → Charge Same Shield
+If no pile's top card matches this rank → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O25" s="9" t="inlineStr">
@@ -3408,7 +3409,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>fires the equipped power</t>
+          <t>conditional: rank-matched power fire</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -3451,7 +3452,8 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>Fire your Same-Power</t>
+          <t>If another pile's top card matches this rank → Fire Same Power
+If no pile's top card matches this rank → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O26" s="9" t="inlineStr">
@@ -8392,7 +8394,7 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>fires the equipped power</t>
+          <t>conditional: rank-matched power fire</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr"/>
@@ -8590,7 +8592,7 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>charges the shield</t>
+          <t>conditional: rank-matched charge</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr"/>
@@ -20740,7 +20742,7 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>charges the shield</t>
+          <t>conditional: rank-matched charge</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr"/>
@@ -20783,7 +20785,8 @@
       <c r="M148" s="8" t="inlineStr"/>
       <c r="N148" s="11" t="inlineStr">
         <is>
-          <t>Charge the Same Shield</t>
+          <t>If another pile's top card matches this rank → Charge Same Shield
+If no pile's top card matches this rank → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O148" s="9" t="inlineStr">
@@ -20806,7 +20809,7 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>fires the equipped power</t>
+          <t>conditional: rank-matched power fire</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr"/>
@@ -20849,7 +20852,8 @@
       <c r="M149" s="8" t="inlineStr"/>
       <c r="N149" s="11" t="inlineStr">
         <is>
-          <t>Fire your Same-Power</t>
+          <t>If another pile's top card matches this rank → Fire Same Power
+If no pile's top card matches this rank → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O149" s="9" t="inlineStr">
@@ -20872,7 +20876,7 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>fires the equipped power</t>
+          <t>conditional: rank-matched power fire</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr"/>
@@ -20938,7 +20942,7 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>charges the shield</t>
+          <t>conditional: rank-matched charge</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr"/>

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -552,7 +552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v6.90)</t>
+          <t>NINELIVES — item pool (v6.91)</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       <c r="M51" s="8" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → shuffle the other piles in this column</t>
+          <t>When a ♦ lands in this column → optionally shuffle the other piles in this column</t>
         </is>
       </c>
       <c r="O51" s="9" t="inlineStr">
@@ -7519,7 +7519,7 @@
       <c r="M90" s="8" t="inlineStr"/>
       <c r="N90" s="11" t="inlineStr">
         <is>
-          <t>Reduce the cost of the Store's Purge by 3</t>
+          <t>Reduce the Store's Purge cost by 2 ({current} → {new}). Minimum 5</t>
         </is>
       </c>
       <c r="O90" s="9" t="inlineStr">
@@ -8714,32 +8714,28 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>Card Change</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>whole rank → one suit, at purchase</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t>Deck Shaping</t>
-        </is>
-      </c>
+          <t>under suit-topped piles</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr"/>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Transmute</t>
+          <t>Burrow</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>transmute</t>
+          <t>linkBury</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
@@ -8748,7 +8744,7 @@
         </is>
       </c>
       <c r="H109" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
@@ -8757,26 +8753,26 @@
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K109" s="8" t="inlineStr">
         <is>
-          <t>bossesBeaten</t>
+          <t>samesCalled</t>
         </is>
       </c>
       <c r="L109" s="8" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="M109" s="8" t="inlineStr"/>
       <c r="N109" s="11" t="inlineStr">
         <is>
-          <t>Change all {rank}s to {suit}</t>
+          <t>Bury 1 card under every pile with a {suit} top card</t>
         </is>
       </c>
       <c r="O109" s="9" t="inlineStr">
         <is>
-          <t>transmute</t>
+          <t>linkBury</t>
         </is>
       </c>
       <c r="P109" s="14" t="inlineStr">
@@ -8793,23 +8789,27 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Bury</t>
+          <t>Curse Removal</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>under suit-topped piles</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr"/>
+          <t>board-wide, every correct Same</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Burrow</t>
+          <t>Cleanse All</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>linkBury</t>
+          <t>sameCleanseAll</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
@@ -8832,28 +8832,24 @@
       </c>
       <c r="K110" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>correctSames</t>
         </is>
       </c>
       <c r="L110" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M110" s="8" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>Bury 1 card under every pile with a {suit} top card</t>
+          <t>When you call a correct Same → clear all curses from every top card on the board</t>
         </is>
       </c>
       <c r="O110" s="9" t="inlineStr">
         <is>
-          <t>linkBury</t>
-        </is>
-      </c>
-      <c r="P110" s="14" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+          <t>sameCleanseAll</t>
+        </is>
+      </c>
+      <c r="P110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -8863,27 +8859,23 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>Curse Removal</t>
+          <t>Coin Gain</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>board-wide, every correct Same</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>per alive pile</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr"/>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Cleanse All</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>sameCleanseAll</t>
+          <t>linkCoins</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -8896,31 +8888,21 @@
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J111" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K111" s="8" t="inlineStr">
-        <is>
-          <t>correctSames</t>
-        </is>
-      </c>
-      <c r="L111" s="8" t="n">
-        <v>40</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J111" s="8" t="inlineStr"/>
+      <c r="K111" s="8" t="inlineStr"/>
+      <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="inlineStr"/>
       <c r="N111" s="11" t="inlineStr">
         <is>
-          <t>When you call a correct Same → clear all curses from every top card on the board</t>
+          <t>Gain 1 coin for each alive pile</t>
         </is>
       </c>
       <c r="O111" s="9" t="inlineStr">
         <is>
-          <t>sameCleanseAll</t>
+          <t>linkCoins</t>
         </is>
       </c>
       <c r="P111" s="8" t="inlineStr"/>
@@ -8933,23 +8915,23 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Coin Gain</t>
+          <t>Shuffle</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>per alive pile</t>
+          <t>every alive pile</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr"/>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Link Shuffler</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>linkCoins</t>
+          <t>linkShuffle</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
@@ -8971,12 +8953,12 @@
       <c r="M112" s="8" t="inlineStr"/>
       <c r="N112" s="11" t="inlineStr">
         <is>
-          <t>Gain 1 coin for each alive pile</t>
+          <t>Shuffle every alive pile</t>
         </is>
       </c>
       <c r="O112" s="9" t="inlineStr">
         <is>
-          <t>linkCoins</t>
+          <t>linkShuffle</t>
         </is>
       </c>
       <c r="P112" s="8" t="inlineStr"/>
@@ -8989,23 +8971,23 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>Shuffle</t>
+          <t>Deck Removal</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>every alive pile</t>
+          <t>chance, from the draw pile</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr"/>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Link Shuffler</t>
+          <t>Long Odds</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>linkShuffle</t>
+          <t>linkPurge</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
@@ -9018,21 +9000,31 @@
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J113" s="8" t="inlineStr"/>
-      <c r="K113" s="8" t="inlineStr"/>
-      <c r="L113" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K113" s="8" t="inlineStr">
+        <is>
+          <t>removalsUsed</t>
+        </is>
+      </c>
+      <c r="L113" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="M113" s="8" t="inlineStr"/>
       <c r="N113" s="11" t="inlineStr">
         <is>
-          <t>Shuffle every alive pile</t>
+          <t>50% chance to purge a card from the deck</t>
         </is>
       </c>
       <c r="O113" s="9" t="inlineStr">
         <is>
-          <t>linkShuffle</t>
+          <t>linkPurge</t>
         </is>
       </c>
       <c r="P113" s="8" t="inlineStr"/>
@@ -9045,23 +9037,23 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Deck Removal</t>
+          <t>Card Change</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>chance, from the draw pile</t>
+          <t>every alive top → the called rank</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr"/>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Long Odds</t>
+          <t>Rank Flood</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>linkPurge</t>
+          <t>rankFlood</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
@@ -9084,21 +9076,21 @@
       </c>
       <c r="K114" s="8" t="inlineStr">
         <is>
-          <t>removalsUsed</t>
+          <t>samesCalled</t>
         </is>
       </c>
       <c r="L114" s="8" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="M114" s="8" t="inlineStr"/>
       <c r="N114" s="11" t="inlineStr">
         <is>
-          <t>50% chance to purge a card from the deck</t>
+          <t>A correct Same sets the top card of every alive pile to this card's rank. A Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
         </is>
       </c>
       <c r="O114" s="9" t="inlineStr">
         <is>
-          <t>linkPurge</t>
+          <t>rankFlood</t>
         </is>
       </c>
       <c r="P114" s="8" t="inlineStr"/>
@@ -9111,23 +9103,23 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>Card Change</t>
+          <t>Safety &amp; Saves</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>every alive top → the called rank</t>
+          <t>revive on a Same</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr"/>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Rank Flood</t>
+          <t>Rekindle</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>rankFlood</t>
+          <t>linkRevive</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
@@ -9150,21 +9142,21 @@
       </c>
       <c r="K115" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>correctSames</t>
         </is>
       </c>
       <c r="L115" s="8" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="M115" s="8" t="inlineStr"/>
       <c r="N115" s="11" t="inlineStr">
         <is>
-          <t>A correct Same sets the top card of every alive pile to this card's rank. A Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
+          <t>Revive a dead pile</t>
         </is>
       </c>
       <c r="O115" s="9" t="inlineStr">
         <is>
-          <t>rankFlood</t>
+          <t>linkRevive</t>
         </is>
       </c>
       <c r="P115" s="8" t="inlineStr"/>
@@ -9177,23 +9169,23 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Safety &amp; Saves</t>
+          <t>Pile Size &amp; Score</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>revive on a Same</t>
+          <t>board-wide + hub</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Rekindle</t>
+          <t>Same Heavy</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>linkRevive</t>
+          <t>linkHeavy</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr">
@@ -9216,21 +9208,21 @@
       </c>
       <c r="K116" s="8" t="inlineStr">
         <is>
-          <t>correctSames</t>
+          <t>perfectDeals</t>
         </is>
       </c>
       <c r="L116" s="8" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="M116" s="8" t="inlineStr"/>
       <c r="N116" s="11" t="inlineStr">
         <is>
-          <t>Revive a dead pile</t>
+          <t>Add +1 pile size to every pile, and +3 to the pile you called Same on</t>
         </is>
       </c>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>linkRevive</t>
+          <t>linkHeavy</t>
         </is>
       </c>
       <c r="P116" s="8" t="inlineStr"/>
@@ -9243,23 +9235,23 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>Pile Size &amp; Score</t>
+          <t>Peek</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>board-wide + hub</t>
+          <t>on a Same</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr"/>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Same Heavy</t>
+          <t>Same Peeker</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>linkHeavy</t>
+          <t>samePeek</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
@@ -9272,31 +9264,21 @@
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J117" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K117" s="8" t="inlineStr">
-        <is>
-          <t>perfectDeals</t>
-        </is>
-      </c>
-      <c r="L117" s="8" t="n">
-        <v>4</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J117" s="8" t="inlineStr"/>
+      <c r="K117" s="8" t="inlineStr"/>
+      <c r="L117" s="8" t="n"/>
       <c r="M117" s="8" t="inlineStr"/>
       <c r="N117" s="11" t="inlineStr">
         <is>
-          <t>Add +1 pile size to every pile, and +3 to the pile you called Same on</t>
+          <t>Peek the next card</t>
         </is>
       </c>
       <c r="O117" s="9" t="inlineStr">
         <is>
-          <t>linkHeavy</t>
+          <t>samePeek</t>
         </is>
       </c>
       <c r="P117" s="8" t="inlineStr"/>
@@ -9309,23 +9291,23 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Peek</t>
+          <t>Tell</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>on a Same</t>
+          <t>every alive pile, next draw</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr"/>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Same Peeker</t>
+          <t>Second Sight</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>samePeek</t>
+          <t>linkTell</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
@@ -9338,21 +9320,31 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J118" s="8" t="inlineStr"/>
-      <c r="K118" s="8" t="inlineStr"/>
-      <c r="L118" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J118" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K118" s="8" t="inlineStr">
+        <is>
+          <t>correctSames</t>
+        </is>
+      </c>
+      <c r="L118" s="8" t="n">
+        <v>16</v>
+      </c>
       <c r="M118" s="8" t="inlineStr"/>
       <c r="N118" s="11" t="inlineStr">
         <is>
-          <t>Peek the next card</t>
+          <t>Every alive pile shows a tell (higher/lower/same) for the next draw</t>
         </is>
       </c>
       <c r="O118" s="9" t="inlineStr">
         <is>
-          <t>samePeek</t>
+          <t>linkTell</t>
         </is>
       </c>
       <c r="P118" s="8" t="inlineStr"/>
@@ -9365,23 +9357,23 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Tell</t>
+          <t>Sticker Grant</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>every alive pile, next draw</t>
+          <t>every top in the column</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr"/>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Second Sight</t>
+          <t>Sticker Spray</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>linkTell</t>
+          <t>linkSticker</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
@@ -9404,21 +9396,21 @@
       </c>
       <c r="K119" s="8" t="inlineStr">
         <is>
-          <t>correctSames</t>
+          <t>stickersApplied</t>
         </is>
       </c>
       <c r="L119" s="8" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="M119" s="8" t="inlineStr"/>
       <c r="N119" s="11" t="inlineStr">
         <is>
-          <t>Every alive pile shows a tell (higher/lower/same) for the next draw</t>
+          <t>Apply a random sticker to every top card in this column</t>
         </is>
       </c>
       <c r="O119" s="9" t="inlineStr">
         <is>
-          <t>linkTell</t>
+          <t>linkSticker</t>
         </is>
       </c>
       <c r="P119" s="8" t="inlineStr"/>
@@ -9426,65 +9418,53 @@
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>Same-Powers</t>
+          <t>Cursed Stickers</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Sticker Grant</t>
+          <t>Curse · Denial</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>every top in the column</t>
+          <t>drains the base</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr"/>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Sticker Spray</t>
+          <t>Base Drain</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>linkSticker</t>
-        </is>
-      </c>
-      <c r="G120" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H120" s="8" t="n">
-        <v>9</v>
-      </c>
+          <t>drainBase</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J120" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K120" s="8" t="inlineStr">
-        <is>
-          <t>stickersApplied</t>
-        </is>
-      </c>
-      <c r="L120" s="8" t="n">
-        <v>70</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J120" s="8" t="inlineStr"/>
+      <c r="K120" s="8" t="inlineStr"/>
+      <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="inlineStr"/>
       <c r="N120" s="11" t="inlineStr">
         <is>
-          <t>Apply a random sticker to every top card in this column</t>
+          <t>Cursed. The column's Base is drained</t>
         </is>
       </c>
       <c r="O120" s="9" t="inlineStr">
         <is>
-          <t>linkSticker</t>
+          <t>drainBase</t>
         </is>
       </c>
       <c r="P120" s="8" t="inlineStr"/>
@@ -9497,23 +9477,23 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Curse · Denial</t>
+          <t>Curse · Size Penalty</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>drains the base</t>
+          <t>pile size 1</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr"/>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Base Drain</t>
+          <t>Flatline</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>drainBase</t>
+          <t>flatline</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -9533,12 +9513,12 @@
       <c r="M121" s="8" t="inlineStr"/>
       <c r="N121" s="11" t="inlineStr">
         <is>
-          <t>Cursed. The column's Base is drained</t>
+          <t>Cursed. While this card is a pile's top card, that pile size is 1</t>
         </is>
       </c>
       <c r="O121" s="9" t="inlineStr">
         <is>
-          <t>drainBase</t>
+          <t>flatline</t>
         </is>
       </c>
       <c r="P121" s="8" t="inlineStr"/>
@@ -9551,23 +9531,23 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Curse · Size Penalty</t>
+          <t>Curse · Denial</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>pile size 1</t>
+          <t>disables the pillar</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr"/>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Flatline</t>
+          <t>Jammer</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>flatline</t>
+          <t>jammer</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -9587,12 +9567,12 @@
       <c r="M122" s="8" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this card is a pile's top card, that pile size is 1</t>
+          <t>Cursed. While this is a pile's top card, the column's Pillar does not work</t>
         </is>
       </c>
       <c r="O122" s="9" t="inlineStr">
         <is>
-          <t>flatline</t>
+          <t>jammer</t>
         </is>
       </c>
       <c r="P122" s="8" t="inlineStr"/>
@@ -9605,23 +9585,23 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>Curse · Denial</t>
+          <t>Curse · Coin Loss</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>disables the pillar</t>
+          <t>takes coins</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Jammer</t>
+          <t>Leech</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>jammer</t>
+          <t>leech</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -9641,12 +9621,12 @@
       <c r="M123" s="8" t="inlineStr"/>
       <c r="N123" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, the column's Pillar does not work</t>
+          <t>Cursed. −3 coins</t>
         </is>
       </c>
       <c r="O123" s="9" t="inlineStr">
         <is>
-          <t>jammer</t>
+          <t>tributeCoin</t>
         </is>
       </c>
       <c r="P123" s="8" t="inlineStr"/>
@@ -9659,23 +9639,23 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Curse · Coin Loss</t>
+          <t>Curse · Denial</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>takes coins</t>
+          <t>forces your next guess</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr"/>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Leech</t>
+          <t>Magnet</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>leech</t>
+          <t>magnet</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -9695,12 +9675,12 @@
       <c r="M124" s="8" t="inlineStr"/>
       <c r="N124" s="11" t="inlineStr">
         <is>
-          <t>Cursed. −3 coins</t>
+          <t>Cursed. While this is a pile's top card, your next guess must be played there</t>
         </is>
       </c>
       <c r="O124" s="9" t="inlineStr">
         <is>
-          <t>tributeCoin</t>
+          <t>magnet</t>
         </is>
       </c>
       <c r="P124" s="8" t="inlineStr"/>
@@ -9713,23 +9693,27 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>Curse · Denial</t>
+          <t>Curse · Destruction</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>forces your next guess</t>
-        </is>
-      </c>
-      <c r="D125" s="8" t="inlineStr"/>
+          <t>chance to kill the pile anyway</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>Pile Destruction</t>
+        </is>
+      </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Magnet</t>
+          <t>Malfunction</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>magnet</t>
+          <t>malfunction</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -9749,12 +9733,12 @@
       <c r="M125" s="8" t="inlineStr"/>
       <c r="N125" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, your next guess must be played there</t>
+          <t>Cursed. 10% chance this card kills the pile anyway, even if the guess is correct</t>
         </is>
       </c>
       <c r="O125" s="9" t="inlineStr">
         <is>
-          <t>magnet</t>
+          <t>malfunction</t>
         </is>
       </c>
       <c r="P125" s="8" t="inlineStr"/>
@@ -9767,27 +9751,23 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Curse · Destruction</t>
+          <t>Curse · Denial</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>chance to kill the pile anyway</t>
-        </is>
-      </c>
-      <c r="D126" s="8" t="inlineStr">
-        <is>
-          <t>Pile Destruction</t>
-        </is>
-      </c>
+          <t>no Same here</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr"/>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Malfunction</t>
+          <t>Mute</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>malfunction</t>
+          <t>mute</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -9807,12 +9787,12 @@
       <c r="M126" s="8" t="inlineStr"/>
       <c r="N126" s="11" t="inlineStr">
         <is>
-          <t>Cursed. 10% chance this card kills the pile anyway, even if the guess is correct</t>
+          <t>Cursed. While this is a pile's top card, Same cannot be called there</t>
         </is>
       </c>
       <c r="O126" s="9" t="inlineStr">
         <is>
-          <t>malfunction</t>
+          <t>mute</t>
         </is>
       </c>
       <c r="P126" s="8" t="inlineStr"/>
@@ -9825,23 +9805,23 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>Curse · Denial</t>
+          <t>Curse · Sticker Removal</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>no Same here</t>
+          <t>strips stickers on contact</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr"/>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Mute</t>
+          <t>Peeler</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>mute</t>
+          <t>peeler</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -9861,12 +9841,12 @@
       <c r="M127" s="8" t="inlineStr"/>
       <c r="N127" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, Same cannot be called there</t>
+          <t>Cursed. Any card that lands on this card loses its stickers</t>
         </is>
       </c>
       <c r="O127" s="9" t="inlineStr">
         <is>
-          <t>mute</t>
+          <t>peeler</t>
         </is>
       </c>
       <c r="P127" s="8" t="inlineStr"/>
@@ -9879,23 +9859,27 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Curse · Sticker Removal</t>
+          <t>Curse · Destruction</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>strips stickers on contact</t>
-        </is>
-      </c>
-      <c r="D128" s="8" t="inlineStr"/>
+          <t>chance to destroy the column's item</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>Loadout</t>
+        </is>
+      </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Peeler</t>
+          <t>Saboteur</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>peeler</t>
+          <t>saboteur</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -9915,12 +9899,12 @@
       <c r="M128" s="8" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr">
         <is>
-          <t>Cursed. Any card this card touches loses ALL of its stickers</t>
+          <t>Cursed. 10% chance the column's Base or Pillar is destroyed</t>
         </is>
       </c>
       <c r="O128" s="9" t="inlineStr">
         <is>
-          <t>peeler</t>
+          <t>saboteur</t>
         </is>
       </c>
       <c r="P128" s="8" t="inlineStr"/>
@@ -9933,27 +9917,27 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>Curse · Destruction</t>
+          <t>Curse · Denial</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>chance to destroy the column's item</t>
+          <t>empties the Same shield</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Loadout</t>
+          <t>Same Shield &amp; Power</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Saboteur</t>
+          <t>Shield Drain</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>saboteur</t>
+          <t>drainShield</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -9973,12 +9957,12 @@
       <c r="M129" s="8" t="inlineStr"/>
       <c r="N129" s="11" t="inlineStr">
         <is>
-          <t>Cursed. 10% chance the column's Base or Pillar is destroyed</t>
+          <t>Cursed. Drain the Same Shield</t>
         </is>
       </c>
       <c r="O129" s="9" t="inlineStr">
         <is>
-          <t>saboteur</t>
+          <t>drainShield</t>
         </is>
       </c>
       <c r="P129" s="8" t="inlineStr"/>
@@ -9991,27 +9975,23 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Curse · Denial</t>
+          <t>Curse · Size Penalty</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>empties the Same shield</t>
-        </is>
-      </c>
-      <c r="D130" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>counts less</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr"/>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Shield Drain</t>
+          <t>Shrink</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>drainShield</t>
+          <t>shrink</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
@@ -10031,12 +10011,12 @@
       <c r="M130" s="8" t="inlineStr"/>
       <c r="N130" s="11" t="inlineStr">
         <is>
-          <t>Cursed. Drain the Same Shield</t>
+          <t>Cursed. This card counts −1 toward pile size</t>
         </is>
       </c>
       <c r="O130" s="9" t="inlineStr">
         <is>
-          <t>drainShield</t>
+          <t>shrink</t>
         </is>
       </c>
       <c r="P130" s="8" t="inlineStr"/>
@@ -10049,23 +10029,23 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>Curse · Size Penalty</t>
+          <t>Curse · Coin Loss</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>counts less</t>
+          <t>wipes bonus coins</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr"/>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Shrink</t>
+          <t>Spoiler</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
-          <t>shrink</t>
+          <t>spoiler</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -10085,12 +10065,12 @@
       <c r="M131" s="8" t="inlineStr"/>
       <c r="N131" s="11" t="inlineStr">
         <is>
-          <t>Cursed. This card counts −1 toward pile size</t>
+          <t>Cursed. Reset bonus coins earned this deal to 0</t>
         </is>
       </c>
       <c r="O131" s="9" t="inlineStr">
         <is>
-          <t>shrink</t>
+          <t>spoiler</t>
         </is>
       </c>
       <c r="P131" s="8" t="inlineStr"/>
@@ -10103,23 +10083,23 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Curse · Coin Loss</t>
+          <t>Curse · Deck Return</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>wipes bonus coins</t>
+          <t>bottom card back to the deck</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr"/>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Spoiler</t>
+          <t>Trapdoor</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>spoiler</t>
+          <t>trapdoor</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
@@ -10139,12 +10119,12 @@
       <c r="M132" s="8" t="inlineStr"/>
       <c r="N132" s="11" t="inlineStr">
         <is>
-          <t>Cursed. Reset bonus coins earned this deal to 0</t>
+          <t>Cursed. When it lands, the card at the BOTTOM of the pile returns to the deck</t>
         </is>
       </c>
       <c r="O132" s="9" t="inlineStr">
         <is>
-          <t>spoiler</t>
+          <t>trapdoor</t>
         </is>
       </c>
       <c r="P132" s="8" t="inlineStr"/>
@@ -10152,28 +10132,28 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>Cursed Stickers</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>Curse · Deck Return</t>
+          <t>Pack</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>bottom card back to the deck</t>
+          <t>stickers</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr"/>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Trapdoor</t>
+          <t>Large Sticker Pack</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>trapdoor</t>
+          <t>largeStickerPack</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -10181,24 +10161,36 @@
           <t>common</t>
         </is>
       </c>
-      <c r="H133" s="8" t="n"/>
+      <c r="H133" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J133" s="8" t="inlineStr"/>
-      <c r="K133" s="8" t="inlineStr"/>
-      <c r="L133" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K133" s="8" t="inlineStr">
+        <is>
+          <t>stickersApplied</t>
+        </is>
+      </c>
+      <c r="L133" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="M133" s="8" t="inlineStr"/>
       <c r="N133" s="11" t="inlineStr">
         <is>
-          <t>Cursed. When it lands, the card at the BOTTOM of the pile returns to the deck</t>
+          <t>Reveals 5 random stickers. Keep 2</t>
         </is>
       </c>
       <c r="O133" s="9" t="inlineStr">
         <is>
-          <t>trapdoor</t>
+          <t>sticker</t>
         </is>
       </c>
       <c r="P133" s="8" t="inlineStr"/>
@@ -10216,18 +10208,18 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>stickers</t>
+          <t>playing cards</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr"/>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Large Sticker Pack</t>
+          <t>Small Card Pack</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>largeStickerPack</t>
+          <t>smallCardPack</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -10236,35 +10228,25 @@
         </is>
       </c>
       <c r="H134" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J134" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K134" s="8" t="inlineStr">
-        <is>
-          <t>stickersApplied</t>
-        </is>
-      </c>
-      <c r="L134" s="8" t="n">
-        <v>50</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J134" s="8" t="inlineStr"/>
+      <c r="K134" s="8" t="inlineStr"/>
+      <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="inlineStr"/>
       <c r="N134" s="11" t="inlineStr">
         <is>
-          <t>Reveals 5 random stickers. Keep 2</t>
+          <t>Reveals 3 random cards. Keep 1 to swap into your deck</t>
         </is>
       </c>
       <c r="O134" s="9" t="inlineStr">
         <is>
-          <t>sticker</t>
+          <t>card</t>
         </is>
       </c>
       <c r="P134" s="8" t="inlineStr"/>
@@ -10282,18 +10264,18 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>playing cards</t>
+          <t>stickers</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr"/>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Small Card Pack</t>
+          <t>Small Sticker Pack</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>smallCardPack</t>
+          <t>stickerPack</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -10302,7 +10284,7 @@
         </is>
       </c>
       <c r="H135" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
@@ -10315,12 +10297,12 @@
       <c r="M135" s="8" t="inlineStr"/>
       <c r="N135" s="11" t="inlineStr">
         <is>
-          <t>Reveals 3 random cards. Keep 1 to swap into your deck</t>
+          <t>Reveals 3 random stickers. Keep 1</t>
         </is>
       </c>
       <c r="O135" s="9" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>sticker</t>
         </is>
       </c>
       <c r="P135" s="8" t="inlineStr"/>
@@ -10338,45 +10320,55 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>stickers</t>
+          <t>playing cards</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr"/>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Small Sticker Pack</t>
+          <t>Large Card Pack</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>stickerPack</t>
-        </is>
-      </c>
-      <c r="G136" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>cardPack</t>
+        </is>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H136" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J136" s="8" t="inlineStr"/>
-      <c r="K136" s="8" t="inlineStr"/>
-      <c r="L136" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J136" s="8" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="K136" s="8" t="inlineStr">
+        <is>
+          <t>dealsWonRegular</t>
+        </is>
+      </c>
+      <c r="L136" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="M136" s="8" t="inlineStr"/>
       <c r="N136" s="11" t="inlineStr">
         <is>
-          <t>Reveals 3 random stickers. Keep 1</t>
+          <t>Reveals 5 random cards. Keep 2 to swap into your deck</t>
         </is>
       </c>
       <c r="O136" s="9" t="inlineStr">
         <is>
-          <t>sticker</t>
+          <t>card</t>
         </is>
       </c>
       <c r="P136" s="8" t="inlineStr"/>
@@ -10384,33 +10376,33 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>Pack</t>
+          <t>Coin Gain</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>playing cards</t>
+          <t>if all column tops match</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr"/>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Large Card Pack</t>
+          <t>All Hearts</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>cardPack</t>
-        </is>
-      </c>
-      <c r="G137" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>allHeartsCoin</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H137" s="8" t="n">
@@ -10428,21 +10420,21 @@
       </c>
       <c r="K137" s="8" t="inlineStr">
         <is>
-          <t>dealsWonRegular</t>
+          <t>coinsEarnedLifetime</t>
         </is>
       </c>
       <c r="L137" s="8" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="M137" s="8" t="inlineStr"/>
       <c r="N137" s="11" t="inlineStr">
         <is>
-          <t>Reveals 5 random cards. Keep 2 to swap into your deck</t>
+          <t>At deal end → +4 coins if every surviving pile in this column has a ♥ top card</t>
         </is>
       </c>
       <c r="O137" s="9" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>allSuitTop</t>
         </is>
       </c>
       <c r="P137" s="8" t="inlineStr"/>
@@ -10460,18 +10452,18 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>if all column tops match</t>
+          <t>on a kill</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr"/>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>All Hearts</t>
+          <t>Last Coin</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>allHeartsCoin</t>
+          <t>deathBounty</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -10480,35 +10472,29 @@
         </is>
       </c>
       <c r="H138" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J138" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K138" s="8" t="inlineStr">
-        <is>
-          <t>coinsEarnedLifetime</t>
-        </is>
-      </c>
-      <c r="L138" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="M138" s="8" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J138" s="8" t="inlineStr"/>
+      <c r="K138" s="8" t="inlineStr"/>
+      <c r="L138" s="8" t="n"/>
+      <c r="M138" s="8" t="inlineStr">
+        <is>
+          <t>♥</t>
+        </is>
+      </c>
       <c r="N138" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +4 coins if every surviving pile in this column has a ♥ top card</t>
+          <t>+3 coins if it kills a pile</t>
         </is>
       </c>
       <c r="O138" s="9" t="inlineStr">
         <is>
-          <t>allSuitTop</t>
+          <t>deathBounty</t>
         </is>
       </c>
       <c r="P138" s="8" t="inlineStr"/>
@@ -10521,23 +10507,23 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>Coin Gain</t>
+          <t>Card Change</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>on a kill</t>
+          <t>counts as every suit</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr"/>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Last Coin</t>
+          <t>Wild Suit</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>deathBounty</t>
+          <t>wildSuit</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
@@ -10546,7 +10532,7 @@
         </is>
       </c>
       <c r="H139" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
@@ -10556,19 +10542,15 @@
       <c r="J139" s="8" t="inlineStr"/>
       <c r="K139" s="8" t="inlineStr"/>
       <c r="L139" s="8" t="n"/>
-      <c r="M139" s="8" t="inlineStr">
-        <is>
-          <t>♥</t>
-        </is>
-      </c>
+      <c r="M139" s="8" t="inlineStr"/>
       <c r="N139" s="11" t="inlineStr">
         <is>
-          <t>+3 coins if it kills a pile</t>
+          <t>Counts as every suit</t>
         </is>
       </c>
       <c r="O139" s="9" t="inlineStr">
         <is>
-          <t>deathBounty</t>
+          <t>wildSuit</t>
         </is>
       </c>
       <c r="P139" s="8" t="inlineStr"/>
@@ -10581,50 +10563,64 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Card Change</t>
+          <t>Safety &amp; Saves</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>counts as every suit</t>
+          <t>conditional: carrier safe on a matched bet</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr"/>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Wild Suit</t>
+          <t>Club Guard</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>wildSuit</t>
-        </is>
-      </c>
-      <c r="G140" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>clubGuard</t>
+        </is>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H140" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J140" s="8" t="inlineStr"/>
-      <c r="K140" s="8" t="inlineStr"/>
-      <c r="L140" s="8" t="n"/>
-      <c r="M140" s="8" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J140" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K140" s="8" t="inlineStr">
+        <is>
+          <t>cardsBuried</t>
+        </is>
+      </c>
+      <c r="L140" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="M140" s="8" t="inlineStr">
+        <is>
+          <t>♣</t>
+        </is>
+      </c>
       <c r="N140" s="11" t="inlineStr">
         <is>
-          <t>Counts as every suit</t>
+          <t>Safe if this card lands on a ♣, or a ♣ lands on this card</t>
         </is>
       </c>
       <c r="O140" s="9" t="inlineStr">
         <is>
-          <t>wildSuit</t>
+          <t>suitImmunity</t>
         </is>
       </c>
       <c r="P140" s="8" t="inlineStr"/>
@@ -10637,23 +10633,23 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>Safety &amp; Saves</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>conditional: carrier safe on a matched bet</t>
+          <t>on ♣ contact</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr"/>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Club Guard</t>
+          <t>Club Snob</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>clubGuard</t>
+          <t>clubSnob</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -10662,7 +10658,7 @@
         </is>
       </c>
       <c r="H141" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
@@ -10676,11 +10672,11 @@
       </c>
       <c r="K141" s="8" t="inlineStr">
         <is>
-          <t>cardsBuried</t>
+          <t>pilesLost</t>
         </is>
       </c>
       <c r="L141" s="8" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
@@ -10689,12 +10685,12 @@
       </c>
       <c r="N141" s="11" t="inlineStr">
         <is>
-          <t>Safe if this card lands on a ♣, or a ♣ lands on this card</t>
+          <t>When a ♣ lands on this card, or this card lands on a ♣ → bury 1 deck card under the pile</t>
         </is>
       </c>
       <c r="O141" s="9" t="inlineStr">
         <is>
-          <t>suitImmunity</t>
+          <t>clubSnob</t>
         </is>
       </c>
       <c r="P141" s="8" t="inlineStr"/>
@@ -10712,18 +10708,18 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>on ♣ contact</t>
+          <t>scales with deck left</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr"/>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Club Snob</t>
+          <t>Club Thin</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>clubSnob</t>
+          <t>clubThin</t>
         </is>
       </c>
       <c r="G142" s="12" t="inlineStr">
@@ -10732,7 +10728,7 @@
         </is>
       </c>
       <c r="H142" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
@@ -10746,25 +10742,21 @@
       </c>
       <c r="K142" s="8" t="inlineStr">
         <is>
-          <t>pilesLost</t>
+          <t>cardsBuried</t>
         </is>
       </c>
       <c r="L142" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="M142" s="8" t="inlineStr">
-        <is>
-          <t>♣</t>
-        </is>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="M142" s="8" t="inlineStr"/>
       <c r="N142" s="11" t="inlineStr">
         <is>
-          <t>When a ♣ lands on this card, or this card lands on a ♣ → bury 1 deck card under the pile</t>
+          <t>When a ♣ lands in this column → bury 1 card per 25 cards remaining in the deck</t>
         </is>
       </c>
       <c r="O142" s="9" t="inlineStr">
         <is>
-          <t>clubSnob</t>
+          <t>clubThin</t>
         </is>
       </c>
       <c r="P142" s="8" t="inlineStr"/>
@@ -10777,23 +10769,23 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>Bury</t>
+          <t>Coin Gain</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>scales with deck left</t>
+          <t>per other sticker</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr"/>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Club Thin</t>
+          <t>Collector</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr">
         <is>
-          <t>clubThin</t>
+          <t>collector</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -10802,7 +10794,7 @@
         </is>
       </c>
       <c r="H143" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
@@ -10816,21 +10808,25 @@
       </c>
       <c r="K143" s="8" t="inlineStr">
         <is>
-          <t>cardsBuried</t>
+          <t>stickersApplied</t>
         </is>
       </c>
       <c r="L143" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="M143" s="8" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="M143" s="8" t="inlineStr">
+        <is>
+          <t>♥</t>
+        </is>
+      </c>
       <c r="N143" s="11" t="inlineStr">
         <is>
-          <t>When a ♣ lands in this column → bury 1 card per 25 cards remaining in the deck</t>
+          <t>+1 coin per other sticker on this card</t>
         </is>
       </c>
       <c r="O143" s="9" t="inlineStr">
         <is>
-          <t>clubThin</t>
+          <t>collector</t>
         </is>
       </c>
       <c r="P143" s="8" t="inlineStr"/>
@@ -10848,18 +10844,18 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>per other sticker</t>
+          <t>per deck card left</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr"/>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Collector</t>
+          <t>Deep Pockets</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>collector</t>
+          <t>deepPockets</t>
         </is>
       </c>
       <c r="G144" s="12" t="inlineStr">
@@ -10868,7 +10864,7 @@
         </is>
       </c>
       <c r="H144" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
@@ -10877,16 +10873,16 @@
       </c>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K144" s="8" t="inlineStr">
         <is>
-          <t>stickersApplied</t>
+          <t>bestCoinsInClimb</t>
         </is>
       </c>
       <c r="L144" s="8" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
@@ -10895,12 +10891,12 @@
       </c>
       <c r="N144" s="11" t="inlineStr">
         <is>
-          <t>+1 coin per other sticker on this card</t>
+          <t>+1 coin per 10 cards left in the deck</t>
         </is>
       </c>
       <c r="O144" s="9" t="inlineStr">
         <is>
-          <t>collector</t>
+          <t>deepPockets</t>
         </is>
       </c>
       <c r="P144" s="8" t="inlineStr"/>
@@ -10913,23 +10909,23 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>Coin Gain</t>
+          <t>Safety &amp; Saves</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>per deck card left</t>
+          <t>conditional: carrier safe on a matched bet</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr"/>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Deep Pockets</t>
+          <t>Diamond Guard</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>deepPockets</t>
+          <t>diamondGuard</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
@@ -10938,7 +10934,7 @@
         </is>
       </c>
       <c r="H145" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
@@ -10956,21 +10952,21 @@
         </is>
       </c>
       <c r="L145" s="8" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>♥</t>
+          <t>♦</t>
         </is>
       </c>
       <c r="N145" s="11" t="inlineStr">
         <is>
-          <t>+1 coin per 10 cards left in the deck</t>
+          <t>Safe if this card lands on a ♦, or a ♦ lands on this card</t>
         </is>
       </c>
       <c r="O145" s="9" t="inlineStr">
         <is>
-          <t>deepPockets</t>
+          <t>suitImmunity</t>
         </is>
       </c>
       <c r="P145" s="8" t="inlineStr"/>
@@ -10983,23 +10979,23 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Safety &amp; Saves</t>
+          <t>Shuffle</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>conditional: carrier safe on a matched bet</t>
+          <t>every ♦-topped pile</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr"/>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Diamond Guard</t>
+          <t>Diamond Ripple</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>diamondGuard</t>
+          <t>diamondRipple</t>
         </is>
       </c>
       <c r="G146" s="12" t="inlineStr">
@@ -11008,7 +11004,7 @@
         </is>
       </c>
       <c r="H146" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
@@ -11017,16 +11013,16 @@
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K146" s="8" t="inlineStr">
         <is>
-          <t>bestCoinsInClimb</t>
+          <t>perfectDeals</t>
         </is>
       </c>
       <c r="L146" s="8" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
@@ -11035,12 +11031,12 @@
       </c>
       <c r="N146" s="11" t="inlineStr">
         <is>
-          <t>Safe if this card lands on a ♦, or a ♦ lands on this card</t>
+          <t>Shuffle every other pile with a ♦ top card</t>
         </is>
       </c>
       <c r="O146" s="9" t="inlineStr">
         <is>
-          <t>suitImmunity</t>
+          <t>diamondRipple</t>
         </is>
       </c>
       <c r="P146" s="8" t="inlineStr"/>
@@ -11053,23 +11049,23 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>Shuffle</t>
+          <t>Coin Gain</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>every ♦-topped pile</t>
+          <t>per buried card</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr"/>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Diamond Ripple</t>
+          <t>Excavator</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>diamondRipple</t>
+          <t>excavator</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
@@ -11078,7 +11074,7 @@
         </is>
       </c>
       <c r="H147" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
@@ -11092,25 +11088,21 @@
       </c>
       <c r="K147" s="8" t="inlineStr">
         <is>
-          <t>perfectDeals</t>
+          <t>cardsBuried</t>
         </is>
       </c>
       <c r="L147" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="M147" s="8" t="inlineStr">
-        <is>
-          <t>♦</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="M147" s="8" t="inlineStr"/>
       <c r="N147" s="11" t="inlineStr">
         <is>
-          <t>Shuffle every other pile with a ♦ top card</t>
+          <t>At deal end → +1 coin per buried card in this column's largest pile with a ♥ top card</t>
         </is>
       </c>
       <c r="O147" s="9" t="inlineStr">
         <is>
-          <t>diamondRipple</t>
+          <t>excavator</t>
         </is>
       </c>
       <c r="P147" s="8" t="inlineStr"/>
@@ -11128,18 +11120,18 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>per buried card</t>
+          <t>coin flip</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr"/>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Excavator</t>
+          <t>Gambler</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>excavator</t>
+          <t>gambler</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
@@ -11148,7 +11140,7 @@
         </is>
       </c>
       <c r="H148" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
@@ -11162,21 +11154,21 @@
       </c>
       <c r="K148" s="8" t="inlineStr">
         <is>
-          <t>cardsBuried</t>
+          <t>jokersPlayed</t>
         </is>
       </c>
       <c r="L148" s="8" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="M148" s="8" t="inlineStr"/>
       <c r="N148" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +1 coin per buried card in this column's largest pile with a ♥ top card</t>
+          <t>At deal end → 50/50: +3 coins or nothing</t>
         </is>
       </c>
       <c r="O148" s="9" t="inlineStr">
         <is>
-          <t>excavator</t>
+          <t>gambler</t>
         </is>
       </c>
       <c r="P148" s="8" t="inlineStr"/>
@@ -11194,18 +11186,18 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>coin flip</t>
+          <t>per ♥ top</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr"/>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Gambler</t>
+          <t>Heart Choir</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>gambler</t>
+          <t>heartChoir</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
@@ -11214,7 +11206,7 @@
         </is>
       </c>
       <c r="H149" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
@@ -11228,21 +11220,25 @@
       </c>
       <c r="K149" s="8" t="inlineStr">
         <is>
-          <t>jokersPlayed</t>
+          <t>heartsPlayed</t>
         </is>
       </c>
       <c r="L149" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M149" s="8" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="M149" s="8" t="inlineStr">
+        <is>
+          <t>♥</t>
+        </is>
+      </c>
       <c r="N149" s="11" t="inlineStr">
         <is>
-          <t>At deal end → 50/50: +3 coins or nothing</t>
+          <t>+1 coin per each pile with a ♥ top card</t>
         </is>
       </c>
       <c r="O149" s="9" t="inlineStr">
         <is>
-          <t>gambler</t>
+          <t>heartChoir</t>
         </is>
       </c>
       <c r="P149" s="8" t="inlineStr"/>
@@ -11255,23 +11251,23 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Coin Gain</t>
+          <t>Safety &amp; Saves</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>per ♥ top</t>
+          <t>conditional: carrier safe on a matched bet</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr"/>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Heart Choir</t>
+          <t>Heart Guard</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>heartChoir</t>
+          <t>heartGuard</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
@@ -11280,7 +11276,7 @@
         </is>
       </c>
       <c r="H150" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
@@ -11289,16 +11285,16 @@
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K150" s="8" t="inlineStr">
         <is>
-          <t>heartsPlayed</t>
+          <t>dealsSurvived</t>
         </is>
       </c>
       <c r="L150" s="8" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
@@ -11307,12 +11303,12 @@
       </c>
       <c r="N150" s="11" t="inlineStr">
         <is>
-          <t>+1 coin per each pile with a ♥ top card</t>
+          <t>Safe if this card lands on a ♥, or a ♥ lands on this card</t>
         </is>
       </c>
       <c r="O150" s="9" t="inlineStr">
         <is>
-          <t>heartChoir</t>
+          <t>suitImmunity</t>
         </is>
       </c>
       <c r="P150" s="8" t="inlineStr"/>
@@ -11325,23 +11321,23 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>Safety &amp; Saves</t>
+          <t>Coin Gain</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>conditional: carrier safe on a matched bet</t>
+          <t>on ♥ contact</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr"/>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Heart Guard</t>
+          <t>Heart Snob</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>heartGuard</t>
+          <t>heartSnob</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -11350,7 +11346,7 @@
         </is>
       </c>
       <c r="H151" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
@@ -11359,16 +11355,16 @@
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K151" s="8" t="inlineStr">
         <is>
-          <t>dealsSurvived</t>
+          <t>heartsPlayed</t>
         </is>
       </c>
       <c r="L151" s="8" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
@@ -11377,12 +11373,12 @@
       </c>
       <c r="N151" s="11" t="inlineStr">
         <is>
-          <t>Safe if this card lands on a ♥, or a ♥ lands on this card</t>
+          <t>When a ♥ lands on this card, or this card lands on a ♥ → +2 coins</t>
         </is>
       </c>
       <c r="O151" s="9" t="inlineStr">
         <is>
-          <t>suitImmunity</t>
+          <t>heartSnob</t>
         </is>
       </c>
       <c r="P151" s="8" t="inlineStr"/>
@@ -11400,18 +11396,18 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>on ♥ contact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr"/>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Heart Snob</t>
+          <t>Loose Change</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>heartSnob</t>
+          <t>looseChange</t>
         </is>
       </c>
       <c r="G152" s="12" t="inlineStr">
@@ -11429,16 +11425,16 @@
       </c>
       <c r="J152" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K152" s="8" t="inlineStr">
         <is>
-          <t>heartsPlayed</t>
+          <t>bestCoinsInClimb</t>
         </is>
       </c>
       <c r="L152" s="8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
@@ -11447,12 +11443,12 @@
       </c>
       <c r="N152" s="11" t="inlineStr">
         <is>
-          <t>When a ♥ lands on this card, or this card lands on a ♥ → +2 coins</t>
+          <t>+0–3 coins (random)</t>
         </is>
       </c>
       <c r="O152" s="9" t="inlineStr">
         <is>
-          <t>heartSnob</t>
+          <t>looseChange</t>
         </is>
       </c>
       <c r="P152" s="8" t="inlineStr"/>
@@ -11465,23 +11461,23 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>Coin Gain</t>
+          <t>Pile Size &amp; Score</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>conditional: +size to matching piles</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr"/>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Loose Change</t>
+          <t>Massive</t>
         </is>
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>looseChange</t>
+          <t>massive</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -11499,30 +11495,30 @@
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K153" s="8" t="inlineStr">
         <is>
-          <t>bestCoinsInClimb</t>
+          <t>stickersApplied</t>
         </is>
       </c>
       <c r="L153" s="8" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>♥</t>
+          <t>♦</t>
         </is>
       </c>
       <c r="N153" s="11" t="inlineStr">
         <is>
-          <t>+0–3 coins (random)</t>
+          <t>+2 pile size</t>
         </is>
       </c>
       <c r="O153" s="9" t="inlineStr">
         <is>
-          <t>looseChange</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="P153" s="8" t="inlineStr"/>
@@ -11535,23 +11531,27 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Pile Size &amp; Score</t>
+          <t>Safety &amp; Saves</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>conditional: +size to matching piles</t>
-        </is>
-      </c>
-      <c r="D154" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Massive</t>
+          <t>Perfect Ten</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>massive</t>
+          <t>sameTolSum10</t>
         </is>
       </c>
       <c r="G154" s="12" t="inlineStr">
@@ -11560,39 +11560,25 @@
         </is>
       </c>
       <c r="H154" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J154" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K154" s="8" t="inlineStr">
-        <is>
-          <t>stickersApplied</t>
-        </is>
-      </c>
-      <c r="L154" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M154" s="8" t="inlineStr">
-        <is>
-          <t>♦</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J154" s="8" t="inlineStr"/>
+      <c r="K154" s="8" t="inlineStr"/>
+      <c r="L154" s="8" t="n"/>
+      <c r="M154" s="8" t="inlineStr"/>
       <c r="N154" s="11" t="inlineStr">
         <is>
-          <t>+2 pile size</t>
+          <t>Ranks summing to 10 survive a Same call in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
         </is>
       </c>
       <c r="O154" s="9" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P154" s="8" t="inlineStr"/>
@@ -11605,27 +11591,23 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>Safety &amp; Saves</t>
+          <t>Shuffle</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>this pile, optional</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr"/>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Perfect Ten</t>
+          <t>Shuffle</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>sameTolSum10</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -11634,7 +11616,7 @@
         </is>
       </c>
       <c r="H155" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
@@ -11644,15 +11626,19 @@
       <c r="J155" s="8" t="inlineStr"/>
       <c r="K155" s="8" t="inlineStr"/>
       <c r="L155" s="8" t="n"/>
-      <c r="M155" s="8" t="inlineStr"/>
+      <c r="M155" s="8" t="inlineStr">
+        <is>
+          <t>♦</t>
+        </is>
+      </c>
       <c r="N155" s="11" t="inlineStr">
         <is>
-          <t>Ranks summing to 10 survive a Same call in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
+          <t>Optionally shuffle the pile</t>
         </is>
       </c>
       <c r="O155" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="P155" s="8" t="inlineStr"/>
@@ -11665,23 +11651,23 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Shuffle</t>
+          <t>Peek</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>this pile, optional</t>
+          <t>on ♠ contact</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr"/>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Shuffle</t>
+          <t>Spade Snob</t>
         </is>
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>suitSnob</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
@@ -11690,29 +11676,39 @@
         </is>
       </c>
       <c r="H156" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J156" s="8" t="inlineStr"/>
-      <c r="K156" s="8" t="inlineStr"/>
-      <c r="L156" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J156" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K156" s="8" t="inlineStr">
+        <is>
+          <t>spadesPlayed</t>
+        </is>
+      </c>
+      <c r="L156" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>♦</t>
+          <t>♠</t>
         </is>
       </c>
       <c r="N156" s="11" t="inlineStr">
         <is>
-          <t>Optionally shuffle the pile</t>
+          <t>When a ♠ lands on this card, or this card lands on a ♠ → peek at the next card</t>
         </is>
       </c>
       <c r="O156" s="9" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>suitSnob</t>
         </is>
       </c>
       <c r="P156" s="8" t="inlineStr"/>
@@ -11725,32 +11721,32 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>Peek</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>on ♠ contact</t>
+          <t>sticker-free ♣</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr"/>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Spade Snob</t>
+          <t>Clean Bury</t>
         </is>
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>suitSnob</t>
-        </is>
-      </c>
-      <c r="G157" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>clubTribute</t>
+        </is>
+      </c>
+      <c r="G157" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H157" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
@@ -11764,25 +11760,21 @@
       </c>
       <c r="K157" s="8" t="inlineStr">
         <is>
-          <t>spadesPlayed</t>
+          <t>clubsPlayed</t>
         </is>
       </c>
       <c r="L157" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="M157" s="8" t="inlineStr">
-        <is>
-          <t>♠</t>
-        </is>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="M157" s="8" t="inlineStr"/>
       <c r="N157" s="11" t="inlineStr">
         <is>
-          <t>When a ♠ lands on this card, or this card lands on a ♠ → peek at the next card</t>
+          <t>When a ♣ with no stickers lands in this column → bury 1 card under that pile</t>
         </is>
       </c>
       <c r="O157" s="9" t="inlineStr">
         <is>
-          <t>suitSnob</t>
+          <t>clubTribute</t>
         </is>
       </c>
       <c r="P157" s="8" t="inlineStr"/>
@@ -11795,23 +11787,23 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Bury</t>
+          <t>Coin Gain</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>sticker-free ♣</t>
+          <t>streak-grown</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr"/>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Clean Bury</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>clubTribute</t>
+          <t>compound</t>
         </is>
       </c>
       <c r="G158" s="13" t="inlineStr">
@@ -11820,7 +11812,7 @@
         </is>
       </c>
       <c r="H158" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
@@ -11829,26 +11821,30 @@
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K158" s="8" t="inlineStr">
         <is>
-          <t>clubsPlayed</t>
+          <t>bestCampaignScore</t>
         </is>
       </c>
       <c r="L158" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="M158" s="8" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="M158" s="8" t="inlineStr">
+        <is>
+          <t>♥</t>
+        </is>
+      </c>
       <c r="N158" s="11" t="inlineStr">
         <is>
-          <t>When a ♣ with no stickers lands in this column → bury 1 card under that pile</t>
+          <t>+X coins. X starts at 0, grows by 1 each correct placement, resets to 0 on a wrong guess</t>
         </is>
       </c>
       <c r="O158" s="9" t="inlineStr">
         <is>
-          <t>clubTribute</t>
+          <t>compound</t>
         </is>
       </c>
       <c r="P158" s="8" t="inlineStr"/>
@@ -11866,18 +11862,18 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>streak-grown</t>
+          <t>highest ♥ top</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr"/>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Compound</t>
+          <t>Highest Heart</t>
         </is>
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>compound</t>
+          <t>highestEven</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
@@ -11886,7 +11882,7 @@
         </is>
       </c>
       <c r="H159" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
@@ -11904,21 +11900,17 @@
         </is>
       </c>
       <c r="L159" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="M159" s="8" t="inlineStr">
-        <is>
-          <t>♥</t>
-        </is>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="M159" s="8" t="inlineStr"/>
       <c r="N159" s="11" t="inlineStr">
         <is>
-          <t>+X coins. X starts at 0, grows by 1 each correct placement, resets to 0 on a wrong guess</t>
+          <t>At deal end → earn coins equal to the highest numbered ♥ top card in this column (2–10 face value, Ace pays 1, royals pay 0)</t>
         </is>
       </c>
       <c r="O159" s="9" t="inlineStr">
         <is>
-          <t>compound</t>
+          <t>highestHeart</t>
         </is>
       </c>
       <c r="P159" s="8" t="inlineStr"/>
@@ -11936,18 +11928,18 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>highest ♥ top</t>
+          <t>on prime ranks</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr"/>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Highest Heart</t>
+          <t>Prime</t>
         </is>
       </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>highestEven</t>
+          <t>prime</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr">
@@ -11956,7 +11948,7 @@
         </is>
       </c>
       <c r="H160" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
@@ -11970,21 +11962,21 @@
       </c>
       <c r="K160" s="8" t="inlineStr">
         <is>
-          <t>bestCampaignScore</t>
+          <t>bossesBeaten</t>
         </is>
       </c>
       <c r="L160" s="8" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="M160" s="8" t="inlineStr"/>
       <c r="N160" s="11" t="inlineStr">
         <is>
-          <t>At deal end → earn coins equal to the highest numbered ♥ top card in this column (2–10 face value, Ace pays 1, royals pay 0)</t>
+          <t>When a prime-rank card (2/3/5/7) lands correctly in this column → +1 coin</t>
         </is>
       </c>
       <c r="O160" s="9" t="inlineStr">
         <is>
-          <t>highestHeart</t>
+          <t>prime</t>
         </is>
       </c>
       <c r="P160" s="8" t="inlineStr"/>
@@ -11997,23 +11989,23 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>Coin Gain</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>on prime ranks</t>
+          <t>per rank-matching top</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr"/>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Prime</t>
+          <t>Rank Roots</t>
         </is>
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>prime</t>
+          <t>clubRoots</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
@@ -12022,7 +12014,7 @@
         </is>
       </c>
       <c r="H161" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I161" s="8" t="inlineStr">
         <is>
@@ -12031,26 +12023,30 @@
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K161" s="8" t="inlineStr">
         <is>
-          <t>bossesBeaten</t>
+          <t>clubsPlayed</t>
         </is>
       </c>
       <c r="L161" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="M161" s="8" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="M161" s="8" t="inlineStr">
+        <is>
+          <t>♣</t>
+        </is>
+      </c>
       <c r="N161" s="11" t="inlineStr">
         <is>
-          <t>When a prime-rank card (2/3/5/7) lands correctly in this column → +1 coin</t>
+          <t>When this card lands → bury 1 card under each pile whose top card matches this card's rank</t>
         </is>
       </c>
       <c r="O161" s="9" t="inlineStr">
         <is>
-          <t>prime</t>
+          <t>clubRoots</t>
         </is>
       </c>
       <c r="P161" s="8" t="inlineStr"/>
@@ -12063,23 +12059,23 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Bury</t>
+          <t>Peek</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>per rank-matching top</t>
+          <t>on landing</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr"/>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Rank Roots</t>
+          <t>Scout</t>
         </is>
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>clubRoots</t>
+          <t>revealNext</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
@@ -12088,7 +12084,7 @@
         </is>
       </c>
       <c r="H162" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
@@ -12102,25 +12098,25 @@
       </c>
       <c r="K162" s="8" t="inlineStr">
         <is>
-          <t>clubsPlayed</t>
+          <t>zenEasyWon</t>
         </is>
       </c>
       <c r="L162" s="8" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="M162" s="8" t="inlineStr">
         <is>
-          <t>♣</t>
+          <t>♠</t>
         </is>
       </c>
       <c r="N162" s="11" t="inlineStr">
         <is>
-          <t>When this card lands → bury 1 card under each pile whose top card matches this card's rank</t>
+          <t>Peek at the next deck card</t>
         </is>
       </c>
       <c r="O162" s="9" t="inlineStr">
         <is>
-          <t>clubRoots</t>
+          <t>revealNext</t>
         </is>
       </c>
       <c r="P162" s="8" t="inlineStr"/>
@@ -12133,23 +12129,23 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>Peek</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>on landing</t>
+          <t>streak-grown</t>
         </is>
       </c>
       <c r="D163" s="8" t="inlineStr"/>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Scout</t>
+          <t>Snowball Bury</t>
         </is>
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>revealNext</t>
+          <t>snowball</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
@@ -12172,25 +12168,25 @@
       </c>
       <c r="K163" s="8" t="inlineStr">
         <is>
-          <t>zenEasyWon</t>
+          <t>perfectDeals</t>
         </is>
       </c>
       <c r="L163" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M163" s="8" t="inlineStr">
         <is>
-          <t>♠</t>
+          <t>♣</t>
         </is>
       </c>
       <c r="N163" s="11" t="inlineStr">
         <is>
-          <t>Peek at the next deck card</t>
+          <t>Bury X cards. X starts at 0, grows by 1 each correct placement, resets to 0 on a wrong guess</t>
         </is>
       </c>
       <c r="O163" s="9" t="inlineStr">
         <is>
-          <t>revealNext</t>
+          <t>snowball</t>
         </is>
       </c>
       <c r="P163" s="8" t="inlineStr"/>
@@ -12203,23 +12199,23 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Bury</t>
+          <t>Tell</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>streak-grown</t>
+          <t>scales with ♠ tops</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr"/>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Snowball Bury</t>
+          <t>Spade Whispers</t>
         </is>
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>snowball</t>
+          <t>spadeWhispers</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
@@ -12228,7 +12224,7 @@
         </is>
       </c>
       <c r="H164" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
@@ -12242,25 +12238,25 @@
       </c>
       <c r="K164" s="8" t="inlineStr">
         <is>
-          <t>perfectDeals</t>
+          <t>spadesPlayed</t>
         </is>
       </c>
       <c r="L164" s="8" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>♣</t>
+          <t>♠</t>
         </is>
       </c>
       <c r="N164" s="11" t="inlineStr">
         <is>
-          <t>Bury X cards. X starts at 0, grows by 1 each correct placement, resets to 0 on a wrong guess</t>
+          <t>The next X cards show a hint (higher/lower/same), where X = other piles with a ♠ top card</t>
         </is>
       </c>
       <c r="O164" s="9" t="inlineStr">
         <is>
-          <t>snowball</t>
+          <t>spadeWhispers</t>
         </is>
       </c>
       <c r="P164" s="8" t="inlineStr"/>
@@ -12273,23 +12269,23 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>Tell</t>
+          <t>Peek</t>
         </is>
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>scales with ♠ tops</t>
+          <t>50% on a ♠</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr"/>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Spade Whispers</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>spadeWhispers</t>
+          <t>static</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
@@ -12298,7 +12294,7 @@
         </is>
       </c>
       <c r="H165" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
@@ -12312,25 +12308,21 @@
       </c>
       <c r="K165" s="8" t="inlineStr">
         <is>
-          <t>spadesPlayed</t>
+          <t>zenMediumWon</t>
         </is>
       </c>
       <c r="L165" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="M165" s="8" t="inlineStr">
-        <is>
-          <t>♠</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M165" s="8" t="inlineStr"/>
       <c r="N165" s="11" t="inlineStr">
         <is>
-          <t>The next X cards show a hint (higher/lower/same), where X = other piles with a ♠ top card</t>
+          <t>When a ♠ lands in this column → 50% chance to peek at the next card</t>
         </is>
       </c>
       <c r="O165" s="9" t="inlineStr">
         <is>
-          <t>spadeWhispers</t>
+          <t>static</t>
         </is>
       </c>
       <c r="P165" s="8" t="inlineStr"/>
@@ -12343,23 +12335,27 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Peek</t>
+          <t>Card Change</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>50% on a ♠</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="inlineStr"/>
+          <t>whole rank → one suit, at purchase</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t>Deck Shaping</t>
+        </is>
+      </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Static</t>
+          <t>Transmute</t>
         </is>
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>transmute</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
@@ -12368,7 +12364,7 @@
         </is>
       </c>
       <c r="H166" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
@@ -12377,29 +12373,33 @@
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K166" s="8" t="inlineStr">
         <is>
-          <t>zenMediumWon</t>
+          <t>bossesBeaten</t>
         </is>
       </c>
       <c r="L166" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M166" s="8" t="inlineStr"/>
       <c r="N166" s="11" t="inlineStr">
         <is>
-          <t>When a ♠ lands in this column → 50% chance to peek at the next card</t>
+          <t>Change all {rank}s to {suit}</t>
         </is>
       </c>
       <c r="O166" s="9" t="inlineStr">
         <is>
-          <t>static</t>
-        </is>
-      </c>
-      <c r="P166" s="8" t="inlineStr"/>
+          <t>transmute</t>
+        </is>
+      </c>
+      <c r="P166" s="14" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
@@ -14470,7 +14470,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -14480,22 +14480,18 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>whole rank → one suit, at purchase</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Deck Shaping</t>
-        </is>
-      </c>
+          <t>every alive top → the called rank</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Transmute</t>
+          <t>Rank Flood</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>transmute</t>
+          <t>rankFlood</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
@@ -14504,7 +14500,7 @@
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
@@ -14513,38 +14509,34 @@
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>bossesBeaten</t>
+          <t>samesCalled</t>
         </is>
       </c>
       <c r="L34" s="8" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>Change all {rank}s to {suit}</t>
+          <t>A correct Same sets the top card of every alive pile to this card's rank. A Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
         </is>
       </c>
       <c r="O34" s="9" t="inlineStr">
         <is>
-          <t>transmute</t>
-        </is>
-      </c>
-      <c r="P34" s="14" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+          <t>rankFlood</t>
+        </is>
+      </c>
+      <c r="P34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Same-Powers</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -14554,18 +14546,22 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>every alive top → the called rank</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr"/>
+          <t>whole rank → one suit, at purchase</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Deck Shaping</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Rank Flood</t>
+          <t>Transmute</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>rankFlood</t>
+          <t>transmute</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -14574,7 +14570,7 @@
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
@@ -14583,29 +14579,33 @@
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>bossesBeaten</t>
         </is>
       </c>
       <c r="L35" s="8" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="M35" s="8" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>A correct Same sets the top card of every alive pile to this card's rank. A Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
+          <t>Change all {rank}s to {suit}</t>
         </is>
       </c>
       <c r="O35" s="9" t="inlineStr">
         <is>
-          <t>rankFlood</t>
-        </is>
-      </c>
-      <c r="P35" s="8" t="inlineStr"/>
+          <t>transmute</t>
+        </is>
+      </c>
+      <c r="P35" s="14" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -21115,7 +21115,7 @@
       <c r="M155" s="8" t="inlineStr"/>
       <c r="N155" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → shuffle the other piles in this column</t>
+          <t>When a ♦ lands in this column → optionally shuffle the other piles in this column</t>
         </is>
       </c>
       <c r="O155" s="9" t="inlineStr">
@@ -21945,7 +21945,7 @@
       <c r="M172" s="8" t="inlineStr"/>
       <c r="N172" s="11" t="inlineStr">
         <is>
-          <t>Reduce the cost of the Store's Purge by 3</t>
+          <t>Reduce the Store's Purge cost by 2 ({current} → {new}). Minimum 5</t>
         </is>
       </c>
       <c r="O172" s="9" t="inlineStr">
@@ -23282,7 +23282,7 @@
       <c r="M210" s="8" t="inlineStr"/>
       <c r="N210" s="11" t="inlineStr">
         <is>
-          <t>Cursed. Any card this card touches loses ALL of its stickers</t>
+          <t>Cursed. Any card that lands on this card loses its stickers</t>
         </is>
       </c>
       <c r="O210" s="9" t="inlineStr">

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v6.93)</t>
+          <t>NINELIVES — item pool (v6.96)</t>
         </is>
       </c>
     </row>
@@ -1906,8 +1906,7 @@
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score.
-Any card played on top of this card is cursed</t>
+          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score</t>
         </is>
       </c>
       <c r="O3" s="9" t="inlineStr">
@@ -2309,8 +2308,8 @@
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this rank → Safe
-If no pile's top card matches this rank → Sticker becomes cursed</t>
+          <t>If another pile shows this rank → Safe
+Otherwise → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
@@ -2555,8 +2554,8 @@
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → +1 coin per pile whose top card matches.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → +1 coin per pile whose top card matches.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
@@ -2612,8 +2611,8 @@
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → make all pile sizes equal.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → make all pile sizes equal.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O15" s="9" t="inlineStr">
@@ -2679,8 +2678,8 @@
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → this card is safe when it lands.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → this card is safe when it lands.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
@@ -2750,8 +2749,7 @@
       <c r="M17" s="8" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → earn coins equal to pile size.
-Any card played on top of this card is cursed</t>
+          <t>At deal end if this card tops its pile → earn coins equal to pile size</t>
         </is>
       </c>
       <c r="O17" s="9" t="inlineStr">
@@ -2874,8 +2872,8 @@
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → bury 1 card under this pile.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → bury 1 card under this pile.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
@@ -2941,8 +2939,8 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → optionally shuffle those piles.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → optionally shuffle those piles.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
@@ -2998,8 +2996,8 @@
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → this card shows a tell (higher, lower, or same) for the next draw.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → this card shows a tell (higher, lower, or same) for the next draw.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
@@ -3069,7 +3067,7 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Peek at the next card if another pile's top card matches this rank</t>
+          <t>Peek at the next card if another pile shows this rank</t>
         </is>
       </c>
       <c r="O22" s="9" t="inlineStr">
@@ -3201,8 +3199,8 @@
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this rank → Charge Same Shield
-If no pile's top card matches this rank → Sticker becomes cursed</t>
+          <t>If another pile shows this rank → Charge Same Shield
+Otherwise → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O24" s="9" t="inlineStr">
@@ -3268,8 +3266,8 @@
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this rank → Fire Same Power
-If no pile's top card matches this rank → Sticker becomes cursed</t>
+          <t>If another pile shows this rank → Fire Same Power
+Otherwise → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O25" s="9" t="inlineStr">
@@ -3539,7 +3537,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Peek</t>
+          <t>Tell</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3581,12 +3579,12 @@
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>While your purse holds under 10 coins → when a ♥ lands in this column, peek 1 card</t>
+          <t>While your purse holds under 10 coins → when a ♥ lands in this column, that pile gets a tell</t>
         </is>
       </c>
       <c r="O30" s="9" t="inlineStr">
         <is>
-          <t>pauperHeartPeek</t>
+          <t>pauperHeartTell</t>
         </is>
       </c>
       <c r="P30" s="8" t="inlineStr"/>
@@ -9791,8 +9789,8 @@
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → bury 1 card under this pile.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → bury 1 card under this pile.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O3" s="9" t="inlineStr">
@@ -11318,8 +11316,8 @@
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → +1 coin per pile whose top card matches.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → +1 coin per pile whose top card matches.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O31" s="9" t="inlineStr">
@@ -11389,8 +11387,7 @@
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → earn coins equal to pile size.
-Any card played on top of this card is cursed</t>
+          <t>At deal end if this card tops its pile → earn coins equal to pile size</t>
         </is>
       </c>
       <c r="O32" s="9" t="inlineStr">
@@ -13097,7 +13094,7 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>Peek  (14)</t>
+          <t>Peek  (13)</t>
         </is>
       </c>
     </row>
@@ -13295,7 +13292,7 @@
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>Peek at the next card if another pile's top card matches this rank</t>
+          <t>Peek at the next card if another pile shows this rank</t>
         </is>
       </c>
       <c r="O71" s="9" t="inlineStr">
@@ -13440,31 +13437,27 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>while broke, per ♥ landing</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Pauper</t>
-        </is>
-      </c>
+          <t>on a royal ♠</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr"/>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Pauper's Heart</t>
+          <t>Queen's Eye</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>pauperHeart</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>queensEye</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
@@ -13477,12 +13470,12 @@
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>While your purse holds under 10 coins → when a ♥ lands in this column, peek 1 card</t>
+          <t>When a royal ♠ (J/Q/K) lands in this column → peek at the next card</t>
         </is>
       </c>
       <c r="O74" s="9" t="inlineStr">
         <is>
-          <t>pauperHeartPeek</t>
+          <t>queensEye</t>
         </is>
       </c>
       <c r="P74" s="8" t="inlineStr"/>
@@ -13490,7 +13483,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -13500,18 +13493,22 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>on a royal ♠</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr"/>
+          <t>trades the deal's banked bonus</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Coin Loss</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Queen's Eye</t>
+          <t>Bonus Reset</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>queensEye</t>
+          <t>bonusResetPeek</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -13524,21 +13521,31 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J75" s="8" t="inlineStr"/>
-      <c r="K75" s="8" t="inlineStr"/>
-      <c r="L75" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="K75" s="8" t="inlineStr">
+        <is>
+          <t>coinsEarnedLifetime</t>
+        </is>
+      </c>
+      <c r="L75" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>When a royal ♠ (J/Q/K) lands in this column → peek at the next card</t>
+          <t>Reset bonus coins earned this deal to zero, then peek the next card</t>
         </is>
       </c>
       <c r="O75" s="9" t="inlineStr">
         <is>
-          <t>queensEye</t>
+          <t>bonusResetPeek</t>
         </is>
       </c>
       <c r="P75" s="8" t="inlineStr"/>
@@ -13556,22 +13563,22 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>trades the deal's banked bonus</t>
+          <t>destroys this column's pillar</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Coin Loss</t>
+          <t>Loadout</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Bonus Reset</t>
+          <t>Demolish</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>bonusResetPeek</t>
+          <t>demolish</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -13580,7 +13587,7 @@
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
@@ -13589,26 +13596,26 @@
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K76" s="8" t="inlineStr">
         <is>
-          <t>coinsEarnedLifetime</t>
+          <t>pillarsPlaced</t>
         </is>
       </c>
       <c r="L76" s="8" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>Reset bonus coins earned this deal to zero, then peek the next card</t>
+          <t>Destroy this column's pillar permanently, then peek the next 3 cards</t>
         </is>
       </c>
       <c r="O76" s="9" t="inlineStr">
         <is>
-          <t>bonusResetPeek</t>
+          <t>demolish</t>
         </is>
       </c>
       <c r="P76" s="8" t="inlineStr"/>
@@ -13626,31 +13633,27 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>destroys this column's pillar</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Loadout</t>
-        </is>
-      </c>
+          <t>spends the whole purse</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr"/>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Demolish</t>
+          <t>Empty Purse</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>demolish</t>
-        </is>
-      </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>emptyPurse</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
@@ -13659,26 +13662,26 @@
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K77" s="8" t="inlineStr">
         <is>
-          <t>pillarsPlaced</t>
+          <t>coinsEarnedLifetime</t>
         </is>
       </c>
       <c r="L77" s="8" t="n">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="M77" s="8" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>Destroy this column's pillar permanently, then peek the next 3 cards</t>
+          <t>Spend ALL your coins → peek 1 card, +1 more per 10 coins spent</t>
         </is>
       </c>
       <c r="O77" s="9" t="inlineStr">
         <is>
-          <t>demolish</t>
+          <t>emptyPurse</t>
         </is>
       </c>
       <c r="P77" s="8" t="inlineStr"/>
@@ -13696,18 +13699,22 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>spends the whole purse</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr"/>
+          <t>kills a ♠ pile first</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Pile Destruction</t>
+        </is>
+      </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Empty Purse</t>
+          <t>Kamikaze</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>emptyPurse</t>
+          <t>kamikaze</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
@@ -13716,7 +13723,7 @@
         </is>
       </c>
       <c r="H78" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
@@ -13730,21 +13737,21 @@
       </c>
       <c r="K78" s="8" t="inlineStr">
         <is>
-          <t>coinsEarnedLifetime</t>
+          <t>dealsWonLegendary</t>
         </is>
       </c>
       <c r="L78" s="8" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>Spend ALL your coins → peek 1 card, +1 more per 10 coins spent</t>
+          <t>Kill a random ♠-topped pile in this column, → peek the next 2 cards</t>
         </is>
       </c>
       <c r="O78" s="9" t="inlineStr">
         <is>
-          <t>emptyPurse</t>
+          <t>kamikaze</t>
         </is>
       </c>
       <c r="P78" s="8" t="inlineStr"/>
@@ -13762,22 +13769,18 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>kills a ♠ pile first</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Pile Destruction</t>
-        </is>
-      </c>
+          <t>needs an empty Same-Power slot</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr"/>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Kamikaze</t>
+          <t>Lone Eye</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>kamikaze</t>
+          <t>lonePeek</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -13786,35 +13789,35 @@
         </is>
       </c>
       <c r="H79" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K79" s="8" t="inlineStr">
+        <is>
+          <t>samesCalled</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="n">
         <v>8</v>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J79" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K79" s="8" t="inlineStr">
-        <is>
-          <t>dealsWonLegendary</t>
-        </is>
-      </c>
-      <c r="L79" s="8" t="n">
-        <v>2</v>
       </c>
       <c r="M79" s="8" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>Kill a random ♠-topped pile in this column, → peek the next 2 cards</t>
+          <t>Peek the next card. Only works while no Same-Power is equipped</t>
         </is>
       </c>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>kamikaze</t>
+          <t>lonePeek</t>
         </is>
       </c>
       <c r="P79" s="8" t="inlineStr"/>
@@ -13832,27 +13835,27 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>needs an empty Same-Power slot</t>
+          <t>needs an all-♠ column</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr"/>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Lone Eye</t>
+          <t>Spade Peeker</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>lonePeek</t>
-        </is>
-      </c>
-      <c r="G80" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>spadePeek</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H80" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
@@ -13866,21 +13869,21 @@
       </c>
       <c r="K80" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>zenHardWon</t>
         </is>
       </c>
       <c r="L80" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>Peek the next card. Only works while no Same-Power is equipped</t>
+          <t>Peek the next card. Requires every pile in this column has a ♠ on top</t>
         </is>
       </c>
       <c r="O80" s="9" t="inlineStr">
         <is>
-          <t>lonePeek</t>
+          <t>spadePeek</t>
         </is>
       </c>
       <c r="P80" s="8" t="inlineStr"/>
@@ -13888,7 +13891,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -13898,121 +13901,115 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>needs an all-♠ column</t>
+          <t>on a Same</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr"/>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Spade Peeker</t>
+          <t>Same Peeker</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>spadePeek</t>
-        </is>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>samePeek</t>
+        </is>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J81" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K81" s="8" t="inlineStr">
-        <is>
-          <t>zenHardWon</t>
-        </is>
-      </c>
-      <c r="L81" s="8" t="n">
-        <v>1</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr"/>
+      <c r="L81" s="8" t="n"/>
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>Peek the next card. Requires every pile in this column has a ♠ on top</t>
+          <t>Peek the next card</t>
         </is>
       </c>
       <c r="O81" s="9" t="inlineStr">
         <is>
-          <t>spadePeek</t>
+          <t>samePeek</t>
         </is>
       </c>
       <c r="P81" s="8" t="inlineStr"/>
     </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>Same-Powers</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Peek</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>on a Same</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr"/>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>Same Peeker</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>samePeek</t>
-        </is>
-      </c>
-      <c r="G82" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H82" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>Pile Size &amp; Score  (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Pile Size &amp; Score</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>score shelter; curses its cover</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Curse Payoff</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J82" s="8" t="inlineStr"/>
-      <c r="K82" s="8" t="inlineStr"/>
-      <c r="L82" s="8" t="n"/>
-      <c r="M82" s="8" t="inlineStr"/>
-      <c r="N82" s="11" t="inlineStr">
-        <is>
-          <t>Peek the next card</t>
-        </is>
-      </c>
-      <c r="O82" s="9" t="inlineStr">
-        <is>
-          <t>samePeek</t>
-        </is>
-      </c>
-      <c r="P82" s="8" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="15" t="inlineStr">
-        <is>
-          <t>Pile Size &amp; Score  (6)</t>
-        </is>
-      </c>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="8" t="n"/>
+      <c r="M84" s="8" t="inlineStr"/>
+      <c r="N84" s="11" t="inlineStr">
+        <is>
+          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score</t>
+        </is>
+      </c>
+      <c r="O84" s="9" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="P84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -14027,31 +14024,27 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>score shelter; curses its cover</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Curse Payoff</t>
-        </is>
-      </c>
+          <t>conditional: equalises the board</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Anchor</t>
+          <t>Donate</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>anchor</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>donate</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
@@ -14064,13 +14057,13 @@
       <c r="M85" s="8" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score.
-Any card played on top of this card is cursed</t>
+          <t>If another pile shows this suit → make all pile sizes equal.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>anchor</t>
+          <t>donate</t>
         </is>
       </c>
       <c r="P85" s="8" t="inlineStr"/>
@@ -14078,7 +14071,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
@@ -14088,46 +14081,55 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>conditional: equalises the board</t>
+          <t>♦ tops excluded</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr"/>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Donate</t>
+          <t>Diamond Anchor</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>donate</t>
-        </is>
-      </c>
-      <c r="G86" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>diamondAnchor</t>
+        </is>
+      </c>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H86" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr"/>
-      <c r="L86" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>diamondsPlayed</t>
+        </is>
+      </c>
+      <c r="L86" s="8" t="n">
+        <v>200</v>
+      </c>
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → make all pile sizes equal.
-If none does → this sticker becomes a curse</t>
+          <t>At deal end → exclude any pile in this column with a ♦ top card from the smallest-pile score</t>
         </is>
       </c>
       <c r="O86" s="9" t="inlineStr">
         <is>
-          <t>donate</t>
+          <t>diamondAnchor</t>
         </is>
       </c>
       <c r="P86" s="8" t="inlineStr"/>
@@ -14145,27 +14147,27 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>♦ tops excluded</t>
+          <t>equalises on a ♦</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr"/>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Diamond Anchor</t>
+          <t>Diamond Distribution</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>diamondAnchor</t>
-        </is>
-      </c>
-      <c r="G87" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>diamondDistribution</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H87" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
@@ -14179,21 +14181,21 @@
       </c>
       <c r="K87" s="8" t="inlineStr">
         <is>
-          <t>diamondsPlayed</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L87" s="8" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="M87" s="8" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>At deal end → exclude any pile in this column with a ♦ top card from the smallest-pile score</t>
+          <t>When a ♦ lands in this column → make all piles in this column equal size</t>
         </is>
       </c>
       <c r="O87" s="9" t="inlineStr">
         <is>
-          <t>diamondAnchor</t>
+          <t>diamondDistribution</t>
         </is>
       </c>
       <c r="P87" s="8" t="inlineStr"/>
@@ -14211,27 +14213,27 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>equalises on a ♦</t>
+          <t>an extra pile</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Diamond Distribution</t>
+          <t>Fourth Seat</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>diamondDistribution</t>
-        </is>
-      </c>
-      <c r="G88" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>fourthSeat</t>
+        </is>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H88" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
@@ -14240,26 +14242,26 @@
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K88" s="8" t="inlineStr">
         <is>
-          <t>removalsUsed</t>
+          <t>endlessStagesReached</t>
         </is>
       </c>
       <c r="L88" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M88" s="8" t="inlineStr"/>
       <c r="N88" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → make all piles in this column equal size</t>
+          <t>This column starts the deal with 1 extra pile (up to 4)</t>
         </is>
       </c>
       <c r="O88" s="9" t="inlineStr">
         <is>
-          <t>diamondDistribution</t>
+          <t>columnPiles</t>
         </is>
       </c>
       <c r="P88" s="8" t="inlineStr"/>
@@ -14267,7 +14269,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -14277,121 +14279,122 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>an extra pile</t>
+          <t>equalises the whole board</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Fourth Seat</t>
+          <t>Ballast</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>fourthSeat</t>
-        </is>
-      </c>
-      <c r="G89" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>evenOut</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J89" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K89" s="8" t="inlineStr">
-        <is>
-          <t>endlessStagesReached</t>
-        </is>
-      </c>
-      <c r="L89" s="8" t="n">
-        <v>1</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr"/>
+      <c r="K89" s="8" t="inlineStr"/>
+      <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="inlineStr"/>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>This column starts the deal with 1 extra pile (up to 4)</t>
+          <t>Make ALL piles on the board equal size</t>
         </is>
       </c>
       <c r="O89" s="9" t="inlineStr">
         <is>
-          <t>columnPiles</t>
+          <t>evenOut</t>
         </is>
       </c>
       <c r="P89" s="8" t="inlineStr"/>
     </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Bases</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Pile Size &amp; Score</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>equalises the whole board</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>Ballast</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>evenOut</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H90" s="8" t="n">
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>Safety &amp; Saves  (15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Safety &amp; Saves</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>conditional: carrier safe on a matched bet</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>suitImmunity</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr"/>
-      <c r="L90" s="8" t="n"/>
-      <c r="M90" s="8" t="inlineStr"/>
-      <c r="N90" s="11" t="inlineStr">
-        <is>
-          <t>Make ALL piles on the board equal size</t>
-        </is>
-      </c>
-      <c r="O90" s="9" t="inlineStr">
-        <is>
-          <t>evenOut</t>
-        </is>
-      </c>
-      <c r="P90" s="8" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="15" t="inlineStr">
-        <is>
-          <t>Safety &amp; Saves  (15)</t>
-        </is>
-      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>spadesPlayed</t>
+        </is>
+      </c>
+      <c r="L92" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="M92" s="8" t="inlineStr"/>
+      <c r="N92" s="11" t="inlineStr">
+        <is>
+          <t>If another pile shows this suit → this card is safe when it lands.
+Otherwise → this sticker becomes a curse</t>
+        </is>
+      </c>
+      <c r="O92" s="9" t="inlineStr">
+        <is>
+          <t>suitImmunity</t>
+        </is>
+      </c>
+      <c r="P92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -14406,56 +14409,46 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>conditional: carrier safe on a matched bet</t>
+          <t>conditional: rank-matched tie save</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Same-Safe</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>suitImmunity</t>
-        </is>
-      </c>
-      <c r="G93" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>tieSafe</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J93" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K93" s="8" t="inlineStr">
-        <is>
-          <t>spadesPlayed</t>
-        </is>
-      </c>
-      <c r="L93" s="8" t="n">
-        <v>150</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr"/>
+      <c r="K93" s="8" t="inlineStr"/>
+      <c r="L93" s="8" t="n"/>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → this card is safe when it lands.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this rank → Safe
+Otherwise → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O93" s="9" t="inlineStr">
         <is>
-          <t>suitImmunity</t>
+          <t>tieSafe</t>
         </is>
       </c>
       <c r="P93" s="8" t="inlineStr"/>
@@ -14463,7 +14456,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
@@ -14473,46 +14466,59 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>conditional: rank-matched tie save</t>
-        </is>
-      </c>
-      <c r="D94" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Same-Safe</t>
+          <t>Close Call</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>tieSafe</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>sameTolNear</t>
+        </is>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr"/>
-      <c r="L94" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>correctSames</t>
+        </is>
+      </c>
+      <c r="L94" s="8" t="n">
+        <v>52</v>
+      </c>
       <c r="M94" s="8" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this rank → Safe
-If no pile's top card matches this rank → Sticker becomes cursed</t>
+          <t>Same calls are safe on cards ±1 in value in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
         </is>
       </c>
       <c r="O94" s="9" t="inlineStr">
         <is>
-          <t>tieSafe</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P94" s="8" t="inlineStr"/>
@@ -14530,22 +14536,18 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>any tie, in column</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr"/>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Close Call</t>
+          <t>Column Tie-Safe</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>sameTolNear</t>
+          <t>columnTieSafe</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -14554,7 +14556,7 @@
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
@@ -14568,21 +14570,21 @@
       </c>
       <c r="K95" s="8" t="inlineStr">
         <is>
-          <t>correctSames</t>
+          <t>samesCalled</t>
         </is>
       </c>
       <c r="L95" s="8" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="M95" s="8" t="inlineStr"/>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>Same calls are safe on cards ±1 in value in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
+          <t>Any tie is safe in this column</t>
         </is>
       </c>
       <c r="O95" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>columnTieSafe</t>
         </is>
       </c>
       <c r="P95" s="8" t="inlineStr"/>
@@ -14600,18 +14602,18 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>any tie, in column</t>
+          <t>majority suit</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr"/>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Column Tie-Safe</t>
+          <t>Majority Rule</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>columnTieSafe</t>
+          <t>suitMajoritySafe</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
@@ -14620,7 +14622,7 @@
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
@@ -14629,29 +14631,33 @@
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K96" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>bossesBeaten</t>
         </is>
       </c>
       <c r="L96" s="8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M96" s="8" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>Any tie is safe in this column</t>
+          <t>If half or more of your full deck is {suit} → {suit} cards are safe when they land in this column</t>
         </is>
       </c>
       <c r="O96" s="9" t="inlineStr">
         <is>
-          <t>columnTieSafe</t>
-        </is>
-      </c>
-      <c r="P96" s="8" t="inlineStr"/>
+          <t>suitMajoritySafe</t>
+        </is>
+      </c>
+      <c r="P96" s="14" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -14666,55 +14672,45 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>majority suit</t>
+          <t>deck's commonest rank</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Majority Rule</t>
+          <t>Rank Shield</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>suitMajoritySafe</t>
-        </is>
-      </c>
-      <c r="G97" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>rankShield</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J97" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K97" s="8" t="inlineStr">
-        <is>
-          <t>bossesBeaten</t>
-        </is>
-      </c>
-      <c r="L97" s="8" t="n">
-        <v>6</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J97" s="8" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr"/>
+      <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="inlineStr"/>
       <c r="N97" s="11" t="inlineStr">
         <is>
-          <t>If half or more of your full deck is {suit} → {suit} cards are safe when they land in this column</t>
+          <t>Most common card in deck ({rank}) is always safe in this column</t>
         </is>
       </c>
       <c r="O97" s="9" t="inlineStr">
         <is>
-          <t>suitMajoritySafe</t>
+          <t>rankShield</t>
         </is>
       </c>
       <c r="P97" s="14" t="inlineStr">
@@ -14736,52 +14732,58 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>deck's commonest rank</t>
+          <t>revive a dead pile</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr"/>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Rank Shield</t>
+          <t>Revive</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>rankShield</t>
-        </is>
-      </c>
-      <c r="G98" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>revive</t>
+        </is>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H98" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="8" t="inlineStr"/>
-      <c r="L98" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J98" s="8" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="K98" s="8" t="inlineStr">
+        <is>
+          <t>dealsWonLegendary</t>
+        </is>
+      </c>
+      <c r="L98" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="M98" s="8" t="inlineStr"/>
       <c r="N98" s="11" t="inlineStr">
         <is>
-          <t>Most common card in deck ({rank}) is always safe in this column</t>
+          <t>When a pile in this column reaches 10 cards → revive one dead pile</t>
         </is>
       </c>
       <c r="O98" s="9" t="inlineStr">
         <is>
-          <t>rankShield</t>
-        </is>
-      </c>
-      <c r="P98" s="14" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+          <t>revive</t>
+        </is>
+      </c>
+      <c r="P98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -14796,18 +14798,22 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>revive a dead pile</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Revive</t>
+          <t>Royal Pair</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>sameTolRoyal</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -14816,7 +14822,7 @@
         </is>
       </c>
       <c r="H99" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
@@ -14825,26 +14831,26 @@
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K99" s="8" t="inlineStr">
         <is>
-          <t>dealsWonLegendary</t>
+          <t>samesCalled</t>
         </is>
       </c>
       <c r="L99" s="8" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="M99" s="8" t="inlineStr"/>
       <c r="N99" s="11" t="inlineStr">
         <is>
-          <t>When a pile in this column reaches 10 cards → revive one dead pile</t>
+          <t>A royal landing on a royal survives a Same call in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
         </is>
       </c>
       <c r="O99" s="9" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P99" s="8" t="inlineStr"/>
@@ -14862,31 +14868,27 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>royals, if no 2s in deck</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr"/>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Royal Pair</t>
+          <t>Royal Sanctuary</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>sameTolRoyal</t>
-        </is>
-      </c>
-      <c r="G100" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>royalSanctuary</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H100" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
@@ -14900,21 +14902,21 @@
       </c>
       <c r="K100" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L100" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M100" s="8" t="inlineStr"/>
       <c r="N100" s="11" t="inlineStr">
         <is>
-          <t>A royal landing on a royal survives a Same call in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
+          <t>If your full deck contains no 2s → royals (J/Q/K) are always safe in this column</t>
         </is>
       </c>
       <c r="O100" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>royalSafeNoTwos</t>
         </is>
       </c>
       <c r="P100" s="8" t="inlineStr"/>
@@ -14932,23 +14934,27 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>royals, if no 2s in deck</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Royal Sanctuary</t>
+          <t>Same Suit Safe</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>royalSanctuary</t>
-        </is>
-      </c>
-      <c r="G101" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>sameTolSuit</t>
+        </is>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H101" s="8" t="n">
@@ -14956,31 +14962,21 @@
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J101" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K101" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L101" s="8" t="n">
-        <v>30</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr"/>
+      <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="inlineStr"/>
       <c r="N101" s="11" t="inlineStr">
         <is>
-          <t>If your full deck contains no 2s → royals (J/Q/K) are always safe in this column</t>
+          <t>A card landing on its own suit is safe in this column</t>
         </is>
       </c>
       <c r="O101" s="9" t="inlineStr">
         <is>
-          <t>royalSafeNoTwos</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P101" s="8" t="inlineStr"/>
@@ -14998,27 +14994,23 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>deck's scarcest suit</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr"/>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Same Suit Safe</t>
+          <t>Scarce Suit</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>sameTolSuit</t>
-        </is>
-      </c>
-      <c r="G102" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>suitShield</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H102" s="8" t="n">
@@ -15035,12 +15027,12 @@
       <c r="M102" s="8" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr">
         <is>
-          <t>A card landing on its own suit is safe in this column</t>
+          <t>The suit your deck holds the fewest of is safe when it lands in this column</t>
         </is>
       </c>
       <c r="O102" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>suitShieldDaily</t>
         </is>
       </c>
       <c r="P102" s="8" t="inlineStr"/>
@@ -15058,23 +15050,23 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>deck's scarcest suit</t>
+          <t>chance to save a dying pile</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr"/>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Scarce Suit</t>
+          <t>Second Wind</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>suitShield</t>
-        </is>
-      </c>
-      <c r="G103" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>secondWind</t>
+        </is>
+      </c>
+      <c r="G103" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H103" s="8" t="n">
@@ -15091,12 +15083,12 @@
       <c r="M103" s="8" t="inlineStr"/>
       <c r="N103" s="11" t="inlineStr">
         <is>
-          <t>The suit your deck holds the fewest of is safe when it lands in this column</t>
+          <t>Each pile that dies in this column has a 25% chance to be saved — the top card stays and the buried cards shuffle back into the deck</t>
         </is>
       </c>
       <c r="O103" s="9" t="inlineStr">
         <is>
-          <t>suitShieldDaily</t>
+          <t>secondWind</t>
         </is>
       </c>
       <c r="P103" s="8" t="inlineStr"/>
@@ -15114,18 +15106,18 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>chance to save a dying pile</t>
+          <t>aces high or low</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr"/>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Second Wind</t>
+          <t>Wild Aces</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>secondWind</t>
+          <t>wildAces</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
@@ -15134,25 +15126,35 @@
         </is>
       </c>
       <c r="H104" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J104" s="8" t="inlineStr"/>
-      <c r="K104" s="8" t="inlineStr"/>
-      <c r="L104" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J104" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K104" s="8" t="inlineStr">
+        <is>
+          <t>jokersPlayed</t>
+        </is>
+      </c>
+      <c r="L104" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="M104" s="8" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr">
         <is>
-          <t>Each pile that dies in this column has a 25% chance to be saved — the top card stays and the buried cards shuffle back into the deck</t>
+          <t>Aces count as high or low in this column</t>
         </is>
       </c>
       <c r="O104" s="9" t="inlineStr">
         <is>
-          <t>secondWind</t>
+          <t>wildAces</t>
         </is>
       </c>
       <c r="P104" s="8" t="inlineStr"/>
@@ -15160,7 +15162,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -15170,55 +15172,45 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>aces high or low</t>
+          <t>revive a dead pile</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr"/>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Wild Aces</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>wildAces</t>
-        </is>
-      </c>
-      <c r="G105" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>revive</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J105" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K105" s="8" t="inlineStr">
-        <is>
-          <t>jokersPlayed</t>
-        </is>
-      </c>
-      <c r="L105" s="8" t="n">
-        <v>8</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr"/>
+      <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="inlineStr"/>
       <c r="N105" s="11" t="inlineStr">
         <is>
-          <t>Aces count as high or low in this column</t>
+          <t>Revive a random dead pile in this column. Buried cards return to the deck</t>
         </is>
       </c>
       <c r="O105" s="9" t="inlineStr">
         <is>
-          <t>wildAces</t>
+          <t>reviveBase</t>
         </is>
       </c>
       <c r="P105" s="8" t="inlineStr"/>
@@ -15226,7 +15218,7 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -15236,121 +15228,132 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>revive a dead pile</t>
+          <t>revive on a Same</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr"/>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Rekindle</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>revive</t>
-        </is>
-      </c>
-      <c r="G106" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>linkRevive</t>
+        </is>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H106" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J106" s="8" t="inlineStr"/>
-      <c r="K106" s="8" t="inlineStr"/>
-      <c r="L106" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J106" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K106" s="8" t="inlineStr">
+        <is>
+          <t>correctSames</t>
+        </is>
+      </c>
+      <c r="L106" s="8" t="n">
+        <v>24</v>
+      </c>
       <c r="M106" s="8" t="inlineStr"/>
       <c r="N106" s="11" t="inlineStr">
         <is>
-          <t>Revive a random dead pile in this column. Buried cards return to the deck</t>
+          <t>Revive a dead pile</t>
         </is>
       </c>
       <c r="O106" s="9" t="inlineStr">
         <is>
-          <t>reviveBase</t>
+          <t>linkRevive</t>
         </is>
       </c>
       <c r="P106" s="8" t="inlineStr"/>
     </row>
-    <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>Same-Powers</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>Safety &amp; Saves</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>revive on a Same</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr"/>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>Rekindle</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>linkRevive</t>
-        </is>
-      </c>
-      <c r="G107" s="13" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power  (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>conditional: rank-matched charge</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr"/>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>Recharge Shield</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>rechargeSameShield</t>
+        </is>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="H107" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
+      <c r="H109" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J107" s="8" t="inlineStr">
+      <c r="J109" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K107" s="8" t="inlineStr">
+      <c r="K109" s="8" t="inlineStr">
         <is>
           <t>correctSames</t>
         </is>
       </c>
-      <c r="L107" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M107" s="8" t="inlineStr"/>
-      <c r="N107" s="11" t="inlineStr">
-        <is>
-          <t>Revive a dead pile</t>
-        </is>
-      </c>
-      <c r="O107" s="9" t="inlineStr">
-        <is>
-          <t>linkRevive</t>
-        </is>
-      </c>
-      <c r="P107" s="8" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power  (4)</t>
-        </is>
-      </c>
+      <c r="L109" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M109" s="8" t="inlineStr"/>
+      <c r="N109" s="11" t="inlineStr">
+        <is>
+          <t>If another pile shows this rank → Charge Same Shield
+Otherwise → Sticker becomes cursed</t>
+        </is>
+      </c>
+      <c r="O109" s="9" t="inlineStr">
+        <is>
+          <t>rechargeSameShield</t>
+        </is>
+      </c>
+      <c r="P109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -15365,18 +15368,18 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>conditional: rank-matched charge</t>
+          <t>conditional: rank-matched power fire</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr"/>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Recharge Shield</t>
+          <t>Tap Power</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>rechargeSameShield</t>
+          <t>activateSamePower</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
@@ -15385,7 +15388,7 @@
         </is>
       </c>
       <c r="H110" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
@@ -15403,18 +15406,18 @@
         </is>
       </c>
       <c r="L110" s="8" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="M110" s="8" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this rank → Charge Same Shield
-If no pile's top card matches this rank → Sticker becomes cursed</t>
+          <t>If another pile shows this rank → Fire Same Power
+Otherwise → Sticker becomes cursed</t>
         </is>
       </c>
       <c r="O110" s="9" t="inlineStr">
         <is>
-          <t>rechargeSameShield</t>
+          <t>activateSamePower</t>
         </is>
       </c>
       <c r="P110" s="8" t="inlineStr"/>
@@ -15422,7 +15425,7 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -15438,12 +15441,12 @@
       <c r="D111" s="8" t="inlineStr"/>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Tap Power</t>
+          <t>Power Surge</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>activateSamePower</t>
+          <t>activateSame</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -15452,7 +15455,7 @@
         </is>
       </c>
       <c r="H111" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
@@ -15470,13 +15473,12 @@
         </is>
       </c>
       <c r="L111" s="8" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M111" s="8" t="inlineStr"/>
       <c r="N111" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this rank → Fire Same Power
-If no pile's top card matches this rank → Sticker becomes cursed</t>
+          <t>Activate your Same-Power</t>
         </is>
       </c>
       <c r="O111" s="9" t="inlineStr">
@@ -15499,18 +15501,18 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>conditional: rank-matched power fire</t>
+          <t>conditional: rank-matched charge</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr"/>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Power Surge</t>
+          <t>Recharge Cell</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>activateSame</t>
+          <t>rechargeSame</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
@@ -15528,7 +15530,7 @@
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K112" s="8" t="inlineStr">
@@ -15537,98 +15539,99 @@
         </is>
       </c>
       <c r="L112" s="8" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="M112" s="8" t="inlineStr"/>
       <c r="N112" s="11" t="inlineStr">
         <is>
-          <t>Activate your Same-Power</t>
+          <t>Charge the Same Shield</t>
         </is>
       </c>
       <c r="O112" s="9" t="inlineStr">
         <is>
-          <t>activateSamePower</t>
+          <t>rechargeSameShield</t>
         </is>
       </c>
       <c r="P112" s="8" t="inlineStr"/>
     </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>Bases</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>conditional: rank-matched charge</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr"/>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>Recharge Cell</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>rechargeSame</t>
-        </is>
-      </c>
-      <c r="G113" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I113" s="8" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>Shuffle  (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>Shuffle</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>conditional: offered, matching piles</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr"/>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>diamondSnob</t>
+        </is>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J113" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K113" s="8" t="inlineStr">
-        <is>
-          <t>correctSames</t>
-        </is>
-      </c>
-      <c r="L113" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="M113" s="8" t="inlineStr"/>
-      <c r="N113" s="11" t="inlineStr">
-        <is>
-          <t>Charge the Same Shield</t>
-        </is>
-      </c>
-      <c r="O113" s="9" t="inlineStr">
-        <is>
-          <t>rechargeSameShield</t>
-        </is>
-      </c>
-      <c r="P113" s="8" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>Shuffle  (4)</t>
-        </is>
-      </c>
+      <c r="J115" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K115" s="8" t="inlineStr">
+        <is>
+          <t>removalsUsed</t>
+        </is>
+      </c>
+      <c r="L115" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M115" s="8" t="inlineStr"/>
+      <c r="N115" s="11" t="inlineStr">
+        <is>
+          <t>If another pile shows this suit → optionally shuffle those piles.
+Otherwise → this sticker becomes a curse</t>
+        </is>
+      </c>
+      <c r="O115" s="9" t="inlineStr">
+        <is>
+          <t>diamondSnob</t>
+        </is>
+      </c>
+      <c r="P115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -15638,18 +15641,18 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>conditional: offered, matching piles</t>
+          <t>column, on a ♦</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Shuffler</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>diamondSnob</t>
+          <t>royalCourt</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -15658,36 +15661,25 @@
         </is>
       </c>
       <c r="H116" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J116" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K116" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L116" s="8" t="n">
-        <v>18</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J116" s="8" t="inlineStr"/>
+      <c r="K116" s="8" t="inlineStr"/>
+      <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="inlineStr"/>
       <c r="N116" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → optionally shuffle those piles.
-If none does → this sticker becomes a curse</t>
+          <t>When a ♦ lands in this column → optionally shuffle the other piles in this column</t>
         </is>
       </c>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>diamondSnob</t>
+          <t>shuffler</t>
         </is>
       </c>
       <c r="P116" s="8" t="inlineStr"/>
@@ -15695,7 +15687,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
@@ -15705,27 +15697,27 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>column, on a ♦</t>
+          <t>this column</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr"/>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Shuffler</t>
+          <t>Upheaval</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>royalCourt</t>
-        </is>
-      </c>
-      <c r="G117" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>shuffleColumn</t>
+        </is>
+      </c>
+      <c r="G117" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
@@ -15738,12 +15730,12 @@
       <c r="M117" s="8" t="inlineStr"/>
       <c r="N117" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → optionally shuffle the other piles in this column</t>
+          <t>Shuffle every pile in this column</t>
         </is>
       </c>
       <c r="O117" s="9" t="inlineStr">
         <is>
-          <t>shuffler</t>
+          <t>shuffleColumn</t>
         </is>
       </c>
       <c r="P117" s="8" t="inlineStr"/>
@@ -15751,7 +15743,7 @@
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
@@ -15761,27 +15753,27 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>this column</t>
+          <t>every alive pile</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr"/>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Upheaval</t>
+          <t>Link Shuffler</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>shuffleColumn</t>
-        </is>
-      </c>
-      <c r="G118" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>linkShuffle</t>
+        </is>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H118" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
@@ -15794,83 +15786,93 @@
       <c r="M118" s="8" t="inlineStr"/>
       <c r="N118" s="11" t="inlineStr">
         <is>
-          <t>Shuffle every pile in this column</t>
+          <t>Shuffle every alive pile</t>
         </is>
       </c>
       <c r="O118" s="9" t="inlineStr">
         <is>
-          <t>shuffleColumn</t>
+          <t>linkShuffle</t>
         </is>
       </c>
       <c r="P118" s="8" t="inlineStr"/>
     </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>Same-Powers</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>Shuffle</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>every alive pile</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr"/>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t>Link Shuffler</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr">
-        <is>
-          <t>linkShuffle</t>
-        </is>
-      </c>
-      <c r="G119" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I119" s="8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J119" s="8" t="inlineStr"/>
-      <c r="K119" s="8" t="inlineStr"/>
-      <c r="L119" s="8" t="n"/>
-      <c r="M119" s="8" t="inlineStr"/>
-      <c r="N119" s="11" t="inlineStr">
-        <is>
-          <t>Shuffle every alive pile</t>
-        </is>
-      </c>
-      <c r="O119" s="9" t="inlineStr">
-        <is>
-          <t>linkShuffle</t>
-        </is>
-      </c>
-      <c r="P119" s="8" t="inlineStr"/>
+    <row r="120">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>Sticker Grant  (3)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="15" t="inlineStr">
-        <is>
-          <t>Sticker Grant  (3)</t>
-        </is>
-      </c>
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>Pillars</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>Sticker Grant</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>chance, on landing</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr"/>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>Flypaper</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>flypaper</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J121" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K121" s="8" t="inlineStr">
+        <is>
+          <t>stickersApplied</t>
+        </is>
+      </c>
+      <c r="L121" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="M121" s="8" t="inlineStr"/>
+      <c r="N121" s="11" t="inlineStr">
+        <is>
+          <t>When a card lands correctly in this column → 5% chance it gains a random sticker</t>
+        </is>
+      </c>
+      <c r="O121" s="9" t="inlineStr">
+        <is>
+          <t>flypaper</t>
+        </is>
+      </c>
+      <c r="P121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
@@ -15880,18 +15882,18 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>chance, on landing</t>
+          <t>one column top</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr"/>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Flypaper</t>
+          <t>Wild Sticker</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>flypaper</t>
+          <t>randomSticker</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -15900,7 +15902,7 @@
         </is>
       </c>
       <c r="H122" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
@@ -15918,17 +15920,17 @@
         </is>
       </c>
       <c r="L122" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M122" s="8" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr">
         <is>
-          <t>When a card lands correctly in this column → 5% chance it gains a random sticker</t>
+          <t>Apply a random sticker to a random top card in this column</t>
         </is>
       </c>
       <c r="O122" s="9" t="inlineStr">
         <is>
-          <t>flypaper</t>
+          <t>randomSticker</t>
         </is>
       </c>
       <c r="P122" s="8" t="inlineStr"/>
@@ -15936,7 +15938,7 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
@@ -15946,27 +15948,27 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>one column top</t>
+          <t>every top in the column</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Wild Sticker</t>
+          <t>Sticker Spray</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>randomSticker</t>
-        </is>
-      </c>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>linkSticker</t>
+        </is>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H123" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
@@ -15984,93 +15986,93 @@
         </is>
       </c>
       <c r="L123" s="8" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="M123" s="8" t="inlineStr"/>
       <c r="N123" s="11" t="inlineStr">
         <is>
-          <t>Apply a random sticker to a random top card in this column</t>
+          <t>Apply a random sticker to every top card in this column</t>
         </is>
       </c>
       <c r="O123" s="9" t="inlineStr">
         <is>
-          <t>randomSticker</t>
+          <t>linkSticker</t>
         </is>
       </c>
       <c r="P123" s="8" t="inlineStr"/>
     </row>
-    <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>Same-Powers</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>Sticker Grant</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
-        <is>
-          <t>every top in the column</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="inlineStr"/>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t>Sticker Spray</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>linkSticker</t>
-        </is>
-      </c>
-      <c r="G124" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H124" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I124" s="8" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>Store Economy  (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>Pillars</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Store Economy</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>Purge ladder climbs slower</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr"/>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>Bulk Rate</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>bulkRate</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H126" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J124" s="8" t="inlineStr">
+      <c r="J126" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K124" s="8" t="inlineStr">
-        <is>
-          <t>stickersApplied</t>
-        </is>
-      </c>
-      <c r="L124" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M124" s="8" t="inlineStr"/>
-      <c r="N124" s="11" t="inlineStr">
-        <is>
-          <t>Apply a random sticker to every top card in this column</t>
-        </is>
-      </c>
-      <c r="O124" s="9" t="inlineStr">
-        <is>
-          <t>linkSticker</t>
-        </is>
-      </c>
-      <c r="P124" s="8" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="15" t="inlineStr">
-        <is>
-          <t>Store Economy  (6)</t>
-        </is>
-      </c>
+      <c r="K126" s="8" t="inlineStr">
+        <is>
+          <t>removalsUsed</t>
+        </is>
+      </c>
+      <c r="L126" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M126" s="8" t="inlineStr"/>
+      <c r="N126" s="11" t="inlineStr">
+        <is>
+          <t>The store's Purge price climbs by 1 instead of 2. No effect during deal</t>
+        </is>
+      </c>
+      <c r="O126" s="9" t="inlineStr">
+        <is>
+          <t>purgeStepDiscount</t>
+        </is>
+      </c>
+      <c r="P126" s="8" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -16085,55 +16087,45 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Purge ladder climbs slower</t>
+          <t>one-time Purge halving on purchase</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr"/>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Bulk Rate</t>
+          <t>Flat Purge</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>bulkRate</t>
-        </is>
-      </c>
-      <c r="G127" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>purgeFlatFive</t>
+        </is>
+      </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H127" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J127" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K127" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L127" s="8" t="n">
-        <v>16</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J127" s="8" t="inlineStr"/>
+      <c r="K127" s="8" t="inlineStr"/>
+      <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="inlineStr"/>
       <c r="N127" s="11" t="inlineStr">
         <is>
-          <t>The store's Purge price climbs by 1 instead of 2. No effect during deal</t>
+          <t>On purchase → the store's Purge price is halved (minimum 5). No effect during deal</t>
         </is>
       </c>
       <c r="O127" s="9" t="inlineStr">
         <is>
-          <t>purgeStepDiscount</t>
+          <t>purgeHalve</t>
         </is>
       </c>
       <c r="P127" s="8" t="inlineStr"/>
@@ -16151,18 +16143,18 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>one-time Purge halving on purchase</t>
+          <t>one free shelf item</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr"/>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Flat Purge</t>
+          <t>Freebie</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>purgeFlatFive</t>
+          <t>freebie</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
@@ -16171,25 +16163,35 @@
         </is>
       </c>
       <c r="H128" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J128" s="8" t="inlineStr"/>
-      <c r="K128" s="8" t="inlineStr"/>
-      <c r="L128" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J128" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K128" s="8" t="inlineStr">
+        <is>
+          <t>pinkyTipsSeen</t>
+        </is>
+      </c>
+      <c r="L128" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="M128" s="8" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr">
         <is>
-          <t>On purchase → the store's Purge price is halved (minimum 5). No effect during deal</t>
+          <t>One random item in every store costs 0 coins. No effect during deal</t>
         </is>
       </c>
       <c r="O128" s="9" t="inlineStr">
         <is>
-          <t>purgeHalve</t>
+          <t>freebie</t>
         </is>
       </c>
       <c r="P128" s="8" t="inlineStr"/>
@@ -16207,18 +16209,18 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>one free shelf item</t>
+          <t>first restock + reshuffle free</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr"/>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Freebie</t>
+          <t>On the House</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>freebie</t>
+          <t>firstFree</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
@@ -16227,35 +16229,25 @@
         </is>
       </c>
       <c r="H129" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J129" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K129" s="8" t="inlineStr">
-        <is>
-          <t>pinkyTipsSeen</t>
-        </is>
-      </c>
-      <c r="L129" s="8" t="n">
-        <v>2</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J129" s="8" t="inlineStr"/>
+      <c r="K129" s="8" t="inlineStr"/>
+      <c r="L129" s="8" t="n"/>
       <c r="M129" s="8" t="inlineStr"/>
       <c r="N129" s="11" t="inlineStr">
         <is>
-          <t>One random item in every store costs 0 coins. No effect during deal</t>
+          <t>The first restock in each store and the first reshuffle of each deal are free</t>
         </is>
       </c>
       <c r="O129" s="9" t="inlineStr">
         <is>
-          <t>freebie</t>
+          <t>firstFree</t>
         </is>
       </c>
       <c r="P129" s="8" t="inlineStr"/>
@@ -16273,18 +16265,18 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>first restock + reshuffle free</t>
+          <t>rares twice as often</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr"/>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>On the House</t>
+          <t>Rare Hunter</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>firstFree</t>
+          <t>rareHunter</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
@@ -16293,25 +16285,35 @@
         </is>
       </c>
       <c r="H130" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J130" s="8" t="inlineStr"/>
-      <c r="K130" s="8" t="inlineStr"/>
-      <c r="L130" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J130" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K130" s="8" t="inlineStr">
+        <is>
+          <t>pillarsPlaced</t>
+        </is>
+      </c>
+      <c r="L130" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="M130" s="8" t="inlineStr"/>
       <c r="N130" s="11" t="inlineStr">
         <is>
-          <t>The first restock in each store and the first reshuffle of each deal are free</t>
+          <t>Rare items appear in the store twice as often. No effect during deal</t>
         </is>
       </c>
       <c r="O130" s="9" t="inlineStr">
         <is>
-          <t>firstFree</t>
+          <t>rareHunter</t>
         </is>
       </c>
       <c r="P130" s="8" t="inlineStr"/>
@@ -16319,7 +16321,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
@@ -16329,27 +16331,27 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>rares twice as often</t>
+          <t>cuts the Purge price</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr"/>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Rare Hunter</t>
+          <t>Purge Coupon</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
-          <t>rareHunter</t>
-        </is>
-      </c>
-      <c r="G131" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>purgeDiscount</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H131" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
@@ -16363,102 +16365,93 @@
       </c>
       <c r="K131" s="8" t="inlineStr">
         <is>
-          <t>pillarsPlaced</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L131" s="8" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="M131" s="8" t="inlineStr"/>
       <c r="N131" s="11" t="inlineStr">
         <is>
-          <t>Rare items appear in the store twice as often. No effect during deal</t>
+          <t>Reduce the Store's Purge cost by 1 for each ♦-topped pile in this column. Minimum 5</t>
         </is>
       </c>
       <c r="O131" s="9" t="inlineStr">
         <is>
-          <t>rareHunter</t>
+          <t>purgeDiscount</t>
         </is>
       </c>
       <c r="P131" s="8" t="inlineStr"/>
     </row>
-    <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>Bases</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>Store Economy</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
-        <is>
-          <t>cuts the Purge price</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr"/>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t>Purge Coupon</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="inlineStr">
-        <is>
-          <t>purgeDiscount</t>
-        </is>
-      </c>
-      <c r="G132" s="12" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>Tell  (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Tell</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>conditional: this pile, next draw</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr"/>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>Tell</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>tell</t>
+        </is>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="H132" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I132" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J132" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K132" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L132" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M132" s="8" t="inlineStr"/>
-      <c r="N132" s="11" t="inlineStr">
-        <is>
-          <t>Reduce the Store's Purge cost by 1 for each ♦-topped pile in this column. Minimum 5</t>
-        </is>
-      </c>
-      <c r="O132" s="9" t="inlineStr">
-        <is>
-          <t>purgeDiscount</t>
-        </is>
-      </c>
-      <c r="P132" s="8" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="inlineStr">
-        <is>
-          <t>Tell  (5)</t>
-        </is>
-      </c>
+      <c r="H134" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J134" s="8" t="inlineStr"/>
+      <c r="K134" s="8" t="inlineStr"/>
+      <c r="L134" s="8" t="n"/>
+      <c r="M134" s="8" t="inlineStr"/>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>If another pile shows this suit → this card shows a tell (higher, lower, or same) for the next draw.
+Otherwise → this sticker becomes a curse</t>
+        </is>
+      </c>
+      <c r="O134" s="9" t="inlineStr">
+        <is>
+          <t>tell</t>
+        </is>
+      </c>
+      <c r="P134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
@@ -16468,27 +16461,31 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>conditional: this pile, next draw</t>
-        </is>
-      </c>
-      <c r="D135" s="8" t="inlineStr"/>
+          <t>while broke, per ♥ landing</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>Pauper</t>
+        </is>
+      </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Tell</t>
+          <t>Pauper's Heart</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>tell</t>
-        </is>
-      </c>
-      <c r="G135" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>pauperHeart</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H135" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
@@ -16501,13 +16498,12 @@
       <c r="M135" s="8" t="inlineStr"/>
       <c r="N135" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → this card shows a tell (higher, lower, or same) for the next draw.
-If none does → this sticker becomes a curse</t>
+          <t>While your purse holds under 10 coins → when a ♥ lands in this column, that pile gets a tell</t>
         </is>
       </c>
       <c r="O135" s="9" t="inlineStr">
         <is>
-          <t>tell</t>
+          <t>pauperHeartTell</t>
         </is>
       </c>
       <c r="P135" s="8" t="inlineStr"/>
@@ -17721,22 +17717,22 @@
     <mergeCell ref="A14:P14"/>
     <mergeCell ref="A141:P141"/>
     <mergeCell ref="A150:P150"/>
-    <mergeCell ref="A126:P126"/>
-    <mergeCell ref="A109:P109"/>
+    <mergeCell ref="A91:P91"/>
     <mergeCell ref="A62:P62"/>
-    <mergeCell ref="A134:P134"/>
+    <mergeCell ref="A125:P125"/>
     <mergeCell ref="A68:P68"/>
-    <mergeCell ref="A121:P121"/>
-    <mergeCell ref="A115:P115"/>
-    <mergeCell ref="A92:P92"/>
+    <mergeCell ref="A114:P114"/>
+    <mergeCell ref="A83:P83"/>
     <mergeCell ref="A30:P30"/>
     <mergeCell ref="A146:P146"/>
     <mergeCell ref="A168:P168"/>
     <mergeCell ref="A153:P153"/>
     <mergeCell ref="A164:P164"/>
     <mergeCell ref="A46:P46"/>
-    <mergeCell ref="A84:P84"/>
+    <mergeCell ref="A133:P133"/>
+    <mergeCell ref="A108:P108"/>
     <mergeCell ref="A56:P56"/>
+    <mergeCell ref="A120:P120"/>
     <mergeCell ref="A50:P50"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -19224,8 +19220,8 @@
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>If another pile's top card matches this card's suit → +1 pile size to every pile whose top matches, including this one.
-If none does → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → +1 pile size to every pile whose top matches, including this one.
+Otherwise → this sticker becomes a curse</t>
         </is>
       </c>
       <c r="O23" s="9" t="inlineStr">

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v6.96)</t>
+          <t>NINELIVES — item pool (v6.97)</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>+1 card rank (stops at Ace)</t>
+          <t>+1 rank (stops at Ace)</t>
         </is>
       </c>
       <c r="O2" s="9" t="inlineStr">
@@ -1869,14 +1869,10 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>score shelter; curses its cover</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Curse Payoff</t>
-        </is>
-      </c>
+          <t>score shelter</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Anchor</t>
@@ -1906,7 +1902,7 @@
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score</t>
+          <t>At deal end if top card → exclude from smallest-pile size</t>
         </is>
       </c>
       <c r="O3" s="9" t="inlineStr">
@@ -1962,7 +1958,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="11" t="inlineStr">
         <is>
-          <t>Change suit to ♠</t>
+          <t>Change to ♠</t>
         </is>
       </c>
       <c r="O4" s="9" t="inlineStr">
@@ -2018,7 +2014,7 @@
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Change suit to ♣</t>
+          <t>Change to ♣</t>
         </is>
       </c>
       <c r="O5" s="9" t="inlineStr">
@@ -2074,7 +2070,7 @@
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>Change suit to ♥</t>
+          <t>Change to ♥</t>
         </is>
       </c>
       <c r="O6" s="9" t="inlineStr">
@@ -2130,7 +2126,7 @@
       <c r="M7" s="8" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>Change suit to ♦</t>
+          <t>Change to ♦</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
@@ -2196,7 +2192,7 @@
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>Change to random rank</t>
+          <t>Randomize rank</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -2252,7 +2248,7 @@
       <c r="M9" s="8" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>Change to random suit</t>
+          <t>Randomize suit</t>
         </is>
       </c>
       <c r="O9" s="9" t="inlineStr">
@@ -2308,8 +2304,8 @@
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this rank → Safe
-Otherwise → Sticker becomes cursed</t>
+          <t>If another pile shows this rank → safe
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
@@ -2365,7 +2361,7 @@
       <c r="M11" s="8" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>-1 card rank (stops at 2)</t>
+          <t>-1 rank (stops at 2)</t>
         </is>
       </c>
       <c r="O11" s="9" t="inlineStr">
@@ -2431,7 +2427,7 @@
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>+2 card rank (stops at Ace)</t>
+          <t>+2 rank (stops at Ace)</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
@@ -2497,8 +2493,8 @@
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>If this column has no Base → peek at the next card.
-If it has one → this sticker becomes a curse</t>
+          <t>If in column with no Base → peek next card
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O13" s="9" t="inlineStr">
@@ -2554,8 +2550,8 @@
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → +1 coin per pile whose top card matches.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → +1 coin per pile with matching suit
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
@@ -2611,8 +2607,8 @@
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → make all pile sizes equal.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → make all pile sizes equal size
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O15" s="9" t="inlineStr">
@@ -2678,8 +2674,8 @@
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → this card is safe when it lands.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → safe
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
@@ -2702,14 +2698,10 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>deal-end payout; curses its cover</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Curse Payoff</t>
-        </is>
-      </c>
+          <t>deal-end payout</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Payout</t>
@@ -2749,7 +2741,7 @@
       <c r="M17" s="8" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → earn coins equal to pile size</t>
+          <t>At deal end if top card → earn coins equal to pile size</t>
         </is>
       </c>
       <c r="O17" s="9" t="inlineStr">
@@ -2815,8 +2807,8 @@
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>If this column has no Pillar → peek at the next card.
-If it has one → this sticker becomes a curse</t>
+          <t>If in column with no Pillar → peek next card
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O18" s="9" t="inlineStr">
@@ -2872,8 +2864,8 @@
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → bury 1 card under this pile.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → bury 1 card under this pile
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
@@ -2939,8 +2931,8 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → optionally shuffle those piles.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → optionally shuffle those piles
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
@@ -2996,8 +2988,8 @@
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → this card shows a tell (higher, lower, or same) for the next draw.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → this card shows a tell (higher/lower/same)
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
@@ -3020,7 +3012,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>if a rank twin is up</t>
+          <t>conditional: rank-twin bet</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr"/>
@@ -3067,7 +3059,8 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Peek at the next card if another pile shows this rank</t>
+          <t>If another pile shows this rank → peek next card
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O22" s="9" t="inlineStr">
@@ -3133,7 +3126,7 @@
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>-2 card rank (stops at 2)</t>
+          <t>-2 rank (stops at 2)</t>
         </is>
       </c>
       <c r="O23" s="9" t="inlineStr">
@@ -3199,8 +3192,8 @@
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this rank → Charge Same Shield
-Otherwise → Sticker becomes cursed</t>
+          <t>If another pile shows this rank → charge Same Shield
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O24" s="9" t="inlineStr">
@@ -3266,8 +3259,8 @@
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this rank → Fire Same Power
-Otherwise → Sticker becomes cursed</t>
+          <t>If another pile shows this rank → fire Same Power
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O25" s="9" t="inlineStr">
@@ -3285,7 +3278,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Peek</t>
+          <t>Tell</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -3323,12 +3316,12 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>When an 8 lands in this column → peek at the next card</t>
+          <t>When an 8 lands in this column → tell on that card</t>
         </is>
       </c>
       <c r="O26" s="9" t="inlineStr">
         <is>
-          <t>eightPeek</t>
+          <t>eightTell</t>
         </is>
       </c>
       <c r="P26" s="8" t="inlineStr"/>
@@ -3389,7 +3382,7 @@
       <c r="M27" s="8" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +2 coins per pile in this column with a ♥ top card</t>
+          <t>At deal end → +2 coins per pile in this column with a ♥</t>
         </is>
       </c>
       <c r="O27" s="9" t="inlineStr">
@@ -3459,7 +3452,7 @@
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +1 coin per 5 cards in your deck, if no other pillar is equipped</t>
+          <t>At deal end if only equipped pillar → +1 coin per 5 cards in your full deck</t>
         </is>
       </c>
       <c r="O28" s="9" t="inlineStr">
@@ -3519,7 +3512,7 @@
       <c r="M29" s="8" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>While your purse holds under 10 coins → when a ♣ lands in this column, bury 1 card under that pile</t>
+          <t>If purse &lt;10 coins → when a ♣ lands in this column bury 1</t>
         </is>
       </c>
       <c r="O29" s="9" t="inlineStr">
@@ -3579,7 +3572,7 @@
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>While your purse holds under 10 coins → when a ♥ lands in this column, that pile gets a tell</t>
+          <t>If purse &lt;10 coins → when a ♥ lands in this column, that card gets a tell</t>
         </is>
       </c>
       <c r="O30" s="9" t="inlineStr">
@@ -3639,7 +3632,7 @@
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>While your purse holds under 10 coins → when a ♠ lands in this column, the next card shows a tell (higher/lower/same)</t>
+          <t>If purse &lt;10 coins → when a ♠ lands in this column, the next card shows a tell (higher/lower/same)</t>
         </is>
       </c>
       <c r="O31" s="9" t="inlineStr">
@@ -3705,7 +3698,7 @@
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>30% chance to turn away a Just a Two mystery. 100% chance if there are no 2s in your deck. No effect during deal</t>
+          <t>30% chance to turn away a Just a Two mystery — 100% if your full deck has no 2s (no effect during deal)</t>
         </is>
       </c>
       <c r="O32" s="9" t="inlineStr">
@@ -3771,7 +3764,7 @@
       <c r="M33" s="8" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>The store's Purge price climbs by 1 instead of 2. No effect during deal</t>
+          <t>The store's Purge price climbs by 1 instead of 2 (no effect during deal)</t>
         </is>
       </c>
       <c r="O33" s="9" t="inlineStr">
@@ -3837,7 +3830,7 @@
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → make all piles in this column equal size</t>
+          <t>When a ♦ lands in this column → make this column's piles equal size</t>
         </is>
       </c>
       <c r="O34" s="9" t="inlineStr">
@@ -4029,7 +4022,7 @@
       <c r="M37" s="8" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +4 coins if every pile in this column survived</t>
+          <t>At deal end if every pile in this column survived → +4 coins</t>
         </is>
       </c>
       <c r="O37" s="9" t="inlineStr">
@@ -4151,7 +4144,7 @@
       <c r="M39" s="8" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +3 coins if no pile in this column survived</t>
+          <t>At deal end if no pile in this column survived → +3 coins</t>
         </is>
       </c>
       <c r="O39" s="9" t="inlineStr">
@@ -4207,7 +4200,7 @@
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>When a royal ♠ (J/Q/K) lands in this column → peek at the next card</t>
+          <t>When a royal ♠ (J/Q/K) lands in this column → peek next card</t>
         </is>
       </c>
       <c r="O40" s="9" t="inlineStr">
@@ -4273,7 +4266,7 @@
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>+30% chance to find a Beheaded Queen at a mystery stop. 100% chance if Queens are the most common rank in your deck (ties don't count). No effect during deal</t>
+          <t>+30% chance to find a Beheaded Queen at a mystery stop — 100% if Queens are the most common rank in your full deck, ties don't count (no effect during deal)</t>
         </is>
       </c>
       <c r="O41" s="9" t="inlineStr">
@@ -4329,7 +4322,7 @@
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>Most common card in deck ({rank}) is always safe in this column</t>
+          <t>The most common rank in your full deck ({rank}) is always safe in this column</t>
         </is>
       </c>
       <c r="O42" s="9" t="inlineStr">
@@ -4399,7 +4392,7 @@
       <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>If your full deck contains no 2s → royals (J/Q/K) are always safe in this column</t>
+          <t>If your full deck has no 2s → royals (J/Q/K) are always safe in this column</t>
         </is>
       </c>
       <c r="O43" s="9" t="inlineStr">
@@ -4455,7 +4448,7 @@
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="11" t="inlineStr">
         <is>
-          <t>The suit your deck holds the fewest of is safe when it lands in this column</t>
+          <t>The suit your full deck holds the fewest of is safe when it lands in this column</t>
         </is>
       </c>
       <c r="O44" s="9" t="inlineStr">
@@ -4511,7 +4504,7 @@
       <c r="M45" s="8" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → optionally shuffle the other piles in this column</t>
+          <t>When a ♦ lands in this column → optionally shuffle this column's other piles</t>
         </is>
       </c>
       <c r="O45" s="9" t="inlineStr">
@@ -4581,7 +4574,7 @@
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="11" t="inlineStr">
         <is>
-          <t>Same calls are safe on cards ±1 in value in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
+          <t>Same calls are safe on cards ±1 in value in this column — a survived Same counts as a full correct Same (charges the Same Shield, fires your Same-Power)</t>
         </is>
       </c>
       <c r="O46" s="9" t="inlineStr">
@@ -4777,7 +4770,7 @@
       <c r="M49" s="8" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>When a cursed card lands in this column → bury 1 card under that pile, then peek at the next card</t>
+          <t>When a cursed card lands in this column → bury 1 card under that pile, then peek next card</t>
         </is>
       </c>
       <c r="O49" s="9" t="inlineStr">
@@ -4843,7 +4836,7 @@
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="11" t="inlineStr">
         <is>
-          <t>Stickers that would convert into curses in this column don't — they stay as stickers</t>
+          <t>Stickers in this column never convert into curses</t>
         </is>
       </c>
       <c r="O50" s="9" t="inlineStr">
@@ -4975,7 +4968,7 @@
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr">
         <is>
-          <t>At deal end → exclude any pile in this column with a ♦ top card from the smallest-pile score</t>
+          <t>At deal end → exclude each ♦-topped pile in this column from the smallest-pile score</t>
         </is>
       </c>
       <c r="O52" s="9" t="inlineStr">
@@ -5041,7 +5034,7 @@
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>Mirrors the center column's pillar</t>
+          <t>Mirror the center column's Pillar</t>
         </is>
       </c>
       <c r="O53" s="9" t="inlineStr">
@@ -5181,7 +5174,7 @@
       <c r="M55" s="8" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>Permanently purge whichever card kills the final pile in this column</t>
+          <t>When the last pile in this column dies → permanently purge the card that killed it</t>
         </is>
       </c>
       <c r="O55" s="9" t="inlineStr">
@@ -5237,7 +5230,7 @@
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr">
         <is>
-          <t>On purchase → the store's Purge price is halved (minimum 5). No effect during deal</t>
+          <t>On purchase → halve the store's Purge price (minimum 5, no effect during deal)</t>
         </is>
       </c>
       <c r="O56" s="9" t="inlineStr">
@@ -5303,7 +5296,7 @@
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>This column starts the deal with 1 extra pile (up to 4)</t>
+          <t>This column starts each deal with 1 extra pile (max 4)</t>
         </is>
       </c>
       <c r="O57" s="9" t="inlineStr">
@@ -5369,7 +5362,7 @@
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="11" t="inlineStr">
         <is>
-          <t>One random item in every store costs 0 coins. No effect during deal</t>
+          <t>One random item in every store costs 0 (no effect during deal)</t>
         </is>
       </c>
       <c r="O58" s="9" t="inlineStr">
@@ -5435,7 +5428,7 @@
       <c r="M59" s="8" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +8 coins if only one pile is alive</t>
+          <t>At deal end if only one pile is alive → +8 coins</t>
         </is>
       </c>
       <c r="O59" s="9" t="inlineStr">
@@ -5501,7 +5494,7 @@
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>When a pile in this column dies → peek the next card</t>
+          <t>When a pile in this column dies → peek next card</t>
         </is>
       </c>
       <c r="O60" s="9" t="inlineStr">
@@ -5627,7 +5620,7 @@
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="11" t="inlineStr">
         <is>
-          <t>The first restock in each store and the first reshuffle of each deal are free</t>
+          <t>First restock of each store and first reshuffle of each deal are free</t>
         </is>
       </c>
       <c r="O62" s="9" t="inlineStr">
@@ -5687,7 +5680,7 @@
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>On purchase → purge every {rank} from your deck. No effect during deal</t>
+          <t>On purchase → purge every {rank} from your deck (no effect during deal)</t>
         </is>
       </c>
       <c r="O63" s="9" t="inlineStr">
@@ -5757,7 +5750,7 @@
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>Rare items appear in the store twice as often. No effect during deal</t>
+          <t>Rare items appear in the store twice as often (no effect during deal)</t>
         </is>
       </c>
       <c r="O64" s="9" t="inlineStr">
@@ -5893,7 +5886,7 @@
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr">
         <is>
-          <t>A royal landing on a royal survives a Same call in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
+          <t>A royal landing on a royal survives a Same call in this column — a survived Same counts as a full correct Same (charges the Same Shield, fires your Same-Power)</t>
         </is>
       </c>
       <c r="O66" s="9" t="inlineStr">
@@ -6009,7 +6002,7 @@
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="11" t="inlineStr">
         <is>
-          <t>Each pile that dies in this column has a 25% chance to be saved — the top card stays and the buried cards shuffle back into the deck</t>
+          <t>When a pile in this column dies → 25% chance to save it: the top card stays, the buried cards shuffle back into the deck</t>
         </is>
       </c>
       <c r="O68" s="9" t="inlineStr">
@@ -6075,7 +6068,7 @@
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>From the 4th consecutive correct guess in this column → bury 1 card per guess. Resets on a wrong guess or any guess in another column</t>
+          <t>From the 4th consecutive correct guess in this column → bury 1 card per guess — resets on a wrong guess or a guess in another column</t>
         </is>
       </c>
       <c r="O69" s="9" t="inlineStr">
@@ -6141,7 +6134,7 @@
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>When a {rank} lands correctly in this column → bury 1 deck card under that pile</t>
+          <t>When a {rank} lands correctly in this column → bury 1 card under that pile</t>
         </is>
       </c>
       <c r="O70" s="9" t="inlineStr">
@@ -6267,7 +6260,7 @@
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>Make ALL piles on the board equal size</t>
+          <t>Make every pile on the board equal size</t>
         </is>
       </c>
       <c r="O72" s="9" t="inlineStr">
@@ -6393,7 +6386,7 @@
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>Reset bonus coins earned this deal to zero, then peek the next card</t>
+          <t>Reset bonus coins earned this deal to 0 → peek next card</t>
         </is>
       </c>
       <c r="O74" s="9" t="inlineStr">
@@ -6449,7 +6442,7 @@
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>Remove all curses from the top cards in this column</t>
+          <t>Remove all curses from this column's top cards</t>
         </is>
       </c>
       <c r="O75" s="9" t="inlineStr">
@@ -6515,7 +6508,7 @@
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>Put a tell marker on each ♣-topped pile in this column for the next draw. Tell marker shows if the next card is higher, lower, or same</t>
+          <t>Tell each ♣-topped pile in this column for the next draw (higher/lower/same)</t>
         </is>
       </c>
       <c r="O76" s="9" t="inlineStr">
@@ -6585,7 +6578,7 @@
       <c r="M77" s="8" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>Destroy this column's pillar permanently, then peek the next 3 cards</t>
+          <t>Permanently destroy this column's Pillar → peek the next 3 cards</t>
         </is>
       </c>
       <c r="O77" s="9" t="inlineStr">
@@ -6655,7 +6648,7 @@
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>Destroy every ♥-topped pile in this column. +4 coins per pile destroyed</t>
+          <t>Destroy every ♥-topped pile in this column → +4 coins per pile</t>
         </is>
       </c>
       <c r="O78" s="9" t="inlineStr">
@@ -6767,7 +6760,7 @@
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>Revive a random dead pile in this column. Buried cards return to the deck</t>
+          <t>Revive a random dead pile in this column — buried cards return to the deck</t>
         </is>
       </c>
       <c r="O80" s="9" t="inlineStr">
@@ -6833,7 +6826,7 @@
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>Reduce the Store's Purge cost by 1 for each ♦-topped pile in this column. Minimum 5</t>
+          <t>−1 to the store's Purge price per ♦-topped pile in this column (minimum 5)</t>
         </is>
       </c>
       <c r="O81" s="9" t="inlineStr">
@@ -6949,7 +6942,7 @@
       <c r="M83" s="8" t="inlineStr"/>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>If the next card is the SAME rank as a top card anywhere on the board, the = mark appears on that card</t>
+          <t>If the next card matches a top card's rank anywhere on the board → that card shows the = mark</t>
         </is>
       </c>
       <c r="O83" s="9" t="inlineStr">
@@ -7015,7 +7008,7 @@
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="11" t="inlineStr">
         <is>
-          <t>Peek the next card. Requires every pile in this column has a ♠ on top</t>
+          <t>If every pile in this column has a ♠ top card → peek next card</t>
         </is>
       </c>
       <c r="O84" s="9" t="inlineStr">
@@ -7347,7 +7340,7 @@
       <c r="M89" s="8" t="inlineStr"/>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>Double your bonus coins earned this deal, then add a curse to a top card in this column</t>
+          <t>Double bonus coins earned this deal → add a curse to a top card in this column</t>
         </is>
       </c>
       <c r="O89" s="9" t="inlineStr">
@@ -7413,7 +7406,7 @@
       <c r="M90" s="8" t="inlineStr"/>
       <c r="N90" s="11" t="inlineStr">
         <is>
-          <t>Spend ALL your coins → peek 1 card, +1 more per 10 coins spent</t>
+          <t>Spend all your coins → peek 1 card, +1 more per 10 coins spent</t>
         </is>
       </c>
       <c r="O90" s="9" t="inlineStr">
@@ -7479,7 +7472,7 @@
       <c r="M91" s="8" t="inlineStr"/>
       <c r="N91" s="11" t="inlineStr">
         <is>
-          <t>Only usable in an ambush from Just a Two → clear the deal instantly</t>
+          <t>If in a Just a Two ambush → clear the deal instantly</t>
         </is>
       </c>
       <c r="O91" s="9" t="inlineStr">
@@ -7549,7 +7542,7 @@
       <c r="M92" s="8" t="inlineStr"/>
       <c r="N92" s="11" t="inlineStr">
         <is>
-          <t>Kill a random ♠-topped pile in this column, → peek the next 2 cards</t>
+          <t>Kill a random ♠-topped pile in this column → peek the next 2 cards</t>
         </is>
       </c>
       <c r="O92" s="9" t="inlineStr">
@@ -7619,7 +7612,7 @@
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="11" t="inlineStr">
         <is>
-          <t>In a non-boss deal, bury the whole deck under a pile in this column and win instantly. Any Base nearby is destroyed</t>
+          <t>If not a boss deal → bury the whole deck under a pile in this column and win instantly (destroys any nearby Base)</t>
         </is>
       </c>
       <c r="O93" s="9" t="inlineStr">
@@ -7685,7 +7678,7 @@
       <c r="M94" s="8" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>Peek the next card. Only works while no Same-Power is equipped</t>
+          <t>If no Same-Power is equipped → peek next card</t>
         </is>
       </c>
       <c r="O94" s="9" t="inlineStr">
@@ -7751,7 +7744,7 @@
       <c r="M95" s="8" t="inlineStr"/>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>Activate your Same-Power</t>
+          <t>Fire your Same-Power</t>
         </is>
       </c>
       <c r="O95" s="9" t="inlineStr">
@@ -7817,7 +7810,7 @@
       <c r="M96" s="8" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>Permanently set every top card's rank in this column to the bottom pile's rank</t>
+          <t>Permanently set this column's top cards to the bottom pile's rank</t>
         </is>
       </c>
       <c r="O96" s="9" t="inlineStr">
@@ -7883,7 +7876,7 @@
       <c r="M97" s="8" t="inlineStr"/>
       <c r="N97" s="11" t="inlineStr">
         <is>
-          <t>Recharge your other two bases</t>
+          <t>Recharge your other two Bases</t>
         </is>
       </c>
       <c r="O97" s="9" t="inlineStr">
@@ -8015,7 +8008,7 @@
       <c r="M99" s="8" t="inlineStr"/>
       <c r="N99" s="11" t="inlineStr">
         <is>
-          <t>Permanently set every top card's suit in this column to the bottom pile's suit</t>
+          <t>Permanently set this column's top cards to the bottom pile's suit</t>
         </is>
       </c>
       <c r="O99" s="9" t="inlineStr">
@@ -8081,7 +8074,7 @@
       <c r="M100" s="8" t="inlineStr"/>
       <c r="N100" s="11" t="inlineStr">
         <is>
-          <t>Bury 1 card under every pile with a {suit} top card</t>
+          <t>Bury 1 card under every {suit}-topped pile</t>
         </is>
       </c>
       <c r="O100" s="9" t="inlineStr">
@@ -8155,7 +8148,7 @@
       <c r="M101" s="8" t="inlineStr"/>
       <c r="N101" s="11" t="inlineStr">
         <is>
-          <t>When you call a correct Same → clear all curses from every top card on the board</t>
+          <t>Clear all curses from every top card on the board</t>
         </is>
       </c>
       <c r="O101" s="9" t="inlineStr">
@@ -8211,7 +8204,7 @@
       <c r="M102" s="8" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr">
         <is>
-          <t>Gain 1 coin for each alive pile</t>
+          <t>+1 coin per alive pile</t>
         </is>
       </c>
       <c r="O102" s="9" t="inlineStr">
@@ -8399,7 +8392,7 @@
       <c r="M105" s="8" t="inlineStr"/>
       <c r="N105" s="11" t="inlineStr">
         <is>
-          <t>A correct Same sets the top card of every alive pile to this card's rank. A Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
+          <t>Set the top card of every alive pile to this card's rank — a Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
         </is>
       </c>
       <c r="O105" s="9" t="inlineStr">
@@ -8521,7 +8514,7 @@
       <c r="M107" s="8" t="inlineStr"/>
       <c r="N107" s="11" t="inlineStr">
         <is>
-          <t>Peek the next card</t>
+          <t>Peek next card</t>
         </is>
       </c>
       <c r="O107" s="9" t="inlineStr">
@@ -8587,7 +8580,7 @@
       <c r="M108" s="8" t="inlineStr"/>
       <c r="N108" s="11" t="inlineStr">
         <is>
-          <t>Every alive pile shows a tell (higher/lower/same) for the next draw</t>
+          <t>Every alive pile gets a tell for the next draw (higher/lower/same)</t>
         </is>
       </c>
       <c r="O108" s="9" t="inlineStr">
@@ -8761,7 +8754,7 @@
       <c r="M111" s="8" t="inlineStr"/>
       <c r="N111" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this card is a pile's top card, that pile size is 1</t>
+          <t>Cursed. While top card → this pile's size is 1</t>
         </is>
       </c>
       <c r="O111" s="9" t="inlineStr">
@@ -8815,7 +8808,7 @@
       <c r="M112" s="8" t="inlineStr"/>
       <c r="N112" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, the column's Pillar does not work</t>
+          <t>Cursed. While top card → the column's Pillar does not work</t>
         </is>
       </c>
       <c r="O112" s="9" t="inlineStr">
@@ -8923,7 +8916,7 @@
       <c r="M114" s="8" t="inlineStr"/>
       <c r="N114" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, your next guess must be played there</t>
+          <t>Cursed. While top card → your next guess must be played here</t>
         </is>
       </c>
       <c r="O114" s="9" t="inlineStr">
@@ -8981,7 +8974,7 @@
       <c r="M115" s="8" t="inlineStr"/>
       <c r="N115" s="11" t="inlineStr">
         <is>
-          <t>Cursed. 10% chance this card kills the pile anyway, even if the guess is correct</t>
+          <t>Cursed. 10% chance to kill the pile even on a correct guess</t>
         </is>
       </c>
       <c r="O115" s="9" t="inlineStr">
@@ -9035,7 +9028,7 @@
       <c r="M116" s="8" t="inlineStr"/>
       <c r="N116" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, Same cannot be called there</t>
+          <t>Cursed. While top card → Same cannot be called on this pile</t>
         </is>
       </c>
       <c r="O116" s="9" t="inlineStr">
@@ -9089,7 +9082,7 @@
       <c r="M117" s="8" t="inlineStr"/>
       <c r="N117" s="11" t="inlineStr">
         <is>
-          <t>Cursed. Any card that lands on this card loses its stickers</t>
+          <t>Cursed. A card landing on this card loses its stickers</t>
         </is>
       </c>
       <c r="O117" s="9" t="inlineStr">
@@ -9147,7 +9140,7 @@
       <c r="M118" s="8" t="inlineStr"/>
       <c r="N118" s="11" t="inlineStr">
         <is>
-          <t>Cursed. 10% chance the column's Base or Pillar is destroyed</t>
+          <t>Cursed. 10% chance to destroy the column's Base or Pillar</t>
         </is>
       </c>
       <c r="O118" s="9" t="inlineStr">
@@ -9259,7 +9252,7 @@
       <c r="M120" s="8" t="inlineStr"/>
       <c r="N120" s="11" t="inlineStr">
         <is>
-          <t>Cursed. This card counts −1 toward pile size</t>
+          <t>Cursed. Counts −1 toward pile size</t>
         </is>
       </c>
       <c r="O120" s="9" t="inlineStr">
@@ -9367,7 +9360,7 @@
       <c r="M122" s="8" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr">
         <is>
-          <t>Cursed. When it lands, the card at the BOTTOM of the pile returns to the deck</t>
+          <t>Cursed. On landing → the pile's bottom card returns to the deck</t>
         </is>
       </c>
       <c r="O122" s="9" t="inlineStr">
@@ -9433,7 +9426,7 @@
       <c r="M123" s="8" t="inlineStr"/>
       <c r="N123" s="11" t="inlineStr">
         <is>
-          <t>Reveals 5 random stickers. Keep 2</t>
+          <t>Reveal 5 random stickers — keep 2</t>
         </is>
       </c>
       <c r="O123" s="9" t="inlineStr">
@@ -9489,7 +9482,7 @@
       <c r="M124" s="8" t="inlineStr"/>
       <c r="N124" s="11" t="inlineStr">
         <is>
-          <t>Reveals 3 random cards. Keep 1 to swap into your deck</t>
+          <t>Reveal 3 random cards — keep 1 to swap into your deck</t>
         </is>
       </c>
       <c r="O124" s="9" t="inlineStr">
@@ -9545,7 +9538,7 @@
       <c r="M125" s="8" t="inlineStr"/>
       <c r="N125" s="11" t="inlineStr">
         <is>
-          <t>Reveals 3 random stickers. Keep 1</t>
+          <t>Reveal 3 random stickers — keep 1</t>
         </is>
       </c>
       <c r="O125" s="9" t="inlineStr">
@@ -9611,7 +9604,7 @@
       <c r="M126" s="8" t="inlineStr"/>
       <c r="N126" s="11" t="inlineStr">
         <is>
-          <t>Reveals 5 random cards. Keep 2 to swap into your deck</t>
+          <t>Reveal 5 random cards — keep 2 to swap into your deck</t>
         </is>
       </c>
       <c r="O126" s="9" t="inlineStr">
@@ -9789,8 +9782,8 @@
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → bury 1 card under this pile.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → bury 1 card under this pile
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O3" s="9" t="inlineStr">
@@ -9850,7 +9843,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="11" t="inlineStr">
         <is>
-          <t>When a cursed card lands in this column → bury 1 card under that pile, then peek at the next card</t>
+          <t>When a cursed card lands in this column → bury 1 card under that pile, then peek next card</t>
         </is>
       </c>
       <c r="O4" s="9" t="inlineStr">
@@ -10046,7 +10039,7 @@
       <c r="M7" s="8" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>While your purse holds under 10 coins → when a ♣ lands in this column, bury 1 card under that pile</t>
+          <t>If purse &lt;10 coins → when a ♣ lands in this column bury 1</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
@@ -10112,7 +10105,7 @@
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>From the 4th consecutive correct guess in this column → bury 1 card per guess. Resets on a wrong guess or any guess in another column</t>
+          <t>From the 4th consecutive correct guess in this column → bury 1 card per guess — resets on a wrong guess or a guess in another column</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -10178,7 +10171,7 @@
       <c r="M9" s="8" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>When a {rank} lands correctly in this column → bury 1 deck card under that pile</t>
+          <t>When a {rank} lands correctly in this column → bury 1 card under that pile</t>
         </is>
       </c>
       <c r="O9" s="9" t="inlineStr">
@@ -10384,7 +10377,7 @@
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Bury 1 card under every pile with a {suit} top card</t>
+          <t>Bury 1 card under every {suit}-topped pile</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
@@ -10451,7 +10444,7 @@
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>+1 card rank (stops at Ace)</t>
+          <t>+1 rank (stops at Ace)</t>
         </is>
       </c>
       <c r="O15" s="9" t="inlineStr">
@@ -10517,7 +10510,7 @@
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>+2 card rank (stops at Ace)</t>
+          <t>+2 rank (stops at Ace)</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
@@ -10573,7 +10566,7 @@
       <c r="M17" s="8" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>Change suit to ♠</t>
+          <t>Change to ♠</t>
         </is>
       </c>
       <c r="O17" s="9" t="inlineStr">
@@ -10629,7 +10622,7 @@
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>Change suit to ♣</t>
+          <t>Change to ♣</t>
         </is>
       </c>
       <c r="O18" s="9" t="inlineStr">
@@ -10685,7 +10678,7 @@
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>Change suit to ♥</t>
+          <t>Change to ♥</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
@@ -10741,7 +10734,7 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>Change suit to ♦</t>
+          <t>Change to ♦</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
@@ -10807,7 +10800,7 @@
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>Change to random rank</t>
+          <t>Randomize rank</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
@@ -10863,7 +10856,7 @@
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Change to random suit</t>
+          <t>Randomize suit</t>
         </is>
       </c>
       <c r="O22" s="9" t="inlineStr">
@@ -10919,7 +10912,7 @@
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>-1 card rank (stops at 2)</t>
+          <t>-1 rank (stops at 2)</t>
         </is>
       </c>
       <c r="O23" s="9" t="inlineStr">
@@ -10985,7 +10978,7 @@
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>-2 card rank (stops at 2)</t>
+          <t>-2 rank (stops at 2)</t>
         </is>
       </c>
       <c r="O24" s="9" t="inlineStr">
@@ -11121,7 +11114,7 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>Permanently set every top card's rank in this column to the bottom pile's rank</t>
+          <t>Permanently set this column's top cards to the bottom pile's rank</t>
         </is>
       </c>
       <c r="O26" s="9" t="inlineStr">
@@ -11187,7 +11180,7 @@
       <c r="M27" s="8" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Permanently set every top card's suit in this column to the bottom pile's suit</t>
+          <t>Permanently set this column's top cards to the bottom pile's suit</t>
         </is>
       </c>
       <c r="O27" s="9" t="inlineStr">
@@ -11253,7 +11246,7 @@
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>A correct Same sets the top card of every alive pile to this card's rank. A Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
+          <t>Set the top card of every alive pile to this card's rank — a Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
         </is>
       </c>
       <c r="O28" s="9" t="inlineStr">
@@ -11316,8 +11309,8 @@
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → +1 coin per pile whose top card matches.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this suit → +1 coin per pile with matching suit
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O31" s="9" t="inlineStr">
@@ -11340,14 +11333,10 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>deal-end payout; curses its cover</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Curse Payoff</t>
-        </is>
-      </c>
+          <t>deal-end payout</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
           <t>Payout</t>
@@ -11387,7 +11376,7 @@
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → earn coins equal to pile size</t>
+          <t>At deal end if top card → earn coins equal to pile size</t>
         </is>
       </c>
       <c r="O32" s="9" t="inlineStr">
@@ -11593,7 +11582,7 @@
       <c r="M35" s="8" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +2 coins per pile in this column with a ♥ top card</t>
+          <t>At deal end → +2 coins per pile in this column with a ♥</t>
         </is>
       </c>
       <c r="O35" s="9" t="inlineStr">
@@ -11663,7 +11652,7 @@
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +1 coin per 5 cards in your deck, if no other pillar is equipped</t>
+          <t>At deal end if only equipped pillar → +1 coin per 5 cards in your full deck</t>
         </is>
       </c>
       <c r="O36" s="9" t="inlineStr">
@@ -11719,7 +11708,7 @@
       <c r="M37" s="8" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +4 coins if every pile in this column survived</t>
+          <t>At deal end if every pile in this column survived → +4 coins</t>
         </is>
       </c>
       <c r="O37" s="9" t="inlineStr">
@@ -11841,7 +11830,7 @@
       <c r="M39" s="8" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +8 coins if only one pile is alive</t>
+          <t>At deal end if only one pile is alive → +8 coins</t>
         </is>
       </c>
       <c r="O39" s="9" t="inlineStr">
@@ -11907,7 +11896,7 @@
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +3 coins if no pile in this column survived</t>
+          <t>At deal end if no pile in this column survived → +3 coins</t>
         </is>
       </c>
       <c r="O40" s="9" t="inlineStr">
@@ -11967,7 +11956,7 @@
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>Double your bonus coins earned this deal, then add a curse to a top card in this column</t>
+          <t>Double bonus coins earned this deal → add a curse to a top card in this column</t>
         </is>
       </c>
       <c r="O41" s="9" t="inlineStr">
@@ -12037,7 +12026,7 @@
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>Destroy every ♥-topped pile in this column. +4 coins per pile destroyed</t>
+          <t>Destroy every ♥-topped pile in this column → +4 coins per pile</t>
         </is>
       </c>
       <c r="O42" s="9" t="inlineStr">
@@ -12149,7 +12138,7 @@
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="11" t="inlineStr">
         <is>
-          <t>Gain 1 coin for each alive pile</t>
+          <t>+1 coin per alive pile</t>
         </is>
       </c>
       <c r="O44" s="9" t="inlineStr">
@@ -12222,7 +12211,7 @@
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>Only usable in an ambush from Just a Two → clear the deal instantly</t>
+          <t>If in a Just a Two ambush → clear the deal instantly</t>
         </is>
       </c>
       <c r="O47" s="9" t="inlineStr">
@@ -12292,7 +12281,7 @@
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="11" t="inlineStr">
         <is>
-          <t>In a non-boss deal, bury the whole deck under a pile in this column and win instantly. Any Base nearby is destroyed</t>
+          <t>If not a boss deal → bury the whole deck under a pile in this column and win instantly (destroys any nearby Base)</t>
         </is>
       </c>
       <c r="O48" s="9" t="inlineStr">
@@ -12369,7 +12358,7 @@
       <c r="M51" s="8" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Permanently purge whichever card kills the final pile in this column</t>
+          <t>When the last pile in this column dies → permanently purge the card that killed it</t>
         </is>
       </c>
       <c r="O51" s="9" t="inlineStr">
@@ -12429,7 +12418,7 @@
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr">
         <is>
-          <t>On purchase → purge every {rank} from your deck. No effect during deal</t>
+          <t>On purchase → purge every {rank} from your deck (no effect during deal)</t>
         </is>
       </c>
       <c r="O52" s="9" t="inlineStr">
@@ -12632,7 +12621,7 @@
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>30% chance to turn away a Just a Two mystery. 100% chance if there are no 2s in your deck. No effect during deal</t>
+          <t>30% chance to turn away a Just a Two mystery — 100% if your full deck has no 2s (no effect during deal)</t>
         </is>
       </c>
       <c r="O57" s="9" t="inlineStr">
@@ -12698,7 +12687,7 @@
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="11" t="inlineStr">
         <is>
-          <t>Mirrors the center column's pillar</t>
+          <t>Mirror the center column's Pillar</t>
         </is>
       </c>
       <c r="O58" s="9" t="inlineStr">
@@ -12764,7 +12753,7 @@
       <c r="M59" s="8" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>+30% chance to find a Beheaded Queen at a mystery stop. 100% chance if Queens are the most common rank in your deck (ties don't count). No effect during deal</t>
+          <t>+30% chance to find a Beheaded Queen at a mystery stop — 100% if Queens are the most common rank in your full deck, ties don't count (no effect during deal)</t>
         </is>
       </c>
       <c r="O59" s="9" t="inlineStr">
@@ -12830,7 +12819,7 @@
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>Recharge your other two bases</t>
+          <t>Recharge your other two Bases</t>
         </is>
       </c>
       <c r="O60" s="9" t="inlineStr">
@@ -12903,7 +12892,7 @@
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>Reveals 5 random cards. Keep 2 to swap into your deck</t>
+          <t>Reveal 5 random cards — keep 2 to swap into your deck</t>
         </is>
       </c>
       <c r="O63" s="9" t="inlineStr">
@@ -12969,7 +12958,7 @@
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>Reveals 5 random stickers. Keep 2</t>
+          <t>Reveal 5 random stickers — keep 2</t>
         </is>
       </c>
       <c r="O64" s="9" t="inlineStr">
@@ -13025,7 +13014,7 @@
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>Reveals 3 random cards. Keep 1 to swap into your deck</t>
+          <t>Reveal 3 random cards — keep 1 to swap into your deck</t>
         </is>
       </c>
       <c r="O65" s="9" t="inlineStr">
@@ -13081,7 +13070,7 @@
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr">
         <is>
-          <t>Reveals 3 random stickers. Keep 1</t>
+          <t>Reveal 3 random stickers — keep 1</t>
         </is>
       </c>
       <c r="O66" s="9" t="inlineStr">
@@ -13094,7 +13083,7 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>Peek  (13)</t>
+          <t>Peek  (12)</t>
         </is>
       </c>
     </row>
@@ -13154,8 +13143,8 @@
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>If this column has no Base → peek at the next card.
-If it has one → this sticker becomes a curse</t>
+          <t>If in column with no Base → peek next card
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O69" s="9" t="inlineStr">
@@ -13221,8 +13210,8 @@
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>If this column has no Pillar → peek at the next card.
-If it has one → this sticker becomes a curse</t>
+          <t>If in column with no Pillar → peek next card
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O70" s="9" t="inlineStr">
@@ -13245,7 +13234,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>if a rank twin is up</t>
+          <t>conditional: rank-twin bet</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr"/>
@@ -13292,7 +13281,8 @@
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>Peek at the next card if another pile shows this rank</t>
+          <t>If another pile shows this rank → peek next card
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O71" s="9" t="inlineStr">
@@ -13315,45 +13305,55 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>on an 8</t>
+          <t>on a pile death</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr"/>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Eight Ball</t>
+          <t>Last Rites</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>eightPeek</t>
-        </is>
-      </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>lastRites</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H72" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J72" s="8" t="inlineStr"/>
-      <c r="K72" s="8" t="inlineStr"/>
-      <c r="L72" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>dealsWonLegendary</t>
+        </is>
+      </c>
+      <c r="L72" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>When an 8 lands in this column → peek at the next card</t>
+          <t>When a pile in this column dies → peek next card</t>
         </is>
       </c>
       <c r="O72" s="9" t="inlineStr">
         <is>
-          <t>eightPeek</t>
+          <t>lastRites</t>
         </is>
       </c>
       <c r="P72" s="8" t="inlineStr"/>
@@ -13371,55 +13371,45 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>on a pile death</t>
+          <t>on a royal ♠</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr"/>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Last Rites</t>
+          <t>Queen's Eye</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>lastRites</t>
-        </is>
-      </c>
-      <c r="G73" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>queensEye</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H73" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K73" s="8" t="inlineStr">
-        <is>
-          <t>dealsWonLegendary</t>
-        </is>
-      </c>
-      <c r="L73" s="8" t="n">
-        <v>1</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr"/>
+      <c r="K73" s="8" t="inlineStr"/>
+      <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>When a pile in this column dies → peek the next card</t>
+          <t>When a royal ♠ (J/Q/K) lands in this column → peek next card</t>
         </is>
       </c>
       <c r="O73" s="9" t="inlineStr">
         <is>
-          <t>lastRites</t>
+          <t>queensEye</t>
         </is>
       </c>
       <c r="P73" s="8" t="inlineStr"/>
@@ -13427,7 +13417,7 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
@@ -13437,18 +13427,22 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>on a royal ♠</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr"/>
+          <t>trades the deal's banked bonus</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Coin Loss</t>
+        </is>
+      </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Queen's Eye</t>
+          <t>Bonus Reset</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>queensEye</t>
+          <t>bonusResetPeek</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -13461,21 +13455,31 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J74" s="8" t="inlineStr"/>
-      <c r="K74" s="8" t="inlineStr"/>
-      <c r="L74" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>coinsEarnedLifetime</t>
+        </is>
+      </c>
+      <c r="L74" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>When a royal ♠ (J/Q/K) lands in this column → peek at the next card</t>
+          <t>Reset bonus coins earned this deal to 0 → peek next card</t>
         </is>
       </c>
       <c r="O74" s="9" t="inlineStr">
         <is>
-          <t>queensEye</t>
+          <t>bonusResetPeek</t>
         </is>
       </c>
       <c r="P74" s="8" t="inlineStr"/>
@@ -13493,22 +13497,22 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>trades the deal's banked bonus</t>
+          <t>destroys this column's pillar</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Coin Loss</t>
+          <t>Loadout</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Bonus Reset</t>
+          <t>Demolish</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>bonusResetPeek</t>
+          <t>demolish</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -13517,7 +13521,7 @@
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
@@ -13526,26 +13530,26 @@
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K75" s="8" t="inlineStr">
         <is>
-          <t>coinsEarnedLifetime</t>
+          <t>pillarsPlaced</t>
         </is>
       </c>
       <c r="L75" s="8" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>Reset bonus coins earned this deal to zero, then peek the next card</t>
+          <t>Permanently destroy this column's Pillar → peek the next 3 cards</t>
         </is>
       </c>
       <c r="O75" s="9" t="inlineStr">
         <is>
-          <t>bonusResetPeek</t>
+          <t>demolish</t>
         </is>
       </c>
       <c r="P75" s="8" t="inlineStr"/>
@@ -13563,31 +13567,27 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>destroys this column's pillar</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Loadout</t>
-        </is>
-      </c>
+          <t>spends the whole purse</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr"/>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Demolish</t>
+          <t>Empty Purse</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>demolish</t>
-        </is>
-      </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>emptyPurse</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
@@ -13596,26 +13596,26 @@
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K76" s="8" t="inlineStr">
         <is>
-          <t>pillarsPlaced</t>
+          <t>coinsEarnedLifetime</t>
         </is>
       </c>
       <c r="L76" s="8" t="n">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>Destroy this column's pillar permanently, then peek the next 3 cards</t>
+          <t>Spend all your coins → peek 1 card, +1 more per 10 coins spent</t>
         </is>
       </c>
       <c r="O76" s="9" t="inlineStr">
         <is>
-          <t>demolish</t>
+          <t>emptyPurse</t>
         </is>
       </c>
       <c r="P76" s="8" t="inlineStr"/>
@@ -13633,18 +13633,22 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>spends the whole purse</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr"/>
+          <t>kills a ♠ pile first</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Pile Destruction</t>
+        </is>
+      </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Empty Purse</t>
+          <t>Kamikaze</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>emptyPurse</t>
+          <t>kamikaze</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
@@ -13653,7 +13657,7 @@
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
@@ -13667,21 +13671,21 @@
       </c>
       <c r="K77" s="8" t="inlineStr">
         <is>
-          <t>coinsEarnedLifetime</t>
+          <t>dealsWonLegendary</t>
         </is>
       </c>
       <c r="L77" s="8" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="M77" s="8" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>Spend ALL your coins → peek 1 card, +1 more per 10 coins spent</t>
+          <t>Kill a random ♠-topped pile in this column → peek the next 2 cards</t>
         </is>
       </c>
       <c r="O77" s="9" t="inlineStr">
         <is>
-          <t>emptyPurse</t>
+          <t>kamikaze</t>
         </is>
       </c>
       <c r="P77" s="8" t="inlineStr"/>
@@ -13699,22 +13703,18 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>kills a ♠ pile first</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Pile Destruction</t>
-        </is>
-      </c>
+          <t>needs an empty Same-Power slot</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Kamikaze</t>
+          <t>Lone Eye</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>kamikaze</t>
+          <t>lonePeek</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
@@ -13723,35 +13723,35 @@
         </is>
       </c>
       <c r="H78" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K78" s="8" t="inlineStr">
+        <is>
+          <t>samesCalled</t>
+        </is>
+      </c>
+      <c r="L78" s="8" t="n">
         <v>8</v>
-      </c>
-      <c r="I78" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J78" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K78" s="8" t="inlineStr">
-        <is>
-          <t>dealsWonLegendary</t>
-        </is>
-      </c>
-      <c r="L78" s="8" t="n">
-        <v>2</v>
       </c>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>Kill a random ♠-topped pile in this column, → peek the next 2 cards</t>
+          <t>If no Same-Power is equipped → peek next card</t>
         </is>
       </c>
       <c r="O78" s="9" t="inlineStr">
         <is>
-          <t>kamikaze</t>
+          <t>lonePeek</t>
         </is>
       </c>
       <c r="P78" s="8" t="inlineStr"/>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>needs an empty Same-Power slot</t>
+          <t>needs an all-♠ column</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr"/>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Lone Eye</t>
+          <t>Spade Peeker</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>lonePeek</t>
-        </is>
-      </c>
-      <c r="G79" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>spadePeek</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H79" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
@@ -13803,21 +13803,21 @@
       </c>
       <c r="K79" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>zenHardWon</t>
         </is>
       </c>
       <c r="L79" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M79" s="8" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>Peek the next card. Only works while no Same-Power is equipped</t>
+          <t>If every pile in this column has a ♠ top card → peek next card</t>
         </is>
       </c>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>lonePeek</t>
+          <t>spadePeek</t>
         </is>
       </c>
       <c r="P79" s="8" t="inlineStr"/>
@@ -13825,7 +13825,7 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
@@ -13835,121 +13835,111 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>needs an all-♠ column</t>
+          <t>on a Same</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr"/>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Spade Peeker</t>
+          <t>Same Peeker</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>spadePeek</t>
-        </is>
-      </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>samePeek</t>
+        </is>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H80" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K80" s="8" t="inlineStr">
-        <is>
-          <t>zenHardWon</t>
-        </is>
-      </c>
-      <c r="L80" s="8" t="n">
-        <v>1</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr"/>
+      <c r="L80" s="8" t="n"/>
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>Peek the next card. Requires every pile in this column has a ♠ on top</t>
+          <t>Peek next card</t>
         </is>
       </c>
       <c r="O80" s="9" t="inlineStr">
         <is>
-          <t>spadePeek</t>
+          <t>samePeek</t>
         </is>
       </c>
       <c r="P80" s="8" t="inlineStr"/>
     </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Same-Powers</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Peek</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>on a Same</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>Same Peeker</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>samePeek</t>
-        </is>
-      </c>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H81" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I81" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>Pile Size &amp; Score  (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Pile Size &amp; Score</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>score shelter</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr"/>
-      <c r="L81" s="8" t="n"/>
-      <c r="M81" s="8" t="inlineStr"/>
-      <c r="N81" s="11" t="inlineStr">
-        <is>
-          <t>Peek the next card</t>
-        </is>
-      </c>
-      <c r="O81" s="9" t="inlineStr">
-        <is>
-          <t>samePeek</t>
-        </is>
-      </c>
-      <c r="P81" s="8" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="15" t="inlineStr">
-        <is>
-          <t>Pile Size &amp; Score  (6)</t>
-        </is>
-      </c>
+      <c r="J83" s="8" t="inlineStr"/>
+      <c r="K83" s="8" t="inlineStr"/>
+      <c r="L83" s="8" t="n"/>
+      <c r="M83" s="8" t="inlineStr"/>
+      <c r="N83" s="11" t="inlineStr">
+        <is>
+          <t>At deal end if top card → exclude from smallest-pile size</t>
+        </is>
+      </c>
+      <c r="O83" s="9" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="P83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -13964,31 +13954,27 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>score shelter; curses its cover</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>Curse Payoff</t>
-        </is>
-      </c>
+          <t>conditional: equalises the board</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Anchor</t>
+          <t>Donate</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>anchor</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>donate</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
@@ -14001,12 +13987,13 @@
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="11" t="inlineStr">
         <is>
-          <t>At deal end if this card tops its pile → exclude the pile from the smallest-pile score</t>
+          <t>If another pile shows this suit → make all pile sizes equal size
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O84" s="9" t="inlineStr">
         <is>
-          <t>anchor</t>
+          <t>donate</t>
         </is>
       </c>
       <c r="P84" s="8" t="inlineStr"/>
@@ -14014,7 +14001,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -14024,46 +14011,55 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>conditional: equalises the board</t>
+          <t>♦ tops excluded</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Donate</t>
+          <t>Diamond Anchor</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>donate</t>
-        </is>
-      </c>
-      <c r="G85" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>diamondAnchor</t>
+        </is>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J85" s="8" t="inlineStr"/>
-      <c r="K85" s="8" t="inlineStr"/>
-      <c r="L85" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>diamondsPlayed</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="n">
+        <v>200</v>
+      </c>
       <c r="M85" s="8" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → make all pile sizes equal.
-Otherwise → this sticker becomes a curse</t>
+          <t>At deal end → exclude each ♦-topped pile in this column from the smallest-pile score</t>
         </is>
       </c>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>donate</t>
+          <t>diamondAnchor</t>
         </is>
       </c>
       <c r="P85" s="8" t="inlineStr"/>
@@ -14081,27 +14077,27 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>♦ tops excluded</t>
+          <t>equalises on a ♦</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr"/>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Diamond Anchor</t>
+          <t>Diamond Distribution</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>diamondAnchor</t>
-        </is>
-      </c>
-      <c r="G86" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>diamondDistribution</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H86" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
@@ -14115,21 +14111,21 @@
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>diamondsPlayed</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L86" s="8" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="11" t="inlineStr">
         <is>
-          <t>At deal end → exclude any pile in this column with a ♦ top card from the smallest-pile score</t>
+          <t>When a ♦ lands in this column → make this column's piles equal size</t>
         </is>
       </c>
       <c r="O86" s="9" t="inlineStr">
         <is>
-          <t>diamondAnchor</t>
+          <t>diamondDistribution</t>
         </is>
       </c>
       <c r="P86" s="8" t="inlineStr"/>
@@ -14147,27 +14143,27 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>equalises on a ♦</t>
+          <t>an extra pile</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr"/>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Diamond Distribution</t>
+          <t>Fourth Seat</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>diamondDistribution</t>
-        </is>
-      </c>
-      <c r="G87" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>fourthSeat</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H87" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
@@ -14176,26 +14172,26 @@
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K87" s="8" t="inlineStr">
         <is>
-          <t>removalsUsed</t>
+          <t>endlessStagesReached</t>
         </is>
       </c>
       <c r="L87" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M87" s="8" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → make all piles in this column equal size</t>
+          <t>This column starts each deal with 1 extra pile (max 4)</t>
         </is>
       </c>
       <c r="O87" s="9" t="inlineStr">
         <is>
-          <t>diamondDistribution</t>
+          <t>columnPiles</t>
         </is>
       </c>
       <c r="P87" s="8" t="inlineStr"/>
@@ -14203,7 +14199,7 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
@@ -14213,121 +14209,122 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>an extra pile</t>
+          <t>equalises the whole board</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Fourth Seat</t>
+          <t>Ballast</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>fourthSeat</t>
-        </is>
-      </c>
-      <c r="G88" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>evenOut</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H88" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J88" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K88" s="8" t="inlineStr">
-        <is>
-          <t>endlessStagesReached</t>
-        </is>
-      </c>
-      <c r="L88" s="8" t="n">
-        <v>1</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="8" t="n"/>
       <c r="M88" s="8" t="inlineStr"/>
       <c r="N88" s="11" t="inlineStr">
         <is>
-          <t>This column starts the deal with 1 extra pile (up to 4)</t>
+          <t>Make every pile on the board equal size</t>
         </is>
       </c>
       <c r="O88" s="9" t="inlineStr">
         <is>
-          <t>columnPiles</t>
+          <t>evenOut</t>
         </is>
       </c>
       <c r="P88" s="8" t="inlineStr"/>
     </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>Bases</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Pile Size &amp; Score</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>equalises the whole board</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr"/>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>Ballast</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>evenOut</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="n">
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>Safety &amp; Saves  (15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Safety &amp; Saves</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>conditional: carrier safe on a matched bet</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>suitImmunity</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J89" s="8" t="inlineStr"/>
-      <c r="K89" s="8" t="inlineStr"/>
-      <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8" t="inlineStr"/>
-      <c r="N89" s="11" t="inlineStr">
-        <is>
-          <t>Make ALL piles on the board equal size</t>
-        </is>
-      </c>
-      <c r="O89" s="9" t="inlineStr">
-        <is>
-          <t>evenOut</t>
-        </is>
-      </c>
-      <c r="P89" s="8" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="15" t="inlineStr">
-        <is>
-          <t>Safety &amp; Saves  (15)</t>
-        </is>
-      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>spadesPlayed</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="M91" s="8" t="inlineStr"/>
+      <c r="N91" s="11" t="inlineStr">
+        <is>
+          <t>If another pile shows this suit → safe
+Otherwise → this becomes a curse</t>
+        </is>
+      </c>
+      <c r="O91" s="9" t="inlineStr">
+        <is>
+          <t>suitImmunity</t>
+        </is>
+      </c>
+      <c r="P91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -14342,56 +14339,46 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>conditional: carrier safe on a matched bet</t>
+          <t>conditional: rank-matched tie save</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Same-Safe</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>suitImmunity</t>
-        </is>
-      </c>
-      <c r="G92" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>tieSafe</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J92" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K92" s="8" t="inlineStr">
-        <is>
-          <t>spadesPlayed</t>
-        </is>
-      </c>
-      <c r="L92" s="8" t="n">
-        <v>150</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr"/>
+      <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="inlineStr"/>
       <c r="N92" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → this card is safe when it lands.
-Otherwise → this sticker becomes a curse</t>
+          <t>If another pile shows this rank → safe
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O92" s="9" t="inlineStr">
         <is>
-          <t>suitImmunity</t>
+          <t>tieSafe</t>
         </is>
       </c>
       <c r="P92" s="8" t="inlineStr"/>
@@ -14399,7 +14386,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -14409,46 +14396,59 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>conditional: rank-matched tie save</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Same-Safe</t>
+          <t>Close Call</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>tieSafe</t>
-        </is>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>sameTolNear</t>
+        </is>
+      </c>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J93" s="8" t="inlineStr"/>
-      <c r="K93" s="8" t="inlineStr"/>
-      <c r="L93" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>correctSames</t>
+        </is>
+      </c>
+      <c r="L93" s="8" t="n">
+        <v>52</v>
+      </c>
       <c r="M93" s="8" t="inlineStr"/>
       <c r="N93" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this rank → Safe
-Otherwise → Sticker becomes cursed</t>
+          <t>Same calls are safe on cards ±1 in value in this column — a survived Same counts as a full correct Same (charges the Same Shield, fires your Same-Power)</t>
         </is>
       </c>
       <c r="O93" s="9" t="inlineStr">
         <is>
-          <t>tieSafe</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P93" s="8" t="inlineStr"/>
@@ -14466,22 +14466,18 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>any tie, in column</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr"/>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Close Call</t>
+          <t>Column Tie-Safe</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>sameTolNear</t>
+          <t>columnTieSafe</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
@@ -14490,7 +14486,7 @@
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
@@ -14504,21 +14500,21 @@
       </c>
       <c r="K94" s="8" t="inlineStr">
         <is>
-          <t>correctSames</t>
+          <t>samesCalled</t>
         </is>
       </c>
       <c r="L94" s="8" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="M94" s="8" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>Same calls are safe on cards ±1 in value in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
+          <t>Any tie is safe in this column</t>
         </is>
       </c>
       <c r="O94" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>columnTieSafe</t>
         </is>
       </c>
       <c r="P94" s="8" t="inlineStr"/>
@@ -14536,18 +14532,18 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>any tie, in column</t>
+          <t>majority suit</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr"/>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Column Tie-Safe</t>
+          <t>Majority Rule</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>columnTieSafe</t>
+          <t>suitMajoritySafe</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -14556,7 +14552,7 @@
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
@@ -14565,29 +14561,33 @@
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K95" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>bossesBeaten</t>
         </is>
       </c>
       <c r="L95" s="8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M95" s="8" t="inlineStr"/>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>Any tie is safe in this column</t>
+          <t>If half or more of your full deck is {suit} → {suit} cards are safe when they land in this column</t>
         </is>
       </c>
       <c r="O95" s="9" t="inlineStr">
         <is>
-          <t>columnTieSafe</t>
-        </is>
-      </c>
-      <c r="P95" s="8" t="inlineStr"/>
+          <t>suitMajoritySafe</t>
+        </is>
+      </c>
+      <c r="P95" s="14" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -14602,55 +14602,45 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>majority suit</t>
+          <t>deck's commonest rank</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr"/>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Majority Rule</t>
+          <t>Rank Shield</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>suitMajoritySafe</t>
-        </is>
-      </c>
-      <c r="G96" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>rankShield</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J96" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K96" s="8" t="inlineStr">
-        <is>
-          <t>bossesBeaten</t>
-        </is>
-      </c>
-      <c r="L96" s="8" t="n">
-        <v>6</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J96" s="8" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>If half or more of your full deck is {suit} → {suit} cards are safe when they land in this column</t>
+          <t>The most common rank in your full deck ({rank}) is always safe in this column</t>
         </is>
       </c>
       <c r="O96" s="9" t="inlineStr">
         <is>
-          <t>suitMajoritySafe</t>
+          <t>rankShield</t>
         </is>
       </c>
       <c r="P96" s="14" t="inlineStr">
@@ -14672,52 +14662,58 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>deck's commonest rank</t>
+          <t>revive a dead pile</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Rank Shield</t>
+          <t>Revive</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>rankShield</t>
-        </is>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>revive</t>
+        </is>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr"/>
-      <c r="L97" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J97" s="8" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>dealsWonLegendary</t>
+        </is>
+      </c>
+      <c r="L97" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="M97" s="8" t="inlineStr"/>
       <c r="N97" s="11" t="inlineStr">
         <is>
-          <t>Most common card in deck ({rank}) is always safe in this column</t>
+          <t>When a pile in this column reaches 10 cards → revive one dead pile</t>
         </is>
       </c>
       <c r="O97" s="9" t="inlineStr">
         <is>
-          <t>rankShield</t>
-        </is>
-      </c>
-      <c r="P97" s="14" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+          <t>revive</t>
+        </is>
+      </c>
+      <c r="P97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -14732,18 +14728,22 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>revive a dead pile</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Revive</t>
+          <t>Royal Pair</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>sameTolRoyal</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
@@ -14752,7 +14752,7 @@
         </is>
       </c>
       <c r="H98" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
@@ -14761,26 +14761,26 @@
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K98" s="8" t="inlineStr">
         <is>
-          <t>dealsWonLegendary</t>
+          <t>samesCalled</t>
         </is>
       </c>
       <c r="L98" s="8" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="M98" s="8" t="inlineStr"/>
       <c r="N98" s="11" t="inlineStr">
         <is>
-          <t>When a pile in this column reaches 10 cards → revive one dead pile</t>
+          <t>A royal landing on a royal survives a Same call in this column — a survived Same counts as a full correct Same (charges the Same Shield, fires your Same-Power)</t>
         </is>
       </c>
       <c r="O98" s="9" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P98" s="8" t="inlineStr"/>
@@ -14798,31 +14798,27 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>royals, if no 2s in deck</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr"/>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Royal Pair</t>
+          <t>Royal Sanctuary</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>sameTolRoyal</t>
-        </is>
-      </c>
-      <c r="G99" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>royalSanctuary</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H99" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
@@ -14836,21 +14832,21 @@
       </c>
       <c r="K99" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L99" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M99" s="8" t="inlineStr"/>
       <c r="N99" s="11" t="inlineStr">
         <is>
-          <t>A royal landing on a royal survives a Same call in this column. A survived Same counts as a full correct Same — charges the Same Shield and fires your Same-Power</t>
+          <t>If your full deck has no 2s → royals (J/Q/K) are always safe in this column</t>
         </is>
       </c>
       <c r="O99" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>royalSafeNoTwos</t>
         </is>
       </c>
       <c r="P99" s="8" t="inlineStr"/>
@@ -14868,23 +14864,27 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>royals, if no 2s in deck</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Royal Sanctuary</t>
+          <t>Same Suit Safe</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>royalSanctuary</t>
-        </is>
-      </c>
-      <c r="G100" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>sameTolSuit</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H100" s="8" t="n">
@@ -14892,31 +14892,21 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J100" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K100" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L100" s="8" t="n">
-        <v>30</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J100" s="8" t="inlineStr"/>
+      <c r="K100" s="8" t="inlineStr"/>
+      <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="inlineStr"/>
       <c r="N100" s="11" t="inlineStr">
         <is>
-          <t>If your full deck contains no 2s → royals (J/Q/K) are always safe in this column</t>
+          <t>A card landing on its own suit is safe in this column</t>
         </is>
       </c>
       <c r="O100" s="9" t="inlineStr">
         <is>
-          <t>royalSafeNoTwos</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P100" s="8" t="inlineStr"/>
@@ -14934,27 +14924,23 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>deck's scarcest suit</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr"/>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Same Suit Safe</t>
+          <t>Scarce Suit</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>sameTolSuit</t>
-        </is>
-      </c>
-      <c r="G101" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>suitShield</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H101" s="8" t="n">
@@ -14971,12 +14957,12 @@
       <c r="M101" s="8" t="inlineStr"/>
       <c r="N101" s="11" t="inlineStr">
         <is>
-          <t>A card landing on its own suit is safe in this column</t>
+          <t>The suit your full deck holds the fewest of is safe when it lands in this column</t>
         </is>
       </c>
       <c r="O101" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>suitShieldDaily</t>
         </is>
       </c>
       <c r="P101" s="8" t="inlineStr"/>
@@ -14994,23 +14980,23 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>deck's scarcest suit</t>
+          <t>chance to save a dying pile</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr"/>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Scarce Suit</t>
+          <t>Second Wind</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>suitShield</t>
-        </is>
-      </c>
-      <c r="G102" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>secondWind</t>
+        </is>
+      </c>
+      <c r="G102" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H102" s="8" t="n">
@@ -15027,12 +15013,12 @@
       <c r="M102" s="8" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr">
         <is>
-          <t>The suit your deck holds the fewest of is safe when it lands in this column</t>
+          <t>When a pile in this column dies → 25% chance to save it: the top card stays, the buried cards shuffle back into the deck</t>
         </is>
       </c>
       <c r="O102" s="9" t="inlineStr">
         <is>
-          <t>suitShieldDaily</t>
+          <t>secondWind</t>
         </is>
       </c>
       <c r="P102" s="8" t="inlineStr"/>
@@ -15050,18 +15036,18 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>chance to save a dying pile</t>
+          <t>aces high or low</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr"/>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Second Wind</t>
+          <t>Wild Aces</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>secondWind</t>
+          <t>wildAces</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
@@ -15070,25 +15056,35 @@
         </is>
       </c>
       <c r="H103" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J103" s="8" t="inlineStr"/>
-      <c r="K103" s="8" t="inlineStr"/>
-      <c r="L103" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K103" s="8" t="inlineStr">
+        <is>
+          <t>jokersPlayed</t>
+        </is>
+      </c>
+      <c r="L103" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="M103" s="8" t="inlineStr"/>
       <c r="N103" s="11" t="inlineStr">
         <is>
-          <t>Each pile that dies in this column has a 25% chance to be saved — the top card stays and the buried cards shuffle back into the deck</t>
+          <t>Aces count as high or low in this column</t>
         </is>
       </c>
       <c r="O103" s="9" t="inlineStr">
         <is>
-          <t>secondWind</t>
+          <t>wildAces</t>
         </is>
       </c>
       <c r="P103" s="8" t="inlineStr"/>
@@ -15096,7 +15092,7 @@
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
@@ -15106,55 +15102,45 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>aces high or low</t>
+          <t>revive a dead pile</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr"/>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Wild Aces</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>wildAces</t>
-        </is>
-      </c>
-      <c r="G104" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>revive</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H104" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J104" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K104" s="8" t="inlineStr">
-        <is>
-          <t>jokersPlayed</t>
-        </is>
-      </c>
-      <c r="L104" s="8" t="n">
-        <v>8</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J104" s="8" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr"/>
+      <c r="L104" s="8" t="n"/>
       <c r="M104" s="8" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr">
         <is>
-          <t>Aces count as high or low in this column</t>
+          <t>Revive a random dead pile in this column — buried cards return to the deck</t>
         </is>
       </c>
       <c r="O104" s="9" t="inlineStr">
         <is>
-          <t>wildAces</t>
+          <t>reviveBase</t>
         </is>
       </c>
       <c r="P104" s="8" t="inlineStr"/>
@@ -15162,7 +15148,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -15172,121 +15158,132 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>revive a dead pile</t>
+          <t>revive on a Same</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr"/>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Rekindle</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>revive</t>
-        </is>
-      </c>
-      <c r="G105" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>linkRevive</t>
+        </is>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J105" s="8" t="inlineStr"/>
-      <c r="K105" s="8" t="inlineStr"/>
-      <c r="L105" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K105" s="8" t="inlineStr">
+        <is>
+          <t>correctSames</t>
+        </is>
+      </c>
+      <c r="L105" s="8" t="n">
+        <v>24</v>
+      </c>
       <c r="M105" s="8" t="inlineStr"/>
       <c r="N105" s="11" t="inlineStr">
         <is>
-          <t>Revive a random dead pile in this column. Buried cards return to the deck</t>
+          <t>Revive a dead pile</t>
         </is>
       </c>
       <c r="O105" s="9" t="inlineStr">
         <is>
-          <t>reviveBase</t>
+          <t>linkRevive</t>
         </is>
       </c>
       <c r="P105" s="8" t="inlineStr"/>
     </row>
-    <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>Same-Powers</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>Safety &amp; Saves</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t>revive on a Same</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr"/>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t>Rekindle</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>linkRevive</t>
-        </is>
-      </c>
-      <c r="G106" s="13" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power  (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>conditional: rank-matched charge</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr"/>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>Recharge Shield</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>rechargeSameShield</t>
+        </is>
+      </c>
+      <c r="G108" s="13" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="H106" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="H108" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J106" s="8" t="inlineStr">
+      <c r="J108" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K106" s="8" t="inlineStr">
+      <c r="K108" s="8" t="inlineStr">
         <is>
           <t>correctSames</t>
         </is>
       </c>
-      <c r="L106" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M106" s="8" t="inlineStr"/>
-      <c r="N106" s="11" t="inlineStr">
-        <is>
-          <t>Revive a dead pile</t>
-        </is>
-      </c>
-      <c r="O106" s="9" t="inlineStr">
-        <is>
-          <t>linkRevive</t>
-        </is>
-      </c>
-      <c r="P106" s="8" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="15" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power  (4)</t>
-        </is>
-      </c>
+      <c r="L108" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M108" s="8" t="inlineStr"/>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>If another pile shows this rank → charge Same Shield
+Otherwise → this becomes a curse</t>
+        </is>
+      </c>
+      <c r="O108" s="9" t="inlineStr">
+        <is>
+          <t>rechargeSameShield</t>
+        </is>
+      </c>
+      <c r="P108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -15301,18 +15298,18 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>conditional: rank-matched charge</t>
+          <t>conditional: rank-matched power fire</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr"/>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Recharge Shield</t>
+          <t>Tap Power</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>rechargeSameShield</t>
+          <t>activateSamePower</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
@@ -15321,7 +15318,7 @@
         </is>
       </c>
       <c r="H109" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
@@ -15339,18 +15336,18 @@
         </is>
       </c>
       <c r="L109" s="8" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="M109" s="8" t="inlineStr"/>
       <c r="N109" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this rank → Charge Same Shield
-Otherwise → Sticker becomes cursed</t>
+          <t>If another pile shows this rank → fire Same Power
+Otherwise → this becomes a curse</t>
         </is>
       </c>
       <c r="O109" s="9" t="inlineStr">
         <is>
-          <t>rechargeSameShield</t>
+          <t>activateSamePower</t>
         </is>
       </c>
       <c r="P109" s="8" t="inlineStr"/>
@@ -15358,7 +15355,7 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
@@ -15374,12 +15371,12 @@
       <c r="D110" s="8" t="inlineStr"/>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Tap Power</t>
+          <t>Power Surge</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>activateSamePower</t>
+          <t>activateSame</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
@@ -15388,7 +15385,7 @@
         </is>
       </c>
       <c r="H110" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
@@ -15406,13 +15403,12 @@
         </is>
       </c>
       <c r="L110" s="8" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M110" s="8" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this rank → Fire Same Power
-Otherwise → Sticker becomes cursed</t>
+          <t>Fire your Same-Power</t>
         </is>
       </c>
       <c r="O110" s="9" t="inlineStr">
@@ -15435,18 +15431,18 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>conditional: rank-matched power fire</t>
+          <t>conditional: rank-matched charge</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr"/>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Power Surge</t>
+          <t>Recharge Cell</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>activateSame</t>
+          <t>rechargeSame</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -15464,7 +15460,7 @@
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K111" s="8" t="inlineStr">
@@ -15473,98 +15469,99 @@
         </is>
       </c>
       <c r="L111" s="8" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="M111" s="8" t="inlineStr"/>
       <c r="N111" s="11" t="inlineStr">
         <is>
-          <t>Activate your Same-Power</t>
+          <t>Charge the Same Shield</t>
         </is>
       </c>
       <c r="O111" s="9" t="inlineStr">
         <is>
-          <t>activateSamePower</t>
+          <t>rechargeSameShield</t>
         </is>
       </c>
       <c r="P111" s="8" t="inlineStr"/>
     </row>
-    <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>Bases</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>conditional: rank-matched charge</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr"/>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>Recharge Cell</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>rechargeSame</t>
-        </is>
-      </c>
-      <c r="G112" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H112" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I112" s="8" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>Shuffle  (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Shuffle</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>conditional: offered, matching piles</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr"/>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>diamondSnob</t>
+        </is>
+      </c>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J112" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K112" s="8" t="inlineStr">
-        <is>
-          <t>correctSames</t>
-        </is>
-      </c>
-      <c r="L112" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="M112" s="8" t="inlineStr"/>
-      <c r="N112" s="11" t="inlineStr">
-        <is>
-          <t>Charge the Same Shield</t>
-        </is>
-      </c>
-      <c r="O112" s="9" t="inlineStr">
-        <is>
-          <t>rechargeSameShield</t>
-        </is>
-      </c>
-      <c r="P112" s="8" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="15" t="inlineStr">
-        <is>
-          <t>Shuffle  (4)</t>
-        </is>
-      </c>
+      <c r="J114" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K114" s="8" t="inlineStr">
+        <is>
+          <t>removalsUsed</t>
+        </is>
+      </c>
+      <c r="L114" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M114" s="8" t="inlineStr"/>
+      <c r="N114" s="11" t="inlineStr">
+        <is>
+          <t>If another pile shows this suit → optionally shuffle those piles
+Otherwise → this becomes a curse</t>
+        </is>
+      </c>
+      <c r="O114" s="9" t="inlineStr">
+        <is>
+          <t>diamondSnob</t>
+        </is>
+      </c>
+      <c r="P114" s="8" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
@@ -15574,18 +15571,18 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>conditional: offered, matching piles</t>
+          <t>column, on a ♦</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr"/>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Shuffler</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>diamondSnob</t>
+          <t>royalCourt</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -15594,36 +15591,25 @@
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J115" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K115" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L115" s="8" t="n">
-        <v>18</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J115" s="8" t="inlineStr"/>
+      <c r="K115" s="8" t="inlineStr"/>
+      <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="inlineStr"/>
       <c r="N115" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → optionally shuffle those piles.
-Otherwise → this sticker becomes a curse</t>
+          <t>When a ♦ lands in this column → optionally shuffle this column's other piles</t>
         </is>
       </c>
       <c r="O115" s="9" t="inlineStr">
         <is>
-          <t>diamondSnob</t>
+          <t>shuffler</t>
         </is>
       </c>
       <c r="P115" s="8" t="inlineStr"/>
@@ -15631,7 +15617,7 @@
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -15641,27 +15627,27 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>column, on a ♦</t>
+          <t>this column</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr"/>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Shuffler</t>
+          <t>Upheaval</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>royalCourt</t>
-        </is>
-      </c>
-      <c r="G116" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>shuffleColumn</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H116" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
@@ -15674,12 +15660,12 @@
       <c r="M116" s="8" t="inlineStr"/>
       <c r="N116" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → optionally shuffle the other piles in this column</t>
+          <t>Shuffle every pile in this column</t>
         </is>
       </c>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>shuffler</t>
+          <t>shuffleColumn</t>
         </is>
       </c>
       <c r="P116" s="8" t="inlineStr"/>
@@ -15687,7 +15673,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
@@ -15697,27 +15683,27 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>this column</t>
+          <t>every alive pile</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr"/>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Upheaval</t>
+          <t>Link Shuffler</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>shuffleColumn</t>
-        </is>
-      </c>
-      <c r="G117" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>linkShuffle</t>
+        </is>
+      </c>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
@@ -15730,83 +15716,93 @@
       <c r="M117" s="8" t="inlineStr"/>
       <c r="N117" s="11" t="inlineStr">
         <is>
-          <t>Shuffle every pile in this column</t>
+          <t>Shuffle every alive pile</t>
         </is>
       </c>
       <c r="O117" s="9" t="inlineStr">
         <is>
-          <t>shuffleColumn</t>
+          <t>linkShuffle</t>
         </is>
       </c>
       <c r="P117" s="8" t="inlineStr"/>
     </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>Same-Powers</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>Shuffle</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>every alive pile</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr"/>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>Link Shuffler</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr">
-        <is>
-          <t>linkShuffle</t>
-        </is>
-      </c>
-      <c r="G118" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H118" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I118" s="8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J118" s="8" t="inlineStr"/>
-      <c r="K118" s="8" t="inlineStr"/>
-      <c r="L118" s="8" t="n"/>
-      <c r="M118" s="8" t="inlineStr"/>
-      <c r="N118" s="11" t="inlineStr">
-        <is>
-          <t>Shuffle every alive pile</t>
-        </is>
-      </c>
-      <c r="O118" s="9" t="inlineStr">
-        <is>
-          <t>linkShuffle</t>
-        </is>
-      </c>
-      <c r="P118" s="8" t="inlineStr"/>
+    <row r="119">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>Sticker Grant  (3)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="15" t="inlineStr">
-        <is>
-          <t>Sticker Grant  (3)</t>
-        </is>
-      </c>
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>Pillars</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Sticker Grant</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>chance, on landing</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr"/>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>Flypaper</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>flypaper</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J120" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K120" s="8" t="inlineStr">
+        <is>
+          <t>stickersApplied</t>
+        </is>
+      </c>
+      <c r="L120" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="M120" s="8" t="inlineStr"/>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>When a card lands correctly in this column → 5% chance it gains a random sticker</t>
+        </is>
+      </c>
+      <c r="O120" s="9" t="inlineStr">
+        <is>
+          <t>flypaper</t>
+        </is>
+      </c>
+      <c r="P120" s="8" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
@@ -15816,18 +15812,18 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>chance, on landing</t>
+          <t>one column top</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr"/>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Flypaper</t>
+          <t>Wild Sticker</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>flypaper</t>
+          <t>randomSticker</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -15836,7 +15832,7 @@
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
@@ -15854,17 +15850,17 @@
         </is>
       </c>
       <c r="L121" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M121" s="8" t="inlineStr"/>
       <c r="N121" s="11" t="inlineStr">
         <is>
-          <t>When a card lands correctly in this column → 5% chance it gains a random sticker</t>
+          <t>Apply a random sticker to a random top card in this column</t>
         </is>
       </c>
       <c r="O121" s="9" t="inlineStr">
         <is>
-          <t>flypaper</t>
+          <t>randomSticker</t>
         </is>
       </c>
       <c r="P121" s="8" t="inlineStr"/>
@@ -15872,7 +15868,7 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Same-Powers</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
@@ -15882,27 +15878,27 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>one column top</t>
+          <t>every top in the column</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr"/>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Wild Sticker</t>
+          <t>Sticker Spray</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>randomSticker</t>
-        </is>
-      </c>
-      <c r="G122" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>linkSticker</t>
+        </is>
+      </c>
+      <c r="G122" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H122" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
@@ -15920,93 +15916,93 @@
         </is>
       </c>
       <c r="L122" s="8" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="M122" s="8" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr">
         <is>
-          <t>Apply a random sticker to a random top card in this column</t>
+          <t>Apply a random sticker to every top card in this column</t>
         </is>
       </c>
       <c r="O122" s="9" t="inlineStr">
         <is>
-          <t>randomSticker</t>
+          <t>linkSticker</t>
         </is>
       </c>
       <c r="P122" s="8" t="inlineStr"/>
     </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>Same-Powers</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>Sticker Grant</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>every top in the column</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr"/>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t>Sticker Spray</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="inlineStr">
-        <is>
-          <t>linkSticker</t>
-        </is>
-      </c>
-      <c r="G123" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I123" s="8" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>Store Economy  (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Pillars</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>Store Economy</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>Purge ladder climbs slower</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr"/>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>Bulk Rate</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>bulkRate</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J123" s="8" t="inlineStr">
+      <c r="J125" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K123" s="8" t="inlineStr">
-        <is>
-          <t>stickersApplied</t>
-        </is>
-      </c>
-      <c r="L123" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M123" s="8" t="inlineStr"/>
-      <c r="N123" s="11" t="inlineStr">
-        <is>
-          <t>Apply a random sticker to every top card in this column</t>
-        </is>
-      </c>
-      <c r="O123" s="9" t="inlineStr">
-        <is>
-          <t>linkSticker</t>
-        </is>
-      </c>
-      <c r="P123" s="8" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="15" t="inlineStr">
-        <is>
-          <t>Store Economy  (6)</t>
-        </is>
-      </c>
+      <c r="K125" s="8" t="inlineStr">
+        <is>
+          <t>removalsUsed</t>
+        </is>
+      </c>
+      <c r="L125" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M125" s="8" t="inlineStr"/>
+      <c r="N125" s="11" t="inlineStr">
+        <is>
+          <t>The store's Purge price climbs by 1 instead of 2 (no effect during deal)</t>
+        </is>
+      </c>
+      <c r="O125" s="9" t="inlineStr">
+        <is>
+          <t>purgeStepDiscount</t>
+        </is>
+      </c>
+      <c r="P125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
@@ -16021,55 +16017,45 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Purge ladder climbs slower</t>
+          <t>one-time Purge halving on purchase</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr"/>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Bulk Rate</t>
+          <t>Flat Purge</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>bulkRate</t>
-        </is>
-      </c>
-      <c r="G126" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>purgeFlatFive</t>
+        </is>
+      </c>
+      <c r="G126" s="13" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H126" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J126" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K126" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L126" s="8" t="n">
-        <v>16</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J126" s="8" t="inlineStr"/>
+      <c r="K126" s="8" t="inlineStr"/>
+      <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="inlineStr"/>
       <c r="N126" s="11" t="inlineStr">
         <is>
-          <t>The store's Purge price climbs by 1 instead of 2. No effect during deal</t>
+          <t>On purchase → halve the store's Purge price (minimum 5, no effect during deal)</t>
         </is>
       </c>
       <c r="O126" s="9" t="inlineStr">
         <is>
-          <t>purgeStepDiscount</t>
+          <t>purgeHalve</t>
         </is>
       </c>
       <c r="P126" s="8" t="inlineStr"/>
@@ -16087,18 +16073,18 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>one-time Purge halving on purchase</t>
+          <t>one free shelf item</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr"/>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Flat Purge</t>
+          <t>Freebie</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>purgeFlatFive</t>
+          <t>freebie</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
@@ -16107,25 +16093,35 @@
         </is>
       </c>
       <c r="H127" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J127" s="8" t="inlineStr"/>
-      <c r="K127" s="8" t="inlineStr"/>
-      <c r="L127" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J127" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K127" s="8" t="inlineStr">
+        <is>
+          <t>pinkyTipsSeen</t>
+        </is>
+      </c>
+      <c r="L127" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="M127" s="8" t="inlineStr"/>
       <c r="N127" s="11" t="inlineStr">
         <is>
-          <t>On purchase → the store's Purge price is halved (minimum 5). No effect during deal</t>
+          <t>One random item in every store costs 0 (no effect during deal)</t>
         </is>
       </c>
       <c r="O127" s="9" t="inlineStr">
         <is>
-          <t>purgeHalve</t>
+          <t>freebie</t>
         </is>
       </c>
       <c r="P127" s="8" t="inlineStr"/>
@@ -16143,18 +16139,18 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>one free shelf item</t>
+          <t>first restock + reshuffle free</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr"/>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Freebie</t>
+          <t>On the House</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>freebie</t>
+          <t>firstFree</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
@@ -16163,35 +16159,25 @@
         </is>
       </c>
       <c r="H128" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J128" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K128" s="8" t="inlineStr">
-        <is>
-          <t>pinkyTipsSeen</t>
-        </is>
-      </c>
-      <c r="L128" s="8" t="n">
-        <v>2</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J128" s="8" t="inlineStr"/>
+      <c r="K128" s="8" t="inlineStr"/>
+      <c r="L128" s="8" t="n"/>
       <c r="M128" s="8" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr">
         <is>
-          <t>One random item in every store costs 0 coins. No effect during deal</t>
+          <t>First restock of each store and first reshuffle of each deal are free</t>
         </is>
       </c>
       <c r="O128" s="9" t="inlineStr">
         <is>
-          <t>freebie</t>
+          <t>firstFree</t>
         </is>
       </c>
       <c r="P128" s="8" t="inlineStr"/>
@@ -16209,18 +16195,18 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>first restock + reshuffle free</t>
+          <t>rares twice as often</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr"/>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>On the House</t>
+          <t>Rare Hunter</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>firstFree</t>
+          <t>rareHunter</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
@@ -16229,25 +16215,35 @@
         </is>
       </c>
       <c r="H129" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J129" s="8" t="inlineStr"/>
-      <c r="K129" s="8" t="inlineStr"/>
-      <c r="L129" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J129" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K129" s="8" t="inlineStr">
+        <is>
+          <t>pillarsPlaced</t>
+        </is>
+      </c>
+      <c r="L129" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="M129" s="8" t="inlineStr"/>
       <c r="N129" s="11" t="inlineStr">
         <is>
-          <t>The first restock in each store and the first reshuffle of each deal are free</t>
+          <t>Rare items appear in the store twice as often (no effect during deal)</t>
         </is>
       </c>
       <c r="O129" s="9" t="inlineStr">
         <is>
-          <t>firstFree</t>
+          <t>rareHunter</t>
         </is>
       </c>
       <c r="P129" s="8" t="inlineStr"/>
@@ -16255,7 +16251,7 @@
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>Pillars</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
@@ -16265,27 +16261,27 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>rares twice as often</t>
+          <t>cuts the Purge price</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr"/>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Rare Hunter</t>
+          <t>Purge Coupon</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>rareHunter</t>
-        </is>
-      </c>
-      <c r="G130" s="13" t="inlineStr">
-        <is>
-          <t>rare</t>
+          <t>purgeDiscount</t>
+        </is>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H130" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
@@ -16299,102 +16295,93 @@
       </c>
       <c r="K130" s="8" t="inlineStr">
         <is>
-          <t>pillarsPlaced</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L130" s="8" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="M130" s="8" t="inlineStr"/>
       <c r="N130" s="11" t="inlineStr">
         <is>
-          <t>Rare items appear in the store twice as often. No effect during deal</t>
+          <t>−1 to the store's Purge price per ♦-topped pile in this column (minimum 5)</t>
         </is>
       </c>
       <c r="O130" s="9" t="inlineStr">
         <is>
-          <t>rareHunter</t>
+          <t>purgeDiscount</t>
         </is>
       </c>
       <c r="P130" s="8" t="inlineStr"/>
     </row>
-    <row r="131">
-      <c r="A131" s="8" t="inlineStr">
-        <is>
-          <t>Bases</t>
-        </is>
-      </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>Store Economy</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr">
-        <is>
-          <t>cuts the Purge price</t>
-        </is>
-      </c>
-      <c r="D131" s="8" t="inlineStr"/>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t>Purge Coupon</t>
-        </is>
-      </c>
-      <c r="F131" s="9" t="inlineStr">
-        <is>
-          <t>purgeDiscount</t>
-        </is>
-      </c>
-      <c r="G131" s="12" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>Tell  (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>Tell</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>conditional: this pile, next draw</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr"/>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>Tell</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>tell</t>
+        </is>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="H131" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I131" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J131" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K131" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L131" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M131" s="8" t="inlineStr"/>
-      <c r="N131" s="11" t="inlineStr">
-        <is>
-          <t>Reduce the Store's Purge cost by 1 for each ♦-topped pile in this column. Minimum 5</t>
-        </is>
-      </c>
-      <c r="O131" s="9" t="inlineStr">
-        <is>
-          <t>purgeDiscount</t>
-        </is>
-      </c>
-      <c r="P131" s="8" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="15" t="inlineStr">
-        <is>
-          <t>Tell  (6)</t>
-        </is>
-      </c>
+      <c r="H133" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr"/>
+      <c r="K133" s="8" t="inlineStr"/>
+      <c r="L133" s="8" t="n"/>
+      <c r="M133" s="8" t="inlineStr"/>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>If another pile shows this suit → this card shows a tell (higher/lower/same)
+Otherwise → this becomes a curse</t>
+        </is>
+      </c>
+      <c r="O133" s="9" t="inlineStr">
+        <is>
+          <t>tell</t>
+        </is>
+      </c>
+      <c r="P133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
@@ -16404,27 +16391,27 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>conditional: this pile, next draw</t>
+          <t>on an 8</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr"/>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Tell</t>
+          <t>Eight Ball</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>tell</t>
-        </is>
-      </c>
-      <c r="G134" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>eightPeek</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H134" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
@@ -16437,13 +16424,12 @@
       <c r="M134" s="8" t="inlineStr"/>
       <c r="N134" s="11" t="inlineStr">
         <is>
-          <t>If another pile shows this suit → this card shows a tell (higher, lower, or same) for the next draw.
-Otherwise → this sticker becomes a curse</t>
+          <t>When an 8 lands in this column → tell on that card</t>
         </is>
       </c>
       <c r="O134" s="9" t="inlineStr">
         <is>
-          <t>tell</t>
+          <t>eightTell</t>
         </is>
       </c>
       <c r="P134" s="8" t="inlineStr"/>
@@ -16498,7 +16484,7 @@
       <c r="M135" s="8" t="inlineStr"/>
       <c r="N135" s="11" t="inlineStr">
         <is>
-          <t>While your purse holds under 10 coins → when a ♥ lands in this column, that pile gets a tell</t>
+          <t>If purse &lt;10 coins → when a ♥ lands in this column, that card gets a tell</t>
         </is>
       </c>
       <c r="O135" s="9" t="inlineStr">
@@ -16558,7 +16544,7 @@
       <c r="M136" s="8" t="inlineStr"/>
       <c r="N136" s="11" t="inlineStr">
         <is>
-          <t>While your purse holds under 10 coins → when a ♠ lands in this column, the next card shows a tell (higher/lower/same)</t>
+          <t>If purse &lt;10 coins → when a ♠ lands in this column, the next card shows a tell (higher/lower/same)</t>
         </is>
       </c>
       <c r="O136" s="9" t="inlineStr">
@@ -16624,7 +16610,7 @@
       <c r="M137" s="8" t="inlineStr"/>
       <c r="N137" s="11" t="inlineStr">
         <is>
-          <t>Put a tell marker on each ♣-topped pile in this column for the next draw. Tell marker shows if the next card is higher, lower, or same</t>
+          <t>Tell each ♣-topped pile in this column for the next draw (higher/lower/same)</t>
         </is>
       </c>
       <c r="O137" s="9" t="inlineStr">
@@ -16680,7 +16666,7 @@
       <c r="M138" s="8" t="inlineStr"/>
       <c r="N138" s="11" t="inlineStr">
         <is>
-          <t>If the next card is the SAME rank as a top card anywhere on the board, the = mark appears on that card</t>
+          <t>If the next card matches a top card's rank anywhere on the board → that card shows the = mark</t>
         </is>
       </c>
       <c r="O138" s="9" t="inlineStr">
@@ -16746,7 +16732,7 @@
       <c r="M139" s="8" t="inlineStr"/>
       <c r="N139" s="11" t="inlineStr">
         <is>
-          <t>Every alive pile shows a tell (higher/lower/same) for the next draw</t>
+          <t>Every alive pile gets a tell for the next draw (higher/lower/same)</t>
         </is>
       </c>
       <c r="O139" s="9" t="inlineStr">
@@ -16819,7 +16805,7 @@
       <c r="M142" s="8" t="inlineStr"/>
       <c r="N142" s="11" t="inlineStr">
         <is>
-          <t>Stickers that would convert into curses in this column don't — they stay as stickers</t>
+          <t>Stickers in this column never convert into curses</t>
         </is>
       </c>
       <c r="O142" s="9" t="inlineStr">
@@ -16875,7 +16861,7 @@
       <c r="M143" s="8" t="inlineStr"/>
       <c r="N143" s="11" t="inlineStr">
         <is>
-          <t>Remove all curses from the top cards in this column</t>
+          <t>Remove all curses from this column's top cards</t>
         </is>
       </c>
       <c r="O143" s="9" t="inlineStr">
@@ -16945,7 +16931,7 @@
       <c r="M144" s="8" t="inlineStr"/>
       <c r="N144" s="11" t="inlineStr">
         <is>
-          <t>When you call a correct Same → clear all curses from every top card on the board</t>
+          <t>Clear all curses from every top card on the board</t>
         </is>
       </c>
       <c r="O144" s="9" t="inlineStr">
@@ -17121,7 +17107,7 @@
       <c r="M151" s="8" t="inlineStr"/>
       <c r="N151" s="11" t="inlineStr">
         <is>
-          <t>Cursed. When it lands, the card at the BOTTOM of the pile returns to the deck</t>
+          <t>Cursed. On landing → the pile's bottom card returns to the deck</t>
         </is>
       </c>
       <c r="O151" s="9" t="inlineStr">
@@ -17236,7 +17222,7 @@
       <c r="M155" s="8" t="inlineStr"/>
       <c r="N155" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, the column's Pillar does not work</t>
+          <t>Cursed. While top card → the column's Pillar does not work</t>
         </is>
       </c>
       <c r="O155" s="9" t="inlineStr">
@@ -17290,7 +17276,7 @@
       <c r="M156" s="8" t="inlineStr"/>
       <c r="N156" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, your next guess must be played there</t>
+          <t>Cursed. While top card → your next guess must be played here</t>
         </is>
       </c>
       <c r="O156" s="9" t="inlineStr">
@@ -17344,7 +17330,7 @@
       <c r="M157" s="8" t="inlineStr"/>
       <c r="N157" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this is a pile's top card, Same cannot be called there</t>
+          <t>Cursed. While top card → Same cannot be called on this pile</t>
         </is>
       </c>
       <c r="O157" s="9" t="inlineStr">
@@ -17467,7 +17453,7 @@
       <c r="M161" s="8" t="inlineStr"/>
       <c r="N161" s="11" t="inlineStr">
         <is>
-          <t>Cursed. 10% chance this card kills the pile anyway, even if the guess is correct</t>
+          <t>Cursed. 10% chance to kill the pile even on a correct guess</t>
         </is>
       </c>
       <c r="O161" s="9" t="inlineStr">
@@ -17525,7 +17511,7 @@
       <c r="M162" s="8" t="inlineStr"/>
       <c r="N162" s="11" t="inlineStr">
         <is>
-          <t>Cursed. 10% chance the column's Base or Pillar is destroyed</t>
+          <t>Cursed. 10% chance to destroy the column's Base or Pillar</t>
         </is>
       </c>
       <c r="O162" s="9" t="inlineStr">
@@ -17586,7 +17572,7 @@
       <c r="M165" s="8" t="inlineStr"/>
       <c r="N165" s="11" t="inlineStr">
         <is>
-          <t>Cursed. While this card is a pile's top card, that pile size is 1</t>
+          <t>Cursed. While top card → this pile's size is 1</t>
         </is>
       </c>
       <c r="O165" s="9" t="inlineStr">
@@ -17640,7 +17626,7 @@
       <c r="M166" s="8" t="inlineStr"/>
       <c r="N166" s="11" t="inlineStr">
         <is>
-          <t>Cursed. This card counts −1 toward pile size</t>
+          <t>Cursed. Counts −1 toward pile size</t>
         </is>
       </c>
       <c r="O166" s="9" t="inlineStr">
@@ -17701,7 +17687,7 @@
       <c r="M169" s="8" t="inlineStr"/>
       <c r="N169" s="11" t="inlineStr">
         <is>
-          <t>Cursed. Any card that lands on this card loses its stickers</t>
+          <t>Cursed. A card landing on this card loses its stickers</t>
         </is>
       </c>
       <c r="O169" s="9" t="inlineStr">
@@ -17717,23 +17703,23 @@
     <mergeCell ref="A14:P14"/>
     <mergeCell ref="A141:P141"/>
     <mergeCell ref="A150:P150"/>
-    <mergeCell ref="A91:P91"/>
     <mergeCell ref="A62:P62"/>
-    <mergeCell ref="A125:P125"/>
     <mergeCell ref="A68:P68"/>
-    <mergeCell ref="A114:P114"/>
-    <mergeCell ref="A83:P83"/>
     <mergeCell ref="A30:P30"/>
+    <mergeCell ref="A82:P82"/>
+    <mergeCell ref="A107:P107"/>
+    <mergeCell ref="A132:P132"/>
     <mergeCell ref="A146:P146"/>
     <mergeCell ref="A168:P168"/>
+    <mergeCell ref="A119:P119"/>
+    <mergeCell ref="A124:P124"/>
     <mergeCell ref="A153:P153"/>
+    <mergeCell ref="A90:P90"/>
     <mergeCell ref="A164:P164"/>
     <mergeCell ref="A46:P46"/>
-    <mergeCell ref="A133:P133"/>
-    <mergeCell ref="A108:P108"/>
     <mergeCell ref="A56:P56"/>
-    <mergeCell ref="A120:P120"/>
     <mergeCell ref="A50:P50"/>
+    <mergeCell ref="A113:P113"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v6.98)</t>
+          <t>NINELIVES — item pool (v6.99)</t>
         </is>
       </c>
     </row>
@@ -5251,27 +5251,27 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Bury</t>
+          <t>Pile Size &amp; Score</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>while broke</t>
+          <t>♦ while broke; flat broke may purge</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Pauper</t>
+          <t>Pauper, Deck Removal</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Pauper's Club</t>
+          <t>Pauper's Diamond</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>pauperClub</t>
+          <t>pauperDiamondEqualize</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -5293,13 +5293,13 @@
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr">
         <is>
-          <t>If purse &lt;10 coins → when a ♣ lands in this column bury 1
-If 0 coins → bury 3</t>
+          <t>If purse &lt;10 coins → when a ♦ lands in this column make all piles the same size
+If 0 coins → optionally purge the top card of any pile board-wide</t>
         </is>
       </c>
       <c r="O56" s="9" t="inlineStr">
         <is>
-          <t>pauperClubBury</t>
+          <t>pauperDiamondEqualize</t>
         </is>
       </c>
       <c r="P56" s="8" t="inlineStr"/>
@@ -5312,27 +5312,27 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Pile Size &amp; Score</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>♦ while broke; flat broke may purge</t>
+          <t>while broke</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Pauper, Deck Removal</t>
+          <t>Pauper</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Pauper's Diamond</t>
+          <t>Pauper's Fattening</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>pauperDiamondEqualize</t>
+          <t>pauperClub</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -5354,13 +5354,13 @@
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>If purse &lt;10 coins → when a ♦ lands in this column make all piles the same size
-If 0 coins → optionally purge the top card of any pile board-wide</t>
+          <t>If purse &lt;10 coins → when a ♣ lands in this column bury 1
+If 0 coins → bury 3</t>
         </is>
       </c>
       <c r="O57" s="9" t="inlineStr">
         <is>
-          <t>pauperDiamondEqualize</t>
+          <t>pauperClubBury</t>
         </is>
       </c>
       <c r="P57" s="8" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
       <c r="M67" s="8" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>A royal landing on a royal survives a Same call in this column — a survived Same counts as a full correct Same (charges the Same Shield, fires your Same-Power)</t>
+          <t>A royal landing on a royal survives a Same call in this column</t>
         </is>
       </c>
       <c r="O67" s="9" t="inlineStr">
@@ -6289,7 +6289,7 @@
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → optionally shuffle this column's other piles</t>
+          <t>When a ♦ lands in this column → optionally shuffle this column's piles</t>
         </is>
       </c>
       <c r="O72" s="9" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Pauper's Club</t>
+          <t>Pauper's Fattening</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -15473,7 +15473,7 @@
       <c r="M103" s="8" t="inlineStr"/>
       <c r="N103" s="11" t="inlineStr">
         <is>
-          <t>A royal landing on a royal survives a Same call in this column — a survived Same counts as a full correct Same (charges the Same Shield, fires your Same-Power)</t>
+          <t>A royal landing on a royal survives a Same call in this column</t>
         </is>
       </c>
       <c r="O103" s="9" t="inlineStr">
@@ -16302,7 +16302,7 @@
       <c r="M120" s="8" t="inlineStr"/>
       <c r="N120" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → optionally shuffle this column's other piles</t>
+          <t>When a ♦ lands in this column → optionally shuffle this column's piles</t>
         </is>
       </c>
       <c r="O120" s="9" t="inlineStr">

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v7.01)</t>
+          <t>NINELIVES — item pool (v7.02)</t>
         </is>
       </c>
     </row>

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v7.02)</t>
+          <t>NINELIVES — item pool (v7.03)</t>
         </is>
       </c>
     </row>

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v7.03)</t>
+          <t>NINELIVES — item pool (v7.04)</t>
         </is>
       </c>
     </row>
@@ -5620,27 +5620,23 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Deck Removal</t>
+          <t>Safety &amp; Saves</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>a whole rank, at purchase</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Deck Shaping</t>
-        </is>
-      </c>
+          <t>deck's commonest rank</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr"/>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Rank Purge</t>
+          <t>Rank Shield</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>purgeRank</t>
+          <t>rankShield</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -5662,12 +5658,12 @@
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="11" t="inlineStr">
         <is>
-          <t>On purchase → purge every {rank} from your deck (no effect during deal)</t>
+          <t>The most common rank in your full deck ({rank}) is always safe in this column</t>
         </is>
       </c>
       <c r="O62" s="9" t="inlineStr">
         <is>
-          <t>purgeRank</t>
+          <t>rankShield</t>
         </is>
       </c>
       <c r="P62" s="13" t="inlineStr">
@@ -5684,23 +5680,23 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Safety &amp; Saves</t>
+          <t>Store Economy</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>deck's commonest rank</t>
+          <t>rares twice as often</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr"/>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Rank Shield</t>
+          <t>Rare Hunter</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>rankShield</t>
+          <t>rareHunter</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -5713,28 +5709,34 @@
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr"/>
-      <c r="L63" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>pillarsPlaced</t>
+        </is>
+      </c>
+      <c r="L63" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>The most common rank in your full deck ({rank}) is always safe in this column</t>
+          <t>Rare items appear in the store twice as often (no effect during deal)</t>
         </is>
       </c>
       <c r="O63" s="9" t="inlineStr">
         <is>
-          <t>rankShield</t>
-        </is>
-      </c>
-      <c r="P63" s="13" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+          <t>rareHunter</t>
+        </is>
+      </c>
+      <c r="P63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -5744,23 +5746,23 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Store Economy</t>
+          <t>Safety &amp; Saves</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>rares twice as often</t>
+          <t>revive a dead pile</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr"/>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Rare Hunter</t>
+          <t>Revive</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>rareHunter</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -5778,26 +5780,26 @@
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>pillarsPlaced</t>
+          <t>dealsWonLegendary</t>
         </is>
       </c>
       <c r="L64" s="8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>Rare items appear in the store twice as often (no effect during deal)</t>
+          <t>When a pile in this column reaches 10 cards → revive one dead pile</t>
         </is>
       </c>
       <c r="O64" s="9" t="inlineStr">
         <is>
-          <t>rareHunter</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="P64" s="8" t="inlineStr"/>
@@ -5815,18 +5817,22 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>revive a dead pile</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Revive</t>
+          <t>Royal Pair</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>sameTolRoyal</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -5844,26 +5850,26 @@
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>dealsWonLegendary</t>
+          <t>samesCalled</t>
         </is>
       </c>
       <c r="L65" s="8" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="M65" s="8" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>When a pile in this column reaches 10 cards → revive one dead pile</t>
+          <t>A royal landing on a royal survives a Same call in this column</t>
         </is>
       </c>
       <c r="O65" s="9" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P65" s="8" t="inlineStr"/>
@@ -5881,22 +5887,18 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>royals, if no 2s in deck</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr"/>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Royal Pair</t>
+          <t>Royal Sanctuary</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>sameTolRoyal</t>
+          <t>royalSanctuary</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -5919,21 +5921,21 @@
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L66" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr">
         <is>
-          <t>A royal landing on a royal survives a Same call in this column</t>
+          <t>If your full deck has no 2s → royals (J/Q/K) are always safe in this column</t>
         </is>
       </c>
       <c r="O66" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>royalSafeNoTwos</t>
         </is>
       </c>
       <c r="P66" s="8" t="inlineStr"/>
@@ -5951,18 +5953,22 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>royals, if no 2s in deck</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr"/>
+          <t>relaxes what survives a Same</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Same Shield &amp; Power</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Royal Sanctuary</t>
+          <t>Same Suit Safe</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>royalSanctuary</t>
+          <t>sameTolSuit</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -5975,31 +5981,21 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K67" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L67" s="8" t="n">
-        <v>30</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr"/>
+      <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>If your full deck has no 2s → royals (J/Q/K) are always safe in this column</t>
+          <t>A card landing on its own suit is safe in this column</t>
         </is>
       </c>
       <c r="O67" s="9" t="inlineStr">
         <is>
-          <t>royalSafeNoTwos</t>
+          <t>sameTolerance</t>
         </is>
       </c>
       <c r="P67" s="8" t="inlineStr"/>
@@ -6017,22 +6013,18 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>relaxes what survives a Same</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Same Shield &amp; Power</t>
-        </is>
-      </c>
+          <t>deck's scarcest suit</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr"/>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Same Suit Safe</t>
+          <t>Scarce Suit</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>sameTolSuit</t>
+          <t>suitShield</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -6054,12 +6046,12 @@
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="11" t="inlineStr">
         <is>
-          <t>A card landing on its own suit is safe in this column</t>
+          <t>The suit your full deck holds the fewest of is safe when it lands in this column</t>
         </is>
       </c>
       <c r="O68" s="9" t="inlineStr">
         <is>
-          <t>sameTolerance</t>
+          <t>suitShieldDaily</t>
         </is>
       </c>
       <c r="P68" s="8" t="inlineStr"/>
@@ -6077,18 +6069,18 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>deck's scarcest suit</t>
+          <t>chance to save a dying pile</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Scarce Suit</t>
+          <t>Second Wind</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>suitShield</t>
+          <t>secondWind</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -6110,12 +6102,12 @@
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>The suit your full deck holds the fewest of is safe when it lands in this column</t>
+          <t>When a pile in this column dies → 25% chance to save it: the top card stays, the buried cards shuffle back into the deck</t>
         </is>
       </c>
       <c r="O69" s="9" t="inlineStr">
         <is>
-          <t>suitShieldDaily</t>
+          <t>secondWind</t>
         </is>
       </c>
       <c r="P69" s="8" t="inlineStr"/>
@@ -6128,23 +6120,23 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Safety &amp; Saves</t>
+          <t>Shuffle</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>chance to save a dying pile</t>
+          <t>column, on a ♦</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr"/>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Second Wind</t>
+          <t>Shuffler</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>secondWind</t>
+          <t>royalCourt</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -6166,12 +6158,12 @@
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>When a pile in this column dies → 25% chance to save it: the top card stays, the buried cards shuffle back into the deck</t>
+          <t>When a ♦ lands in this column → optionally shuffle this column's piles</t>
         </is>
       </c>
       <c r="O70" s="9" t="inlineStr">
         <is>
-          <t>secondWind</t>
+          <t>shuffler</t>
         </is>
       </c>
       <c r="P70" s="8" t="inlineStr"/>
@@ -6184,23 +6176,23 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Shuffle</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>column, on a ♦</t>
+          <t>streak-gated</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr"/>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Shuffler</t>
+          <t>Streak Bury</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>royalCourt</t>
+          <t>streakTribute</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -6213,21 +6205,31 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J71" s="8" t="inlineStr"/>
-      <c r="K71" s="8" t="inlineStr"/>
-      <c r="L71" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>cardsBuried</t>
+        </is>
+      </c>
+      <c r="L71" s="8" t="n">
+        <v>90</v>
+      </c>
       <c r="M71" s="8" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>When a ♦ lands in this column → optionally shuffle this column's piles</t>
+          <t>From the 4th consecutive correct guess in this column → bury 1 card per guess — resets on a wrong guess or a guess in another column</t>
         </is>
       </c>
       <c r="O71" s="9" t="inlineStr">
         <is>
-          <t>shuffler</t>
+          <t>streakTribute</t>
         </is>
       </c>
       <c r="P71" s="8" t="inlineStr"/>
@@ -6240,23 +6242,23 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Bury</t>
+          <t>Coin Gain</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>streak-gated</t>
+          <t>streak-grown</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr"/>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Streak Bury</t>
+          <t>Streak Coin</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>streakTribute</t>
+          <t>streakCoin</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
@@ -6269,31 +6271,22 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J72" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K72" s="8" t="inlineStr">
-        <is>
-          <t>cardsBuried</t>
-        </is>
-      </c>
-      <c r="L72" s="8" t="n">
-        <v>90</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr"/>
+      <c r="K72" s="8" t="inlineStr"/>
+      <c r="L72" s="8" t="n"/>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>From the 4th consecutive correct guess in this column → bury 1 card per guess — resets on a wrong guess or a guess in another column</t>
+          <t>From the 4th consecutive correct guess in this column → +1 coin per guess
+Resets on a wrong guess or a guess in another column</t>
         </is>
       </c>
       <c r="O72" s="9" t="inlineStr">
         <is>
-          <t>streakTribute</t>
+          <t>streakCoin</t>
         </is>
       </c>
       <c r="P72" s="8" t="inlineStr"/>
@@ -6306,23 +6299,23 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Coin Gain</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>streak-grown</t>
+          <t>on the locked rank</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr"/>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Streak Coin</t>
+          <t>Underdog</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>streakCoin</t>
+          <t>underdog</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -6335,25 +6328,38 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr"/>
-      <c r="K73" s="8" t="inlineStr"/>
-      <c r="L73" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="inlineStr">
+        <is>
+          <t>cardsBuried</t>
+        </is>
+      </c>
+      <c r="L73" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="M73" s="8" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>From the 4th consecutive correct guess in this column → +1 coin per guess
-Resets on a wrong guess or a guess in another column</t>
+          <t>When a {rank} lands in this column → bury 1 card under that pile</t>
         </is>
       </c>
       <c r="O73" s="9" t="inlineStr">
         <is>
-          <t>streakCoin</t>
-        </is>
-      </c>
-      <c r="P73" s="8" t="inlineStr"/>
+          <t>rankBury</t>
+        </is>
+      </c>
+      <c r="P73" s="13" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -6363,23 +6369,23 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Bury</t>
+          <t>Safety &amp; Saves</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>on the locked rank</t>
+          <t>aces high or low</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr"/>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Underdog</t>
+          <t>Wild Aces</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>underdog</t>
+          <t>wildAces</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -6402,28 +6408,24 @@
       </c>
       <c r="K74" s="8" t="inlineStr">
         <is>
-          <t>cardsBuried</t>
+          <t>jokersPlayed</t>
         </is>
       </c>
       <c r="L74" s="8" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>When a {rank} lands in this column → bury 1 card under that pile</t>
+          <t>Aces count as high or low in this column</t>
         </is>
       </c>
       <c r="O74" s="9" t="inlineStr">
         <is>
-          <t>rankBury</t>
-        </is>
-      </c>
-      <c r="P74" s="13" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+          <t>wildAces</t>
+        </is>
+      </c>
+      <c r="P74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -6433,28 +6435,32 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Safety &amp; Saves</t>
+          <t>Tell</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>aces high or low</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr"/>
+          <t>most-held rank</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Deck Shaping</t>
+        </is>
+      </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Wild Aces</t>
+          <t>Most-Held Tell</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>wildAces</t>
-        </is>
-      </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>mostHeldRankTell</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
@@ -6472,24 +6478,28 @@
       </c>
       <c r="K75" s="8" t="inlineStr">
         <is>
-          <t>jokersPlayed</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L75" s="8" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="M75" s="8" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>Aces count as high or low in this column</t>
+          <t>When your most-held rank ({rank}) lands in this column → it shows a tell</t>
         </is>
       </c>
       <c r="O75" s="9" t="inlineStr">
         <is>
-          <t>wildAces</t>
-        </is>
-      </c>
-      <c r="P75" s="8" t="inlineStr"/>
+          <t>mostHeldRankTell</t>
+        </is>
+      </c>
+      <c r="P75" s="13" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -6499,12 +6509,12 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Tell</t>
+          <t>Deck Removal</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>most-held rank</t>
+          <t>a whole rank, at purchase</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -6514,12 +6524,12 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Most-Held Tell</t>
+          <t>Rank Purge</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>mostHeldRankTell</t>
+          <t>purgeRank</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6532,31 +6542,21 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K76" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L76" s="8" t="n">
-        <v>25</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J76" s="8" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr"/>
+      <c r="L76" s="8" t="n"/>
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>When your most-held rank ({rank}) lands in this column → it shows a tell</t>
+          <t>On purchase → purge every {rank} from your deck (no effect during deal)</t>
         </is>
       </c>
       <c r="O76" s="9" t="inlineStr">
         <is>
-          <t>mostHeldRankTell</t>
+          <t>purgeRank</t>
         </is>
       </c>
       <c r="P76" s="13" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>per missing rank, every alive pile</t>
+          <t>per pile, its top's missing-neighbour ranks</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -7603,7 +7603,7 @@
       <c r="M92" s="8" t="inlineStr"/>
       <c r="N92" s="11" t="inlineStr">
         <is>
-          <t>Bury 1 card under each pile per rank missing from your full deck</t>
+          <t>For each pile in this column → bury 1 card per neighbor rank of its top card missing from your full deck</t>
         </is>
       </c>
       <c r="O92" s="9" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>per missing rank, every alive pile</t>
+          <t>per pile, its top's missing-neighbour ranks</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -10807,7 +10807,7 @@
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Bury 1 card under each pile per rank missing from your full deck</t>
+          <t>For each pile in this column → bury 1 card per neighbor rank of its top card missing from your full deck</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
@@ -13026,9 +13026,9 @@
           <t>purgeRank</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>rare</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v7.04)</t>
+          <t>NINELIVES — item pool (v7.05)</t>
         </is>
       </c>
     </row>
@@ -5127,10 +5127,14 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>first restock + reshuffle free</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr"/>
+          <t>first restock + reshuffle free; +coins at deal end</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Coin Gain</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
           <t>On the House</t>
@@ -5160,7 +5164,7 @@
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="11" t="inlineStr">
         <is>
-          <t>First restock of each store and first reshuffle of each deal are free</t>
+          <t>First restock of each store and first reshuffle of each deal are free. +2 coins at end of deal</t>
         </is>
       </c>
       <c r="O54" s="9" t="inlineStr">
@@ -16966,10 +16970,14 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>first restock + reshuffle free</t>
-        </is>
-      </c>
-      <c r="D134" s="8" t="inlineStr"/>
+          <t>first restock + reshuffle free; +coins at deal end</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>Coin Gain</t>
+        </is>
+      </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
           <t>On the House</t>
@@ -16999,7 +17007,7 @@
       <c r="M134" s="8" t="inlineStr"/>
       <c r="N134" s="11" t="inlineStr">
         <is>
-          <t>First restock of each store and first reshuffle of each deal are free</t>
+          <t>First restock of each store and first reshuffle of each deal are free. +2 coins at end of deal</t>
         </is>
       </c>
       <c r="O134" s="9" t="inlineStr">

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v7.05)</t>
+          <t>NINELIVES — item pool (v7.06)</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>needs an empty Same-Power slot</t>
+          <t>peek the next card</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr"/>
@@ -7537,7 +7537,7 @@
       <c r="M91" s="8" t="inlineStr"/>
       <c r="N91" s="11" t="inlineStr">
         <is>
-          <t>If no Same-Power is equipped → peek next card</t>
+          <t>Peek the next card</t>
         </is>
       </c>
       <c r="O91" s="9" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>needs an empty Same-Power slot</t>
+          <t>peek the next card</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr"/>
@@ -14385,7 +14385,7 @@
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>If no Same-Power is equipped → peek next card</t>
+          <t>Peek the next card</t>
         </is>
       </c>
       <c r="O81" s="9" t="inlineStr">

--- a/item-list.xlsx
+++ b/item-list.xlsx
@@ -553,7 +553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NINELIVES — item pool (v7.08)</t>
+          <t>NINELIVES — item pool (v7.09)</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>sticker-heavy ♣</t>
+          <t>2+ stickers, any suit</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
@@ -3987,7 +3987,7 @@
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>When a ♣ with 3+ stickers lands correctly in this column → bury 1 card under that pile</t>
+          <t>When a card with 2+ stickers lands correctly in this column → bury 1 card under that pile</t>
         </is>
       </c>
       <c r="O36" s="9" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>rares twice as often; +1 per stickered landing</t>
+          <t>rares twice as often; deal-end +1 per sticker bought this climb</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
@@ -5886,7 +5886,7 @@
       <c r="N65" s="11" t="inlineStr">
         <is>
           <t>Rare items appear in the store twice as often
-When a stickered card lands in this column → +1 coin</t>
+At deal end → +1 coin per sticker bought in the shop this climb</t>
         </is>
       </c>
       <c r="O65" s="9" t="inlineStr">
@@ -6723,17 +6723,17 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Peek</t>
+          <t>Bury</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>trades the deal's banked bonus</t>
+          <t>1 per 3 bonus coins, then peek; the bonus resets</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Coin Loss</t>
+          <t>Peek, Coin Loss</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -6775,7 +6775,7 @@
       <c r="M79" s="8" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>Reset bonus coins earned this deal to 0 → peek next card</t>
+          <t>Bury 1 card per 3 bonus coins earned this deal, spread across this column's piles → peek next card. Bonus coins earned this deal reset to 0</t>
         </is>
       </c>
       <c r="O79" s="9" t="inlineStr">
@@ -10243,7 +10243,7 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Bury  (13)</t>
+          <t>Bury  (14)</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>sticker-heavy ♣</t>
+          <t>2+ stickers, any suit</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
@@ -10487,7 +10487,7 @@
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>When a ♣ with 3+ stickers lands correctly in this column → bury 1 card under that pile</t>
+          <t>When a card with 2+ stickers lands correctly in this column → bury 1 card under that pile</t>
         </is>
       </c>
       <c r="O6" s="9" t="inlineStr">
@@ -10851,18 +10851,22 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>under each ♣ top</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
+          <t>1 per 3 bonus coins, then peek; the bonus resets</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Peek, Coin Loss</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Club Dig</t>
+          <t>Bonus Reset</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>clubDig</t>
+          <t>bonusResetPeek</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -10880,26 +10884,26 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>clubsPlayed</t>
+          <t>coinsEarnedLifetime</t>
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Bury 1 card under each ♣-topped pile in this column</t>
+          <t>Bury 1 card per 3 bonus coins earned this deal, spread across this column's piles → peek next card. Bonus coins earned this deal reset to 0</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
         <is>
-          <t>suitDig</t>
+          <t>bonusResetPeek</t>
         </is>
       </c>
       <c r="P12" s="8" t="inlineStr"/>
@@ -10917,22 +10921,18 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>per pile, its top's missing-neighbour ranks</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Deck Shaping</t>
-        </is>
-      </c>
+          <t>under each ♣ top</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr"/>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Missing Rank Dig</t>
+          <t>Club Dig</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>missingRankDig</t>
+          <t>clubDig</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -10955,21 +10955,21 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>removalsUsed</t>
+          <t>clubsPlayed</t>
         </is>
       </c>
       <c r="L13" s="8" t="n">
-        <v>35</v>
+        <v>250</v>
       </c>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>For each pile in this column → bury 1 card per neighbor rank of its top card missing from your full deck</t>
+          <t>Bury 1 card under each ♣-topped pile in this column</t>
         </is>
       </c>
       <c r="O13" s="9" t="inlineStr">
         <is>
-          <t>missingRankDig</t>
+          <t>suitDig</t>
         </is>
       </c>
       <c r="P13" s="8" t="inlineStr"/>
@@ -10987,22 +10987,22 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>peels stickers to bury</t>
+          <t>per pile, its top's missing-neighbour ranks</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Sticker Removal</t>
+          <t>Deck Shaping</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Sticker Harvest</t>
+          <t>Missing Rank Dig</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>stickerHarvest</t>
+          <t>missingRankDig</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -11025,21 +11025,21 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>stickersApplied</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>Choose a pile → bury 2 cards per sticker on its top card, then peel all those stickers</t>
+          <t>For each pile in this column → bury 1 card per neighbor rank of its top card missing from your full deck</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>stickerHarvest</t>
+          <t>missingRankDig</t>
         </is>
       </c>
       <c r="P14" s="8" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Same-Powers</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -11057,18 +11057,22 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>under every pile (experiment)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr"/>
+          <t>peels stickers to bury</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Sticker Removal</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Burrow</t>
+          <t>Sticker Harvest</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>linkBury</t>
+          <t>stickerHarvest</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -11077,7 +11081,7 @@
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
@@ -11091,87 +11095,97 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>stickersApplied</t>
         </is>
       </c>
       <c r="L15" s="8" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
+          <t>Choose a pile → bury 2 cards per sticker on its top card, then peel all those stickers</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>stickerHarvest</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Same-Powers</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Bury</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>under every pile (experiment)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Burrow</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>linkBury</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>samesCalled</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="M16" s="8" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
           <t>Bury 1 card under every pile</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O16" s="9" t="inlineStr">
         <is>
           <t>linkBury</t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="P16" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Card Change  (14)</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Stickers</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Card Change</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>rank ±</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>+1 Rank</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>rankUp</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="inlineStr"/>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>+1 rank (stops at Ace)</t>
-        </is>
-      </c>
-      <c r="O18" s="9" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -11192,44 +11206,34 @@
       <c r="D19" s="8" t="inlineStr"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>+2 Rank</t>
+          <t>+1 Rank</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>rankUp2</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>rankUp</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>dealsWonRegular</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>4</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>+2 rank (stops at Ace)</t>
+          <t>+1 rank (stops at Ace)</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
@@ -11252,45 +11256,55 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>suit, chosen</t>
+          <t>rank ±</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr"/>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Change to ♠</t>
+          <t>+2 Rank</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>changeSuitSpade</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>rankUp2</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>dealsWonRegular</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>Change to ♠</t>
+          <t>+2 rank (stops at Ace)</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
         <is>
-          <t>changeSuitTo</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="P20" s="8" t="inlineStr"/>
@@ -11314,12 +11328,12 @@
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Change to ♣</t>
+          <t>Change to ♠</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>changeSuitClub</t>
+          <t>changeSuitSpade</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -11341,7 +11355,7 @@
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>Change to ♣</t>
+          <t>Change to ♠</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
@@ -11370,12 +11384,12 @@
       <c r="D22" s="8" t="inlineStr"/>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Change to ♥</t>
+          <t>Change to ♣</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>changeSuitHeart</t>
+          <t>changeSuitClub</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -11397,7 +11411,7 @@
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Change to ♥</t>
+          <t>Change to ♣</t>
         </is>
       </c>
       <c r="O22" s="9" t="inlineStr">
@@ -11426,12 +11440,12 @@
       <c r="D23" s="8" t="inlineStr"/>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Change to ♦</t>
+          <t>Change to ♥</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>changeSuitDiamond</t>
+          <t>changeSuitHeart</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -11453,7 +11467,7 @@
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>Change to ♦</t>
+          <t>Change to ♥</t>
         </is>
       </c>
       <c r="O23" s="9" t="inlineStr">
@@ -11476,18 +11490,18 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>rank, random</t>
+          <t>suit, chosen</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Random Rank</t>
+          <t>Change to ♦</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>randomFixedValue</t>
+          <t>changeSuitDiamond</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -11500,31 +11514,21 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>runsPlayed</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>3</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr"/>
+      <c r="K24" s="8" t="inlineStr"/>
+      <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>Randomize rank</t>
+          <t>Change to ♦</t>
         </is>
       </c>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>randomFixedValue</t>
+          <t>changeSuitTo</t>
         </is>
       </c>
       <c r="P24" s="8" t="inlineStr"/>
@@ -11542,18 +11546,18 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>suit, random</t>
+          <t>rank, random</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Random Suit</t>
+          <t>Random Rank</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>changeSuitRandom</t>
+          <t>randomFixedValue</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -11566,21 +11570,31 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>runsPlayed</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Randomize suit</t>
+          <t>Randomize rank</t>
         </is>
       </c>
       <c r="O25" s="9" t="inlineStr">
         <is>
-          <t>changeSuitRandom</t>
+          <t>randomFixedValue</t>
         </is>
       </c>
       <c r="P25" s="8" t="inlineStr"/>
@@ -11598,18 +11612,18 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>rank ±</t>
+          <t>suit, random</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>−1 Rank</t>
+          <t>Random Suit</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>rankDown</t>
+          <t>changeSuitRandom</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -11631,12 +11645,12 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>-1 rank (stops at 2)</t>
+          <t>Randomize suit</t>
         </is>
       </c>
       <c r="O26" s="9" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>changeSuitRandom</t>
         </is>
       </c>
       <c r="P26" s="8" t="inlineStr"/>
@@ -11660,44 +11674,34 @@
       <c r="D27" s="8" t="inlineStr"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>−2 Rank</t>
+          <t>−1 Rank</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>rankDown2</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>rankDown</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>dealsSurvived</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>12</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
+      <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>-2 rank (stops at 2)</t>
+          <t>-1 rank (stops at 2)</t>
         </is>
       </c>
       <c r="O27" s="9" t="inlineStr">
@@ -11710,7 +11714,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Stickers</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -11720,18 +11724,18 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>column tops → deck's commonest rank</t>
+          <t>rank ±</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Chorus</t>
+          <t>−2 Rank</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>chorus</t>
+          <t>rankDown2</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -11740,7 +11744,7 @@
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
@@ -11754,28 +11758,24 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>bestCampaignScore</t>
+          <t>dealsSurvived</t>
         </is>
       </c>
       <c r="L28" s="8" t="n">
-        <v>160</v>
+        <v>12</v>
       </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Set every top card in this column to {rank}</t>
+          <t>-2 rank (stops at 2)</t>
         </is>
       </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
-          <t>chorus</t>
-        </is>
-      </c>
-      <c r="P28" s="13" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -11790,18 +11790,18 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>column tops → one rank</t>
+          <t>column tops → deck's commonest rank</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr"/>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Rank Setter</t>
+          <t>Chorus</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>setValue</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -11824,24 +11824,28 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>runsWon</t>
+          <t>bestCampaignScore</t>
         </is>
       </c>
       <c r="L29" s="8" t="n">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="M29" s="8" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Permanently set this column's top cards to the bottom pile's rank</t>
+          <t>Set every top card in this column to {rank}</t>
         </is>
       </c>
       <c r="O29" s="9" t="inlineStr">
         <is>
-          <t>setValue</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="inlineStr"/>
+          <t>chorus</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -11856,18 +11860,18 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>column tops → one suit</t>
+          <t>column tops → one rank</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Suit Setter</t>
+          <t>Rank Setter</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>setSuit</t>
+          <t>setValue</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -11894,17 +11898,17 @@
         </is>
       </c>
       <c r="L30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Permanently set this column's top cards to the bottom pile's suit</t>
+          <t>Permanently set this column's top cards to the bottom pile's rank</t>
         </is>
       </c>
       <c r="O30" s="9" t="inlineStr">
         <is>
-          <t>setSuit</t>
+          <t>setValue</t>
         </is>
       </c>
       <c r="P30" s="8" t="inlineStr"/>
@@ -11912,7 +11916,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Same-Powers</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -11922,18 +11926,18 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>every alive top → the called rank</t>
+          <t>column tops → one suit</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Rank Flood</t>
+          <t>Suit Setter</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>rankFlood</t>
+          <t>setSuit</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -11942,7 +11946,7 @@
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
@@ -11951,156 +11955,156 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>samesCalled</t>
+          <t>runsWon</t>
         </is>
       </c>
       <c r="L31" s="8" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
+          <t>Permanently set this column's top cards to the bottom pile's suit</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>setSuit</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Same-Powers</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Card Change</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>every alive top → the called rank</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Rank Flood</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>rankFlood</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>samesCalled</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="M32" s="8" t="inlineStr"/>
+      <c r="N32" s="11" t="inlineStr">
+        <is>
           <t>Set the top card of every alive pile to this card's rank — a Joker on either side ranks them by the ranked card; Joker-on-Joker makes Aces</t>
         </is>
       </c>
-      <c r="O31" s="9" t="inlineStr">
+      <c r="O32" s="9" t="inlineStr">
         <is>
           <t>rankFlood</t>
         </is>
       </c>
-      <c r="P31" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="P32" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Coin Gain  (16)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Stickers</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Coin Gain</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>flat +1; curse on kill</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Bonus Coin</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>gainCoin</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n">
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr"/>
-      <c r="K34" s="8" t="inlineStr"/>
-      <c r="L34" s="8" t="n"/>
-      <c r="M34" s="8" t="inlineStr"/>
-      <c r="N34" s="11" t="inlineStr">
+      <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="8" t="inlineStr"/>
+      <c r="N35" s="11" t="inlineStr">
         <is>
           <t>+1 coin
 If this card kills its pile → this becomes a curse</t>
         </is>
       </c>
-      <c r="O34" s="9" t="inlineStr">
+      <c r="O35" s="9" t="inlineStr">
         <is>
           <t>gainCoin</t>
-        </is>
-      </c>
-      <c r="P34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Stickers</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Coin Gain</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>deal-end payout</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>Payout</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>extraCoin</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>perfectDeals</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="8" t="inlineStr"/>
-      <c r="N35" s="11" t="inlineStr">
-        <is>
-          <t>At deal end if top card → earn coins equal to pile size</t>
-        </is>
-      </c>
-      <c r="O35" s="9" t="inlineStr">
-        <is>
-          <t>extraCoin</t>
         </is>
       </c>
       <c r="P35" s="8" t="inlineStr"/>
@@ -12118,18 +12122,18 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>per-card growth; curse on kill</t>
+          <t>deal-end payout</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Snowball Coins</t>
+          <t>Payout</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>snowballCoins</t>
+          <t>extraCoin</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -12156,91 +12160,87 @@
         </is>
       </c>
       <c r="L36" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr">
         <is>
+          <t>At deal end if top card → earn coins equal to pile size</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="inlineStr">
+        <is>
+          <t>extraCoin</t>
+        </is>
+      </c>
+      <c r="P36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Coin Gain</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>per-card growth; curse on kill</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Snowball Coins</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>snowballCoins</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>perfectDeals</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" s="8" t="inlineStr"/>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
           <t>+X coins, X = times this card has landed correctly
 If this card kills its pile → this becomes a curse</t>
         </is>
       </c>
-      <c r="O36" s="9" t="inlineStr">
+      <c r="O37" s="9" t="inlineStr">
         <is>
           <t>snowballCoins</t>
         </is>
       </c>
-      <c r="P36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Pillars</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Coin Gain</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>on the locked rank</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>Crowd Favorite</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>crowdFavorite</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>dealsSurvived</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="M37" s="8" t="inlineStr"/>
-      <c r="N37" s="11" t="inlineStr">
-        <is>
-          <t>When a {rank} lands correctly in this column → +2 coins</t>
-        </is>
-      </c>
-      <c r="O37" s="9" t="inlineStr">
-        <is>
-          <t>rankCoin</t>
-        </is>
-      </c>
-      <c r="P37" s="13" t="inlineStr">
-        <is>
-          <t>TEMPLATE</t>
-        </is>
-      </c>
+      <c r="P37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -12255,22 +12255,18 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>per empty rank, most-held landing</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Deck Shaping</t>
-        </is>
-      </c>
+          <t>on the locked rank</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr"/>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Empty Ranks Coins</t>
+          <t>Crowd Favorite</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>heartZeroRanksCoin</t>
+          <t>crowdFavorite</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -12288,26 +12284,26 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>removalsUsed</t>
+          <t>dealsSurvived</t>
         </is>
       </c>
       <c r="L38" s="8" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>When your most-held rank ({rank}) lands in this column → +2 coins per rank with zero copies in your full deck</t>
+          <t>When a {rank} lands correctly in this column → +2 coins</t>
         </is>
       </c>
       <c r="O38" s="9" t="inlineStr">
         <is>
-          <t>heartZeroRanksCoin</t>
+          <t>rankCoin</t>
         </is>
       </c>
       <c r="P38" s="13" t="inlineStr">
@@ -12329,18 +12325,22 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>per ♥ top at end</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr"/>
+          <t>per empty rank, most-held landing</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Deck Shaping</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Envy</t>
+          <t>Empty Ranks Coins</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>envy</t>
+          <t>heartZeroRanksCoin</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -12358,29 +12358,33 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>milestone</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>runsPlayed</t>
+          <t>removalsUsed</t>
         </is>
       </c>
       <c r="L39" s="8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="M39" s="8" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>At deal end → +2 coins per pile in this column with a ♥</t>
+          <t>When your most-held rank ({rank}) lands in this column → +2 coins per rank with zero copies in your full deck</t>
         </is>
       </c>
       <c r="O39" s="9" t="inlineStr">
         <is>
-          <t>heartPiles</t>
-        </is>
-      </c>
-      <c r="P39" s="8" t="inlineStr"/>
+          <t>heartZeroRanksCoin</t>
+        </is>
+      </c>
+      <c r="P39" s="13" t="inlineStr">
+        <is>
+          <t>TEMPLATE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -12395,22 +12399,18 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>only pillar equipped</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Loadout</t>
-        </is>
-      </c>
+          <t>per ♥ top at end</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Greedy</t>
+          <t>Envy</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>envy</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -12433,21 +12433,21 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>dealsSurvived</t>
+          <t>runsPlayed</t>
         </is>
       </c>
       <c r="L40" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>At deal end if only equipped pillar → +1 coin per 5 cards in your full deck</t>
+          <t>At deal end → +2 coins per pile in this column with a ♥</t>
         </is>
       </c>
       <c r="O40" s="9" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>heartPiles</t>
         </is>
       </c>
       <c r="P40" s="8" t="inlineStr"/>
@@ -12465,18 +12465,22 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>if all survive</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr"/>
+          <t>only pillar equipped</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Loadout</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Greedy</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>columnGuardian</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -12489,21 +12493,31 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr"/>
-      <c r="L41" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>dealsSurvived</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="M41" s="8" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>At deal end if every pile in this column survived → +4 coins</t>
+          <t>At deal end if only equipped pillar → +1 coin per 5 cards in your full deck</t>
         </is>
       </c>
       <c r="O41" s="9" t="inlineStr">
         <is>
-          <t>columnAllAlive</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="P41" s="8" t="inlineStr"/>
@@ -12521,23 +12535,23 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>per suit landing</t>
+          <t>if all survive</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Heart Bonus</t>
+          <t>Guardian</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>heartBounty</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>columnGuardian</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
@@ -12554,12 +12568,12 @@
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>When a ♥ lands in this column → +1 coin</t>
+          <t>At deal end if every pile in this column survived → +4 coins</t>
         </is>
       </c>
       <c r="O42" s="9" t="inlineStr">
         <is>
-          <t>suitBounty</t>
+          <t>columnAllAlive</t>
         </is>
       </c>
       <c r="P42" s="8" t="inlineStr"/>
@@ -12577,23 +12591,23 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>if one pile survives</t>
+          <t>per suit landing</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Heart Bonus</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
+          <t>heartBounty</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
@@ -12601,31 +12615,21 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>pilesLost</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>55</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>At deal end if only one pile is alive → +8 coins</t>
+          <t>When a ♥ lands in this column → +1 coin</t>
         </is>
       </c>
       <c r="O43" s="9" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>suitBounty</t>
         </is>
       </c>
       <c r="P43" s="8" t="inlineStr"/>
@@ -12643,18 +12647,18 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>if none survive</t>
+          <t>if one pile survives</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Last Licks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>lastLicks</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -12681,17 +12685,17 @@
         </is>
       </c>
       <c r="L44" s="8" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="11" t="inlineStr">
         <is>
-          <t>At deal end if no pile in this column survived → +8 coins</t>
+          <t>At deal end if only one pile is alive → +8 coins</t>
         </is>
       </c>
       <c r="O44" s="9" t="inlineStr">
         <is>
-          <t>columnNoneAlive</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="P44" s="8" t="inlineStr"/>
@@ -12709,18 +12713,18 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>streak-grown</t>
+          <t>if none survive</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Streak Coin</t>
+          <t>Last Licks</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>streakCoin</t>
+          <t>lastLicks</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -12733,22 +12737,31 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J45" s="8" t="inlineStr"/>
-      <c r="K45" s="8" t="inlineStr"/>
-      <c r="L45" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>pilesLost</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>18</v>
+      </c>
       <c r="M45" s="8" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>From the 4th consecutive correct guess in this column → +1 coin per guess
-Resets on a wrong guess or a guess in another column</t>
+          <t>At deal end if no pile in this column survived → +8 coins</t>
         </is>
       </c>
       <c r="O45" s="9" t="inlineStr">
         <is>
-          <t>streakCoin</t>
+          <t>columnNoneAlive</t>
         </is>
       </c>
       <c r="P45" s="8" t="inlineStr"/>
@@ -12756,7 +12769,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -12766,22 +12779,18 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>doubles bonus, adds a curse</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Curse Payoff</t>
-        </is>
-      </c>
+          <t>streak-grown</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr"/>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Devil's Deal</t>
+          <t>Streak Coin</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>devilsDeal</t>
+          <t>streakCoin</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -12803,12 +12812,13 @@
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="11" t="inlineStr">
         <is>
-          <t>Double bonus coins earned this deal → add a curse to a top card in this column</t>
+          <t>From the 4th consecutive correct guess in this column → +1 coin per guess
+Resets on a wrong guess or a guess in another column</t>
         </is>
       </c>
       <c r="O46" s="9" t="inlineStr">
         <is>
-          <t>devilsDeal</t>
+          <t>streakCoin</t>
         </is>
       </c>
       <c r="P46" s="8" t="inlineStr"/>
@@ -12826,22 +12836,22 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>kills ♥ piles for coins</t>
+          <t>doubles bonus, adds a curse</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Pile Destruction</t>
+          <t>Curse Payoff</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Heart Demolish</t>
+          <t>Devil's Deal</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>heartDemolish</t>
+          <t>devilsDeal</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -12854,31 +12864,21 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J47" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K47" s="8" t="inlineStr">
-        <is>
-          <t>heartsPlayed</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="n">
-        <v>90</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>Destroy every ♥-topped pile in this column → +4 coins per pile</t>
+          <t>Double bonus coins earned this deal → add a curse to a top card in this column</t>
         </is>
       </c>
       <c r="O47" s="9" t="inlineStr">
         <is>
-          <t>heartDemolish</t>
+          <t>devilsDeal</t>
         </is>
       </c>
       <c r="P47" s="8" t="inlineStr"/>
@@ -12896,18 +12896,22 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>per ♥ in the column's piles, buried included</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr"/>
+          <t>kills ♥ piles for coins</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Pile Destruction</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Heart Tax</t>
+          <t>Heart Demolish</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>heartDemolish</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -12920,21 +12924,31 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J48" s="8" t="inlineStr"/>
-      <c r="K48" s="8" t="inlineStr"/>
-      <c r="L48" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>heartsPlayed</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>90</v>
+      </c>
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="11" t="inlineStr">
         <is>
-          <t>+1 coin per ♥ card in this column's piles — every card, not just the tops</t>
+          <t>Destroy every ♥-topped pile in this column → +4 coins per pile</t>
         </is>
       </c>
       <c r="O48" s="9" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>heartDemolish</t>
         </is>
       </c>
       <c r="P48" s="8" t="inlineStr"/>
@@ -12942,7 +12956,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Same-Powers</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -12952,18 +12966,18 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>per alive pile</t>
+          <t>per ♥ in the column's piles, buried included</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr"/>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Heart Tax</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>linkCoins</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -12972,7 +12986,7 @@
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
@@ -12985,88 +12999,78 @@
       <c r="M49" s="8" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
+          <t>+1 coin per ♥ card in this column's piles — every card, not just the tops</t>
+        </is>
+      </c>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="P49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Same-Powers</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Coin Gain</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>per alive pile</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr"/>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Dividend</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>linkCoins</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr"/>
+      <c r="K50" s="8" t="inlineStr"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="8" t="inlineStr"/>
+      <c r="N50" s="11" t="inlineStr">
+        <is>
           <t>+1 coin per alive pile</t>
         </is>
       </c>
-      <c r="O49" s="9" t="inlineStr">
+      <c r="O50" s="9" t="inlineStr">
         <is>
           <t>linkCoins</t>
         </is>
       </c>
-      <c r="P49" s="8" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="P50" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Deal Control  (2)</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Bases</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Deal Control</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>clears an ambush instantly</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>Escape Hatch</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>ambushOut</t>
-        </is>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K52" s="8" t="inlineStr">
-        <is>
-          <t>ambushesWon</t>
-        </is>
-      </c>
-      <c r="L52" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M52" s="8" t="inlineStr"/>
-      <c r="N52" s="11" t="inlineStr">
-        <is>
-          <t>If in a Just a Two ambush → clear the deal instantly</t>
-        </is>
-      </c>
-      <c r="O52" s="9" t="inlineStr">
-        <is>
-          <t>ambushWin</t>
-        </is>
-      </c>
-      <c r="P52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -13081,22 +13085,18 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>buries the deck, wins the deal</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Bury</t>
-        </is>
-      </c>
+          <t>clears an ambush instantly</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr"/>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Last Resort</t>
+          <t>Escape Hatch</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>lastResort</t>
+          <t>ambushOut</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -13119,106 +13119,106 @@
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>pilesLost</t>
+          <t>ambushesWon</t>
         </is>
       </c>
       <c r="L53" s="8" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="M53" s="8" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
+          <t>If in a Just a Two ambush → clear the deal instantly</t>
+        </is>
+      </c>
+      <c r="O53" s="9" t="inlineStr">
+        <is>
+          <t>ambushWin</t>
+        </is>
+      </c>
+      <c r="P53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Bases</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Deal Control</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>buries the deck, wins the deal</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Bury</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>Last Resort</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>lastResort</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>pilesLost</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="M54" s="8" t="inlineStr"/>
+      <c r="N54" s="11" t="inlineStr">
+        <is>
           <t>If not a boss deal → bury the whole deck under a pile in this column and win instantly (destroys itself and any adjacent Base)</t>
         </is>
       </c>
-      <c r="O53" s="9" t="inlineStr">
+      <c r="O54" s="9" t="inlineStr">
         <is>
           <t>lastResort</t>
         </is>
       </c>
-      <c r="P53" s="8" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="P54" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Deck Removal  (3)</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Pillars</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Deck Removal</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>the column's last death purges the killer</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Deck Shaping</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>Final Cut</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>finalPilePurge</t>
-        </is>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J56" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>pilesLost</t>
-        </is>
-      </c>
-      <c r="L56" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="M56" s="8" t="inlineStr"/>
-      <c r="N56" s="11" t="inlineStr">
-        <is>
-          <t>When the last pile in this column dies → permanently purge the card that killed it</t>
-        </is>
-      </c>
-      <c r="O56" s="9" t="inlineStr">
-        <is>
-          <t>finalPilePurge</t>
-        </is>
-      </c>
-      <c r="P56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -13228,22 +13228,22 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>the chosen top card</t>
+          <t>the column's last death purges the killer</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Pile Destruction</t>
+          <t>Deck Shaping</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Final Cut</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>sacrifice</t>
+          <t>finalPilePurge</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -13256,21 +13256,31 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J57" s="8" t="inlineStr"/>
-      <c r="K57" s="8" t="inlineStr"/>
-      <c r="L57" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>pilesLost</t>
+        </is>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="M57" s="8" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>Choose a pile → purge its top card from your deck, then kill that pile</t>
+          <t>When the last pile in this column dies → permanently purge the card that killed it</t>
         </is>
       </c>
       <c r="O57" s="9" t="inlineStr">
         <is>
-          <t>sacrifice</t>
+          <t>finalPilePurge</t>
         </is>
       </c>
       <c r="P57" s="8" t="inlineStr"/>
@@ -13278,7 +13288,7 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Same-Powers</t>
+          <t>Bases</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
@@ -13288,18 +13298,22 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>granted per Same, chosen at deal end (experiment)</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr"/>
+          <t>the chosen top card</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Pile Destruction</t>
+        </is>
+      </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Long Odds</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>linkPurge</t>
+          <t>sacrifice</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -13308,180 +13322,170 @@
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K58" s="8" t="inlineStr">
-        <is>
-          <t>removalsUsed</t>
-        </is>
-      </c>
-      <c r="L58" s="8" t="n">
-        <v>14</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr"/>
+      <c r="K58" s="8" t="inlineStr"/>
+      <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="11" t="inlineStr">
         <is>
+          <t>Choose a pile → purge its top card from your deck, then kill that pile</t>
+        </is>
+      </c>
+      <c r="O58" s="9" t="inlineStr">
+        <is>
+          <t>sacrifice</t>
+        </is>
+      </c>
+      <c r="P58" s="8" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Same-Powers</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Deck Removal</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>granted per Same, chosen at deal end (experiment)</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr"/>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Long Odds</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>linkPurge</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>removalsUsed</t>
+        </is>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="M59" s="8" t="inlineStr"/>
+      <c r="N59" s="11" t="inlineStr">
+        <is>
           <t>At deal end → purge a card of your choice, one per correct Same</t>
         </is>
       </c>
-      <c r="O58" s="9" t="inlineStr">
+      <c r="O59" s="9" t="inlineStr">
         <is>
           <t>linkPurge</t>
         </is>
       </c>
-      <c r="P58" s="8" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+      <c r="P59" s="8" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>Loadout &amp; Meta  (4)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>Pillars</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Loadout &amp; Meta</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>wards a Two; cleanses cursed landings</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Curse Removal</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Bouncer</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="F62" s="9" t="inlineStr">
         <is>
           <t>twoWard</t>
         </is>
       </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="n">
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J61" s="8" t="inlineStr">
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K61" s="8" t="inlineStr">
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>jokersPlayed</t>
         </is>
       </c>
-      <c r="L61" s="8" t="n">
+      <c r="L62" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="M61" s="8" t="inlineStr"/>
-      <c r="N61" s="11" t="inlineStr">
+      <c r="M62" s="8" t="inlineStr"/>
+      <c r="N62" s="11" t="inlineStr">
         <is>
           <t>50% chance to turn away a Just a Two mystery
 100% if your full deck has no 2s
 When a cursed card lands in this column → remove that curse from the card</t>
         </is>
       </c>
-      <c r="O61" s="9" t="inlineStr">
+      <c r="O62" s="9" t="inlineStr">
         <is>
           <t>twoWard</t>
-        </is>
-      </c>
-      <c r="P61" s="8" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>Pillars</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Loadout &amp; Meta</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>mirrors the centre pillar</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr"/>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>Ditto</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>ditto</t>
-        </is>
-      </c>
-      <c r="G62" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J62" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>runsWon</t>
-        </is>
-      </c>
-      <c r="L62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" s="8" t="inlineStr"/>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>Mirror the center column's Pillar</t>
-        </is>
-      </c>
-      <c r="O62" s="9" t="inlineStr">
-        <is>
-          <t>ditto</t>
         </is>
       </c>
       <c r="P62" s="8" t="inlineStr"/>
@@ -13499,22 +13503,18 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>finds the Queen; Queens pay on landing</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Coin Gain</t>
-        </is>
-      </c>
+          <t>mirrors the centre pillar</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr"/>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Queen-Finder</t>
+          <t>Ditto</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>queenFinder</t>
+          <t>ditto</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -13532,170 +13532,174 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>jokersPlayed</t>
+          <t>runsWon</t>
         </is>
       </c>
       <c r="L63" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M63" s="8" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
+        <is>
+          <t>Mirror the center column's Pillar</t>
+        </is>
+      </c>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t>ditto</t>
+        </is>
+      </c>
+      <c r="P63" s="8" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Pillars</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Loadout &amp; Meta</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>finds the Queen; Queens pay on landing</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Coin Gain</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Queen-Finder</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>queenFinder</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>jokersPlayed</t>
+        </is>
+      </c>
+      <c r="L64" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M64" s="8" t="inlineStr"/>
+      <c r="N64" s="11" t="inlineStr">
         <is>
           <t>+50% chance to find a Beheaded Queen at a mystery node
 100% if Queens are your most-held rank
 When a Queen lands in this column → +1 coin</t>
         </is>
       </c>
-      <c r="O63" s="9" t="inlineStr">
+      <c r="O64" s="9" t="inlineStr">
         <is>
           <t>queenFinder</t>
         </is>
       </c>
-      <c r="P63" s="8" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="P64" s="8" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>Bases</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Loadout &amp; Meta</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>recharges the other bases</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr"/>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr"/>
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>Reactor</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F65" s="9" t="inlineStr">
         <is>
           <t>refreshBases</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H64" s="8" t="n">
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J64" s="8" t="inlineStr">
+      <c r="J65" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K64" s="8" t="inlineStr">
+      <c r="K65" s="8" t="inlineStr">
         <is>
           <t>basesPlaced</t>
         </is>
       </c>
-      <c r="L64" s="8" t="n">
+      <c r="L65" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="M64" s="8" t="inlineStr"/>
-      <c r="N64" s="11" t="inlineStr">
+      <c r="M65" s="8" t="inlineStr"/>
+      <c r="N65" s="11" t="inlineStr">
         <is>
           <t>Recharge your other two Bases</t>
         </is>
       </c>
-      <c r="O64" s="9" t="inlineStr">
+      <c r="O65" s="9" t="inlineStr">
         <is>
           <t>refreshBases</t>
         </is>
       </c>
-      <c r="P64" s="8" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="inlineStr">
+      <c r="P65" s="8" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>Pack  (4)</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>Packs</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Pack</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>playing cards</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>Large Card Pack</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>cardPack</t>
-        </is>
-      </c>
-      <c r="G67" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K67" s="8" t="inlineStr">
-        <is>
-          <t>dealsWonRegular</t>
-        </is>
-      </c>
-      <c r="L67" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="M67" s="8" t="inlineStr"/>
-      <c r="N67" s="11" t="inlineStr">
-        <is>
-          <t>Reveal 5 random cards — keep 2 to swap into your deck</t>
-        </is>
-      </c>
-      <c r="O67" s="9" t="inlineStr">
-        <is>
-          <t>card</t>
-        </is>
-      </c>
-      <c r="P67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -13710,27 +13714,27 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>stickers</t>
+          <t>playing cards</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr"/>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Large Sticker Pack</t>
+          <t>Large Card Pack</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>largeStickerPack</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>cardPack</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
@@ -13739,26 +13743,26 @@
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>milestone</t>
         </is>
       </c>
       <c r="K68" s="8" t="inlineStr">
         <is>
-          <t>stickersApplied</t>
+          <t>dealsWonRegular</t>
         </is>
       </c>
       <c r="L68" s="8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="11" t="inlineStr">
         <is>
-          <t>Reveal 5 random stickers — keep 2</t>
+          <t>Reveal 5 random cards — keep 2 to swap into your deck</t>
         </is>
       </c>
       <c r="O68" s="9" t="inlineStr">
         <is>
-          <t>sticker</t>
+          <t>card</t>
         </is>
       </c>
       <c r="P68" s="8" t="inlineStr"/>
@@ -13776,18 +13780,18 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>playing cards</t>
+          <t>stickers</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Small Card Pack</t>
+          <t>Large Sticker Pack</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>smallCardPack</t>
+          <t>largeStickerPack</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -13796,25 +13800,35 @@
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J69" s="8" t="inlineStr"/>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K69" s="8" t="inlineStr">
+        <is>
+          <t>stickersApplied</t>
+        </is>
+      </c>
+      <c r="L69" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="M69" s="8" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>Reveal 3 random cards — keep 1 to swap into your deck</t>
+          <t>Reveal 5 random stickers — keep 2</t>
         </is>
       </c>
       <c r="O69" s="9" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>sticker</t>
         </is>
       </c>
       <c r="P69" s="8" t="inlineStr"/>
@@ -13832,18 +13846,18 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>stickers</t>
+          <t>playing cards</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr"/>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Small Sticker Pack</t>
+          <t>Small Card Pack</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>stickerPack</t>
+          <t>smallCardPack</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -13852,7 +13866,7 @@
         </is>
       </c>
       <c r="H70" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
@@ -13865,286 +13879,276 @@
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr">
         <is>
+          <t>Reveal 3 random cards — keep 1 to swap into your deck</t>
+        </is>
+      </c>
+      <c r="O70" s="9" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="P70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>stickers</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Small Sticker Pack</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>stickerPack</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr"/>
+      <c r="K71" s="8" t="inlineStr"/>
+      <c r="L71" s="8" t="n"/>
+      <c r="M71" s="8" t="inlineStr"/>
+      <c r="N71" s="11" t="inlineStr">
+        <is>
           <t>Reveal 3 random stickers — keep 1</t>
         </is>
       </c>
-      <c r="O70" s="9" t="inlineStr">
+      <c r="O71" s="9" t="inlineStr">
         <is>
           <t>sticker</t>
         </is>
       </c>
-      <c r="P70" s="8" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="15" t="inlineStr">
-        <is>
-          <t>Peek  (12)</t>
-        </is>
-      </c>
+      <c r="P71" s="8" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>Peek  (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>Stickers</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>Peek</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>needs a base-free column</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr"/>
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>Base Scout</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F74" s="9" t="inlineStr">
         <is>
           <t>baseScout</t>
         </is>
       </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="n">
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J73" s="8" t="inlineStr">
+      <c r="J74" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K73" s="8" t="inlineStr">
+      <c r="K74" s="8" t="inlineStr">
         <is>
           <t>basesPlaced</t>
         </is>
       </c>
-      <c r="L73" s="8" t="n">
+      <c r="L74" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="M73" s="8" t="inlineStr"/>
-      <c r="N73" s="11" t="inlineStr">
+      <c r="M74" s="8" t="inlineStr"/>
+      <c r="N74" s="11" t="inlineStr">
         <is>
           <t>If in column with no Base → peek next card
 If this card kills its pile → this becomes a curse</t>
         </is>
       </c>
-      <c r="O73" s="9" t="inlineStr">
+      <c r="O74" s="9" t="inlineStr">
         <is>
           <t>baseScout</t>
         </is>
       </c>
-      <c r="P73" s="8" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="P74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>Stickers</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Peek</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>needs a pillar-free column</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr"/>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr"/>
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>Pillar Scout</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>pillarScout</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="n">
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I74" s="8" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J74" s="8" t="inlineStr">
+      <c r="J75" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K74" s="8" t="inlineStr">
+      <c r="K75" s="8" t="inlineStr">
         <is>
           <t>pillarsPlaced</t>
         </is>
       </c>
-      <c r="L74" s="8" t="n">
+      <c r="L75" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="M74" s="8" t="inlineStr"/>
-      <c r="N74" s="11" t="inlineStr">
+      <c r="M75" s="8" t="inlineStr"/>
+      <c r="N75" s="11" t="inlineStr">
         <is>
           <t>If in column with no Pillar → peek next card
 If this card kills its pile → this becomes a curse</t>
         </is>
       </c>
-      <c r="O74" s="9" t="inlineStr">
+      <c r="O75" s="9" t="inlineStr">
         <is>
           <t>pillarScout</t>
         </is>
       </c>
-      <c r="P74" s="8" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="P75" s="8" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>Stickers</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Peek</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>on landing; curse on kill</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr"/>
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>Twin Spark</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F76" s="9" t="inlineStr">
         <is>
           <t>twinSpark</t>
         </is>
       </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="n">
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J75" s="8" t="inlineStr">
+      <c r="J76" s="8" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="K75" s="8" t="inlineStr">
+      <c r="K76" s="8" t="inlineStr">
         <is>
           <t>zenGamesPlayed</t>
         </is>
       </c>
-      <c r="L75" s="8" t="n">
+      <c r="L76" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="M75" s="8" t="inlineStr"/>
-      <c r="N75" s="11" t="inlineStr">
+      <c r="M76" s="8" t="inlineStr"/>
+      <c r="N76" s="11" t="inlineStr">
         <is>
           <t>Peek next card
 If this card kills its pile → this becomes a curse</t>
         </is>
       </c>
-      <c r="O75" s="9" t="inlineStr">
+      <c r="O76" s="9" t="inlineStr">
         <is>
           <t>twinSpark</t>
-        </is>
-      </c>
-      <c r="P75" s="8" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Pillars</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Peek</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>on a pile death</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>Last Rites</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>lastRites</t>
-        </is>
-      </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>behavior</t>
-        </is>
-      </c>
-      <c r="K76" s="8" t="inlineStr">
-        <is>
-          <t>dealsWonLegendary</t>
-        </is>
-      </c>
-      <c r="L76" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M76" s="8" t="inlineStr"/>
-      <c r="N76" s="11" t="inlineStr">
-        <is>
-          <t>When a pile in this column dies → peek next card</t>
-        </is>
-      </c>
-      <c r="O76" s="9" t="inlineStr">
-        <is>
-          <t>lastRites</t>
         </is>
       </c>
       <c r="P76" s="8" t="inlineStr"/>
@@ -14162,18 +14166,18 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>on a royal ♠</t>
+          <t>on a pile death</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr"/>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Queen's Eye</t>
+          <t>Last Rites</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>queensEye</t>
+          <t>lastRites</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -14186,21 +14190,31 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J77" s="8" t="inlineStr"/>
-      <c r="K77" s="8" t="inlineStr"/>
-      <c r="L77" s="8" t="n"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>dealsWonLegendary</t>
+        </is>
+      </c>
+      <c r="L77" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="M77" s="8" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>When a royal ♠ (J/Q/K) lands in this column → peek next card</t>
+          <t>When a pile in this column dies → peek next card</t>
         </is>
       </c>
       <c r="O77" s="9" t="inlineStr">
         <is>
-          <t>queensEye</t>
+          <t>lastRites</t>
         </is>
       </c>
       <c r="P77" s="8" t="inlineStr"/>
@@ -14208,7 +14222,7 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>Bases</t>
+          <t>Pillars</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -14218,22 +14232,18 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>trades the deal's banked bonus</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Coin Loss</t>
-        </is>
-      </c>
+          <t>on a royal ♠</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Bonus Reset</t>
+          <t>Queen's Eye</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>bonusResetPeek</t>
+          <t>queensEye</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -14246,31 +14256,21 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J78" s="8" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="K78" s="8" t="inlineStr">
-        <is>
-          <t>coinsEarnedLifetime</t>
-        </is>
-      </c>
-      <c r="L78" s="8" t="n">
-        <v>80</v>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr"/>
+      <c r="K78" s="8" t="inlineStr"/>
+      <c r="L78" s="8" t="n"/>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>Reset bonus coins earned this deal to 0 → peek next card</t>
+          <t>When a royal ♠ (J/Q/K) lands in this column → peek next card</t>
         </is>
       </c>
       <c r="O78" s="9" t="inlineStr">
         <is>
-          <t>bonusResetPeek</t>
+          <t>queensEye</t>
         </is>
       </c>
       <c r="P78" s="8" t="inlineStr"/>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>rares twice as often; +1 per stickered landing</t>
+          <t>rares twice as often; deal-end +1 per sticker bought this climb</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
@@ -17245,7 +17245,7 @@
       <c r="N136" s="11" t="inlineStr">
         <is>
           <t>Rare items appear in the store twice as often
-When a stickered card lands in this column → +1 coin</t>
+At deal end → +1 coin per sticker bought in the shop this climb</t>
         </is>
       </c>
       <c r="O136" s="9" t="inlineStr">
@@ -18722,24 +18722,24 @@
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A160:P160"/>
-    <mergeCell ref="A17:P17"/>
     <mergeCell ref="A126:P126"/>
     <mergeCell ref="A131:P131"/>
     <mergeCell ref="A171:P171"/>
-    <mergeCell ref="A72:P72"/>
+    <mergeCell ref="A52:P52"/>
+    <mergeCell ref="A67:P67"/>
     <mergeCell ref="A114:P114"/>
+    <mergeCell ref="A34:P34"/>
     <mergeCell ref="A167:P167"/>
     <mergeCell ref="A157:P157"/>
     <mergeCell ref="A148:P148"/>
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="A60:P60"/>
+    <mergeCell ref="A73:P73"/>
+    <mergeCell ref="A61:P61"/>
     <mergeCell ref="A153:P153"/>
-    <mergeCell ref="A66:P66"/>
+    <mergeCell ref="A18:P18"/>
+    <mergeCell ref="A56:P56"/>
     <mergeCell ref="A120:P120"/>
-    <mergeCell ref="A55:P55"/>
     <mergeCell ref="A139:P139"/>
     <mergeCell ref="A86:P86"/>
-    <mergeCell ref="A33:P33"/>
     <mergeCell ref="A175:P175"/>
     <mergeCell ref="A95:P95"/>
     <mergeCell ref="A2:P2"/>
